--- a/exports/TEA_2023_importacao_comentada_com_niveis_ia.xlsx
+++ b/exports/TEA_2023_importacao_comentada_com_niveis_ia.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Código Civil Brasileiro, art. 951; Código de Ética Médica, CFM.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 3: Legislação Aplicada à Prática da Anestesiologia</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sociedade Brasileira de Anestesiologia. Estatuto Social e documentos institucionais.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 2: As Associações de Anestesiologistas no Brasil e no Mundo</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash Clinical Anesthesia, 9th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 5: Risco Profissional do Anestesiologista e Transtorno de Uso de Susbstâncias</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 72: Avaliação e Condutas Pré-anestésicas</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 72: Avaliação e Condutas Pré-anestésicas</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 68: Via Aérea Difícil</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 23: Anatomia do Sistema Respiratório</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 86: Monitorização do Sistema Nervoso • Miller's Anesthesia, 10ª ed. — cap. 30: Patient Positioning and Associated Risks</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 171: Anestesia para Cirurgias da Coluna</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 85: Princípios da Monitorização e Instrumentação Intraoperatória</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 87: Monitorização do Sistema Respiratório</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 87: Monitorização do Sistema Respiratório</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 21: Anatomia e Fisiologia do Sistema Nervoso Autônomo • Guyton &amp; Hall, Tratado de Fisiologia Médica, 14ª ed. — cap. 61: Sistema Nervoso Autônomo e Medula Adrenal</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 172: Fatores Determinantes das Pressões Intracranianas e de Perfusão Encefálica • Miller's Anesthesia, 10ª ed. — cap. 10: Cerebral Physiology and the Effects of Anesthetic Drugs</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 49: Antagonistas Adrenérgicos</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 51: Arritmias Cardíacas e Tratamento Farmacológico</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 24: Mecânica Respiratória e Controle da Respiração • Guyton &amp; Hall, Tratado de Fisiologia Médica, 14ª ed. — cap. 38: Ventilação Pulmonar</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 23: Anatomia do Sistema Respiratório • Guyton &amp; Hall, Tratado de Fisiologia Médica, 14ª ed. — cap. 38: Ventilação Pulmonar</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 38: Conceitos Farmacocinéticos e Farmacodinâmicos • Stoelting's Pharmacology &amp; Physiology in Anesthetic Practice, 6ª ed. — cap. 2: Basic Principles of Pharmacology</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 101: Anestesia Venosa Total Luiz Eduardo de Paula Gomes Miziara • Miller's Anesthesia, 10ª ed. — cap. 23: Intravenous Drug Delivery Systems</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 44: Hipnóticos: Propofol, Etomidato, Cetamina e Alfa 2 Agonistas • Miller's Anesthesia, 10ª ed. — cap. 21: Intravenous Anesthetics</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 44: Hipnóticos: Propofol, Etomidato, Cetamina e Alfa 2 Agonistas • Miller's Anesthesia, 10ª ed. — cap. 21: Intravenous Anesthetics</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 41: Farmacocinética dos Anestésicos Inalatórios • Miller's Anesthesia, 10ª ed. — cap. 18: Inhaled Anesthetic Uptake, Distribution, Metabolism, and Toxicity</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 41: Farmacocinética dos Anestésicos Inalatórios • Miller's Anesthesia, 10ª ed. — cap. 18: Inhaled Anesthetic Uptake, Distribution, Metabolism, and Toxicity</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 42: Anestésicos Locais • Peripheral Nerve Blocks and Anatomy for Ultrasound-Guided Regional Anesthesia (2021) — cap. 2: Local Anesthetics: Clinical Pharmacology and Selection</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 42: Anestésicos Locais • Peripheral Nerve Blocks and Anatomy for Ultrasound-Guided Regional Anesthesia (2021) — cap. 2: Local Anesthetics: Clinical Pharmacology and Selection</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 53: Bloqueadores Neuromusculares e Antagonistas • Stoelting's Pharmacology &amp; Physiology in Anesthetic Practice, 6ª ed. — cap. 12: Neuromuscular-Blocking Drugs and Reversal Agents</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 22: Fisiologia da Função Neuromuscular • Miller's Anesthesia, 10ª ed. — cap. 31: Neuromuscular Disorders and Other Genetic Disorders</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>American Heart Association. Guidelines for CPR and ECC; Morgan &amp; Mikhail, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 201: Reanimação Cardiorrespiratória no Adulto</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>American Heart Association. Guidelines for CPR and ECC; Morgan &amp; Mikhail, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 201: Reanimação Cardiorrespiratória no Adulto</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 106: Anestesia Peridural Bruno Erick Sinedino de Araújo • Miller's Anesthesia, 10ª ed. — cap. 41: Spinal, Epidural, and Caudal Anesthesia</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 103: Elementos de Anatomia: Ressonância Nuclear Magnética e Tomografia Computadorizada • Miller's Anesthesia, 10ª ed. — cap. 52: Anesthesia for Vascular Surgery</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 53: Bloqueadores Neuromusculares e Antagonistas • Miller's Anesthesia, 10ª ed. — cap. 39: Neuromuscular Monitoring</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 125: Eventos Adversos na Recuperação Pós-Anestésica</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash Clinical Anesthesia, 9th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 227: Tipos de Estudo e Planejamento de Pesquisa</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 87: Monitorização do Sistema Respiratório</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 61: Vaporizadores e Fluxômetros</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 60: Componenetes dos Aparelhos de Anestesia</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 40: Anestésicos Inalatórios • Miller's Anesthesia, 10ª ed. — cap. 17: Inhaled Anesthetics: Mechanisms of Action</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 190: Anestesia para Eletroconvulsoterapia Julio Cesar Mercador de Freitas</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 113: Anestesia Regional Intravenosa Leonardo de Andrade Reis • Miller's Anesthesia, 10ª ed. — cap. 25: Local Anesthetics</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 104: Bloqueios Regionais Guiados pela Ultrassonografia • Peripheral Nerve Blocks and Anatomy for Ultrasound-Guided Regional Anesthesia (2021) — cap. 6: Monitoring and Documentation in Regional Anesthesia</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 95: Equilíbrio Ácido-base e Hidroeletrolítico</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 98: Terapia de Fluidos Perioperatória</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; diretrizes de reversão de anticoagulantes.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 57: Anticoagulantes e Antiagregantes Plaquetários</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 76: Avaliação do Sistema Renal • Miller's Anesthesia, 10ª ed. — cap. 55: Anesthesia and the Renal and Genitourinary Systems</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.; referências de anestesia urológica.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 167: Anestesia para Litotripsia Extracorpórea por Ondas de Choque</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Chestnut's Obstetric Anesthesia, 6th ed.; Miller's Anesthesia, 9th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 128: Analgesia Para o Trabalho de Parto</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Chestnut's Obstetric Anesthesia, 6th ed.; Miller's Anesthesia, 9th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 128: Analgesia Para o Trabalho de Parto</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 171: Anestesia para Cirurgias da Coluna</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 163: Anestesia para Cirurgia Videolaparoscópica e Robótica</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 183: Anestesia para Cirurgias Orais, Nasais, Seios da Face e Ouvidos</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 181: Anestesia em Oftalmologia: Fisiologia Ocular e</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 185: Anestesia Ambulatorial</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 124: Estágios da Recuperação da Anestesia: Aspectos Clínicos e Critérios de Alta André de Moraes Porto</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 37: Resposta Neuroendócrina, Imunológica e Metabólica ao Trauma Cirúrgico • Miller's Anesthesia, 10ª ed. — cap. 41: Spinal, Epidural, and Caudal Anesthesia</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 72: Avaliação e Condutas Pré-anestésicas</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 82: Jejum Pré-anestésico e Avaliação do Conteúdo Gástrico</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 209: Fisiopatologia do Estado de Choque</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 176: Anestesia no Trauma Cranioencefálico</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 91: Monitorização do Sistema Endócrino</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 169: Anestesia para Cirurgias Ortopédicas dos Membros Superiores • Peripheral Nerve Blocks and Anatomy for Ultrasound-Guided Regional Anesthesia (2021) — cap. 8: Continuous Peripheral Nerve Blocks</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 178: Anestesia para Cirurgia Bucomaxilofacial</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 149: Ventilação Monopulmonar</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 155: Anestesia para Cirurgia Valvar</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 153: Circulação Extracorpórea e Assistência Circulatória Mecânica</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 173: Anestesia para Cirurgia de Tumores Cerebrais Christiano dos Santos e Santos</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 94: Regulação e Monitorização da Temperatura</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; textos de medicina perioperatória e choque.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 215: Avaliação e Abordagem do Paciente Politraumatizado</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; textos de medicina perioperatória e choque.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 209: Fisiopatologia do Estado de Choque</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 82: Jejum Pré-anestésico e Avaliação do Conteúdo Gástrico</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>A Practice of Anesthesia for Infants and Children, 7th ed.; Morgan &amp; Mikhail, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 145: Reposição Volêmica e Hemotransfusão em</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>A Practice of Anesthesia for Infants and Children, 7th ed.; Morgan &amp; Mikhail, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 143: Anestesia Regional em Pediatria</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 186: Anestesia para Radiodiagnóstico Antônio Márcio de Sanfim Arantes Pereira</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash Clinical Anesthesia, 9th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 116: Avaliação e Tratamento da Dor Aguda</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash Clinical Anesthesia, 9th ed.</t>
+          <t>Miller's Anesthesia, 10ª ed. — cap. 28: Preoperative Evaluation</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 60: Componenetes dos Aparelhos de Anestesia</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash Clinical Anesthesia, 9th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 10: Segurança do Paciente na Anestesia</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash Clinical Anesthesia, 9th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 6: Fundamentos de Organização e Gestão para Serviços de Anestesia</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Miller's Anesthesia, 9th ed.; Barash, Cullen and Stoelting's Clinical Anesthesia, 9th ed.; Morgan &amp; Mikhail's Clinical Anesthesiology, 7th ed.</t>
+          <t>SAESP, Tratado de Anestesiologia, 10ª ed. — cap. 92: Monitorização do Sistema Hematológico</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">

--- a/exports/TEA_2023_importacao_comentada_com_niveis_ia.xlsx
+++ b/exports/TEA_2023_importacao_comentada_com_niveis_ia.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A responsabilidade civil do médico, como regra, é subjetiva: exige demonstração de conduta culposa, dano e nexo causal. Resultado desfavorável, isoladamente, não prova erro médico; a análise deve considerar imperícia, imprudência ou negligência.</t>
+          <t>&lt;p&gt;A responsabilidade profissional do médico organiza-se em eixos distintos (civil, penal e ético-profissional), todos assentados sobre um mesmo núcleo: a existência de &lt;strong&gt;conduta culposa&lt;/strong&gt; e a comprovação do &lt;strong&gt;nexo de causalidade&lt;/strong&gt; entre o ato médico e o dano. É esse núcleo que define a chamada &lt;strong&gt;responsabilidade subjetiva&lt;/strong&gt;: sem demonstração de imperícia, imprudência ou negligência, não há dever de indenizar, por mais grave que tenha sido o desfecho.&lt;/p&gt;&lt;p&gt;Daí decorre o segundo pilar do tema: a anestesiologia constitui &lt;strong&gt;obrigação de meio&lt;/strong&gt;, e não de resultado. O anestesiologista compromete-se a dedicar tempo, conhecimento atualizado e a tecnologia disponível ao cuidado do paciente; não se compromete a entregar um desfecho determinado. Quando o resultado almejado não é alcançado apesar da conduta tecnicamente adequada, não se lhe pode atribuir responsabilidade. Convém separar ainda &lt;strong&gt;iatrogenia&lt;/strong&gt; (gênero que reúne todos os resultados negativos da intervenção em saúde) do &lt;strong&gt;erro médico&lt;/strong&gt; propriamente dito, que é a espécie decorrente da violação do dever de cuidado. No caso descrito, a parestesia intensa referida durante a punção e a recusa em acolher a queixa são elementos que devem ser periciados como possível quebra do dever de cuidado; o déficit motor, isoladamente, não prova nada.&lt;/p&gt;&lt;p&gt;Vale registrar que a responsabilidade das &lt;strong&gt;pessoas jurídicas&lt;/strong&gt; prestadoras de serviço de saúde segue lógica oposta: é &lt;strong&gt;objetiva&lt;/strong&gt;, bastando ação de preposto, dano e nexo causal, ainda que ausente a culpa.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Responsabilidade civil do médico é subjetiva&lt;/strong&gt;: correta. Exige a tríade conduta culposa, dano e nexo causal, exatamente o núcleo comum aos eixos civil, penal e ético.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Prova da culpa incumbiria ao hospital e ao plano de saúde&lt;/strong&gt;: incorreta. Confunde dois regimes autônomos: o hospital responde objetivamente por seus prepostos, o que não desloca para ele o encargo de demonstrar a culpa pessoal do anestesiologista.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Responsabilidade médica seria de resultado&lt;/strong&gt;: incorreta. A prática anestésica é obrigação de meio; a obrigação de resultado impõe a entrega do produto da atividade, situação que não se aplica aqui.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Mau resultado decorreria de erro médico&lt;/strong&gt;: incorreta. É precisamente a equação que a doutrina rejeita: o resultado desfavorável pode ocorrer sem qualquer violação do dever de cuidado.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Conforme a estrutura estatutária da SBA, o Conselho Superior reúne os três últimos presidentes da entidade e os presidentes das associações regionais. As demais alternativas atribuem composição ou direitos que não correspondem ao estatuto.</t>
+          <t>&lt;p&gt;A estrutura associativa da SBA cobra do candidato precisão sobre dois pontos que costumam ser confundidos: a &lt;strong&gt;composição dos órgãos&lt;/strong&gt; e as &lt;strong&gt;categorias de membros&lt;/strong&gt;. A Sociedade organiza-se em Assembleia Geral, Assembleia de Representantes, Conselho Superior, Conselho Fiscal, Diretoria, Conselho de Defesa Profissional e Departamentos.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;Conselho Superior&lt;/strong&gt; é órgão de natureza consultiva e independente da Diretoria, formado pelos &lt;strong&gt;três últimos Diretores-Presidentes&lt;/strong&gt; da entidade somados aos &lt;strong&gt;Presidentes das Regionais&lt;/strong&gt;, desenho que preserva memória institucional e representatividade federativa, coerente com a constituição da SBA como federação de associações regionais. Não confundir com o &lt;strong&gt;Conselho Fiscal&lt;/strong&gt;, composto por três membros efetivos e três suplentes eleitos pela Assembleia Geral, com mandato de três anos e função de auditoria financeira trimestral.&lt;/p&gt;&lt;p&gt;Quanto às categorias, a distinção decisiva é entre &lt;strong&gt;Aspirante&lt;/strong&gt; (o médico em especialização em Centro de Ensino e Treinamento credenciado pela SBA) e &lt;strong&gt;Adjunto&lt;/strong&gt; (o associado que já pratica a Anestesiologia mas não possui o Título de Especialista). Há ainda o Aspirante-adjunto, para quem cursa residência em serviço credenciado pela CNRM-MEC fora do quadro oficial de CETs.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Conselho Superior formado pelos três últimos presidentes e pelos presidentes das Regionais&lt;/strong&gt;: correta, reproduz literalmente a composição estatutária.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Departamentos sob diretores administrativo, científico e fiscal&lt;/strong&gt;: incorreta. Os Departamentos são Administrativo, Científico e de Defesa Profissional; o Fiscal é Conselho, não Departamento.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Adjuntos seriam os médicos em especialização nos CETs&lt;/strong&gt;: incorreta. Essa é a definição de membro Aspirante; Adjunto é quem exerce a especialidade sem o TEA.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aspirantes teriam direito de participar da Assembleia Geral&lt;/strong&gt;: incorreta. Esse direito integra o rol excetuado para as demais categorias, permanecendo com os membros Ativos e equiparados.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A síndrome de burnout é caracterizada por exaustão emocional, despersonalização e redução da realização profissional. A despersonalização leva a atitudes frias, distantes ou cínicas em relação aos pacientes e ao trabalho.</t>
+          <t>&lt;p&gt;A anestesiologia figura entre as especialidades de maior carga de estresse ocupacional, e as consequências documentadas desse estresse são graves e mensuráveis: &lt;strong&gt;queda da vigilância&lt;/strong&gt;, indução ao &lt;strong&gt;erro médico&lt;/strong&gt;, instalação de quadros de &lt;strong&gt;ansiedade e depressão&lt;/strong&gt;, evolução para dependência de álcool e outras drogas e taxa de &lt;strong&gt;suicídio superior à de outras especialidades médicas&lt;/strong&gt;. É esse conjunto que se organiza sob o rótulo de &lt;strong&gt;síndrome de burnout&lt;/strong&gt;, cada vez mais reconhecida na especialidade.&lt;/p&gt;&lt;p&gt;O ponto que a questão explora é a natureza do fenômeno: burnout não é falha de caráter nem indisciplina, e sim um &lt;strong&gt;processo de desgaste ocupacional&lt;/strong&gt; no qual o profissional se distancia afetivamente do trabalho e das pessoas de quem cuida. A &lt;strong&gt;despersonalização&lt;/strong&gt; traduz exatamente esse distanciamento, em que a relação com o paciente torna-se impessoal, instrumental, por vezes cínica, e é o eixo que melhor diferencia o burnout de um simples quadro de fadiga ou de um transtorno de humor isolado.&lt;/p&gt;&lt;p&gt;A vulnerabilidade é maior entre &lt;strong&gt;residentes e profissionais nos primeiros anos&lt;/strong&gt; de atividade. As medidas protetoras descritas são organizacionais antes de individuais: jornadas definidas e não superiores a oito horas diárias, períodos de descanso ao longo do turno, plantões que não ultrapassem 24 horas e ao menos um dia de folga semanal.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Despersonalização do profissional&lt;/strong&gt;: correta. É a dimensão que caracteriza o afastamento afetivo do trabalho e do paciente, marca central da síndrome.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Autoconfiança em excesso&lt;/strong&gt;: incorreta. O curso descrito é de esgotamento e retração, com ansiedade e depressão, e não de autoconfiança inflada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Imprudência na prática profissional&lt;/strong&gt;: incorreta. Imprudência é modalidade de culpa no campo jurídico; o que o burnout produz é queda de vigilância, que pode favorecer o erro, mas não se confunde com a categoria legal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Desrespeito às regras institucionais&lt;/strong&gt;: incorreta. Trata-se de conduta disciplinar, sem qualquer respaldo como elemento definidor da síndrome.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A investigação pré-operatória deve ser seletiva e guiada por história clínica, exame físico, comorbidades e porte do procedimento. Solicitar exames de rotina sem indicação clínica aumenta custos e falsos-positivos sem benefício comprovado.</t>
+          <t>&lt;p&gt;O conceito que estrutura toda a questão é a definição de &lt;strong&gt;exame de rotina&lt;/strong&gt;: aquele solicitado para procurar condições não detectadas pela história clínica e pelo exame físico, em paciente assintomático e sem qualquer indicação clínica. Uma vez fixada essa definição, a conclusão das revisões sistemáticas e das recomendações de sociedades é direta: &lt;strong&gt;exames pré-operatórios não devem ser solicitados de rotina&lt;/strong&gt;, mas apenas quando indicados pela anamnese e pelo exame físico.&lt;/p&gt;&lt;p&gt;A racionalidade é dupla. Do ponto de vista epidemiológico, aplicar um teste a uma população de baixa prevalência multiplica os &lt;strong&gt;falso-positivos&lt;/strong&gt;, que geram investigação adicional, adiamento cirúrgico, ansiedade e custo sem qualquer ganho de desfecho. Do ponto de vista assistencial, o exame indiscriminado desloca a atenção da avaliação clínica, que é o instrumento de maior rendimento na estratificação de risco. Essa lógica foi consolidada na campanha &lt;strong&gt;Choosing Wisely&lt;/strong&gt;, cuja recomendação explícita é não obter hemograma, bioquímica e testes de coagulação em pacientes &lt;strong&gt;ASA I ou II&lt;/strong&gt; submetidos a cirurgias de &lt;strong&gt;baixo risco&lt;/strong&gt; com perda volêmica mínima esperada.&lt;/p&gt;&lt;p&gt;O mesmo princípio se aplica aos exames cardiológicos: ecocardiograma, teste ergométrico e teste de estresse são reservados a situações específicas, definidas em conjunto com o especialista, diante de escassez de evidência de impacto sobre a evolução perioperatória quando aplicados amplamente.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Exames seletivos solicitados após considerar informações específicas do prontuário&lt;/strong&gt;: correta. Traduz o princípio da indicação individualizada, ancorada em dados clínicos, que é a conduta recomendada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Radiografia de tórax em todos acima de 60 anos&lt;/strong&gt;: incorreta. Idade isolada não indica exame; o gatilho deve ser um achado clínico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Provas de função pulmonar para cirurgia não cardíaca&lt;/strong&gt;: incorreta. Não integram a avaliação de rotina desse cenário, tendo indicação restrita e situacional.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hemograma e hemoglobina necessários antes de toda cirurgia eletiva&lt;/strong&gt;: incorreta. É exatamente a prática desaconselhada de forma nominal em pacientes ASA I e II operados de procedimentos de baixo risco.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pacientes dependentes de opioides podem necessitar de abordagem pré-anestésica individualizada para evitar abstinência, reduzir ansiedade e manter terapia basal. Nos extremos de idade, baixa reserva fisiológica e trauma cranioencefálico, depressores exigem maior cautela.</t>
+          <t>&lt;p&gt;A medicação pré-anestésica persegue objetivos definidos: reduzir &lt;strong&gt;ansiedade&lt;/strong&gt; e medo, diminuir o metabolismo basal, potencializar os agentes anestésicos, produzir &lt;strong&gt;amnésia&lt;/strong&gt; e oferecer analgesia pré e pós-operatória. O fármaco mais empregado é o &lt;strong&gt;midazolam&lt;/strong&gt;, benzodiazepínico hidrossolúvel de curta duração, que seda, produz amnésia e relaxamento muscular com depressão ventilatória e cardiovascular mínimas, mas que é &lt;strong&gt;desprovido de efeito analgésico&lt;/strong&gt; e pode causar agitação paradoxal na vigência de dor.&lt;/p&gt;&lt;p&gt;O raciocínio-chave da questão é reconhecer quem tem &lt;strong&gt;margem de segurança estreita&lt;/strong&gt; diante de um depressor do sistema nervoso central. Deve-se reconsiderar a indicação ou reduzir a dose em pacientes de &lt;strong&gt;idade avançada&lt;/strong&gt;, com &lt;strong&gt;insuficiência hepática ou renal&lt;/strong&gt;, obesos, portadores de insuficiência respiratória ou classificados como ASA III, e naqueles com fatores de risco para obstrução respiratória ou em uso de outros depressores do SNC e álcool. Em todos, a mesma dose produz efeito clínico desproporcional, seja por redução do clearance, seja por perda de reserva funcional.&lt;/p&gt;&lt;p&gt;O paciente em uso crônico de opioides ocupa a posição oposta. A &lt;strong&gt;dependência física&lt;/strong&gt; é propriedade farmacológica do opioide, caracterizada pela ocorrência de &lt;strong&gt;síndrome de abstinência&lt;/strong&gt; à suspensão abrupta ou à administração de antagonista, e não deve ser confundida com adicção. Esse paciente já apresenta &lt;strong&gt;tolerância&lt;/strong&gt;, necessita de doses maiores de analgésico &lt;em&gt;somadas&lt;/em&gt; à sua necessidade basal, e é justamente quem se beneficia de receber medicação depressora no pré-operatório: mantém-se a exigência basal, previne-se a abstinência e trata-se a dor pré-existente.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Paciente dependente de opioides&lt;/strong&gt;: correta. Manter o aporte opioide no pré-operatório previne a síndrome de abstinência e atende a uma necessidade basal já estabelecida pela tolerância.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Extremos de idade&lt;/strong&gt;: incorreta. A idade avançada está nominalmente entre as condições que impõem reconsiderar a indicação ou reduzir a dose.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Baixa reserva fisiológica&lt;/strong&gt;: incorreta. É o cenário clássico de cautela: insuficiência respiratória e classificação ASA III elevada aumentam o risco de depressão ventilatória e instabilidade hemodinâmica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Traumatismo cranioencefálico&lt;/strong&gt;: incorreta. A sedação prejudica a avaliação neurológica seriada e, ao permitir hipoventilação, eleva a PaCO2 com vasodilatação cerebral e aumento da pressão intracraniana.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A intubação retrógrada é alternativa para via aérea difícil não emergencial quando a ventilação por máscara permanece adequada. Não é técnica preferencial no cenário 'não intubo, não oxigeno', em que se indica acesso invasivo de emergência.</t>
+          <t>&lt;p&gt;A &lt;strong&gt;intubação retrógrada&lt;/strong&gt; consiste em guiar o tubo traqueal por um fio flexível introduzido percutaneamente através da &lt;strong&gt;membrana cricotireóidea&lt;/strong&gt;, que percorre a traqueia em sentido retrógrado, atravessa laringe e faringe e emerge pela boca ou pela narina. O guia costuma ser um fio-guia de aço, embora um cateter peridural possa cumprir a mesma função. A técnica pode ser executada em paciente acordado, sedado, obnubilado ou apneico, tanto em via aérea difícil antecipada quanto inesperada.&lt;/p&gt;&lt;p&gt;O ponto que define a questão é o &lt;strong&gt;posicionamento da técnica dentro do algoritmo&lt;/strong&gt;. A intubação retrógrada é descrita como abordagem alternativa à intubação difícil na &lt;strong&gt;via não emergencial&lt;/strong&gt;, isto é, na situação em que a intubação falhou, mas a &lt;strong&gt;ventilação sob máscara permanece adequada&lt;/strong&gt;. Esse é o ramo do algoritmo em que há tempo disponível, e tempo é exatamente o que a técnica exige: sua execução consome vários minutos, o que a torna &lt;strong&gt;contraindicada no cenário de não intubo, não ventilo&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Entre as &lt;strong&gt;indicações&lt;/strong&gt; estão a falha da laringoscopia direta, a obstrução da visão das cordas vocais por sangue, secreções ou distorção anatômica, e cenários como instabilidade da coluna cervical, espondilite anquilosante, trismo e &lt;strong&gt;trauma maxilofacial&lt;/strong&gt;, precisamente o caso apresentado. As contraindicações são em geral relativas: alterações anatômicas que impeçam o acesso à membrana cricotireóidea, estenose traqueal nesse nível, coagulopatia e infecção local.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Abordagem alternativa à intubação difícil na via não emergencial, com intubação malsucedida e ventilação sob máscara adequada&lt;/strong&gt;: correta. Reproduz a posição da técnica no algoritmo de via aérea difícil.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Trauma maxilofacial como contraindicação relativa&lt;/strong&gt;: incorreta. Inverte o sentido: o trauma maxilofacial é uma das indicações nominais da técnica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Técnica de rápida realização, indicada também em não intubo, não ventilo&lt;/strong&gt;: incorreta em ambos os termos. A execução leva vários minutos e por isso mesmo é contraindicada no cenário emergencial.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Posição supina com pescoço em extensão para palpar a cartilagem tireoide&lt;/strong&gt;: incorreta. A posição está certa, mas a estrutura de referência palpada é a &lt;strong&gt;cartilagem cricoide&lt;/strong&gt; e as estruturas circundantes.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>No paciente acordado, o tônus da musculatura faríngea ajuda a manter a patência da via aérea. Com a perda de consciência, há redução desse tônus, favorecendo queda da língua e obstrução.</t>
+          <t>&lt;p&gt;A questão percorre quatro marcos anatômicos da via aérea, e cada distrator troca deliberadamente uma estrutura por outra. É o tipo de item que se resolve por precisão, não por raciocínio.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;musculatura faríngea do paciente acordado contribui ativamente para manter a permeabilidade da via aérea&lt;/strong&gt;. Esse é o conceito de maior consequência clínica de todo o enunciado: a &lt;strong&gt;perda do tônus da musculatura faríngea&lt;/strong&gt; é uma das causas primárias de obstrução de via aérea superior durante a anestesia. É também o que fundamenta manobras corriqueiras: a elevação do mento com fechamento da boca aumenta a tensão longitudinal sobre esses músculos e contrapõe a tendência ao colapso faríngeo.&lt;/p&gt;&lt;p&gt;Quanto aos limites, a &lt;strong&gt;faringe&lt;/strong&gt; é um tubo muscular que vai da base do crânio até o nível da &lt;strong&gt;cartilagem cricoide&lt;/strong&gt;, conectando as cavidades nasal e oral à laringe e ao esôfago; divide-se em nasofaringe, orofaringe e hipofaringe. Na laringe, dentre as cartilagens ímpares e pares, a &lt;strong&gt;tireoide&lt;/strong&gt; é a maior e sustenta a maior parte dos tecidos moles laríngeos; sua incisura superior e a proeminência laríngea são referências para técnicas percutâneas e bloqueios de nervos laríngeos. A &lt;strong&gt;cricoide&lt;/strong&gt;, por sua vez, tem outra particularidade relevante: é o único anel cartilaginoso completo da via aérea. Já na bifurcação traqueal, é o &lt;strong&gt;brônquio principal direito&lt;/strong&gt; que emerge com ângulo mais verticalizado, razão pela qual corpos estranhos e tubos traqueais migram preferencialmente para o lado direito.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Musculatura faríngea do paciente acordado ajuda a manter a desobstrução da via aérea&lt;/strong&gt;: correta. A perda desse tônus sob anestesia é causa primária de obstrução da via aérea superior.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Faringe terminando ao nível da cartilagem tireoide&lt;/strong&gt;: incorreta. O limite inferior é a cartilagem cricoide.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cricoide como maior cartilagem e suporte dos tecidos moles laríngeos&lt;/strong&gt;: incorreta. Essa descrição pertence à cartilagem tireoide.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Brônquio principal esquerdo mais verticalizado&lt;/strong&gt;: incorreta. A verticalização maior é do brônquio direito, o que responde pela maior frequência de intubação seletiva desse lado.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Na posição de cadeira de praia, a pressão medida no braço pode superestimar a pressão ao nível cerebral. A oximetria cerebral pode detectar hipoperfusão regional e auxiliar no ajuste hemodinâmico para preservar a perfusão cerebral.</t>
+          <t>&lt;p&gt;A posição de &lt;strong&gt;cadeira de praia&lt;/strong&gt; cria um problema hemodinâmico específico: entre o ponto onde a pressão arterial é medida e a base do crânio existe uma &lt;strong&gt;coluna hidrostática&lt;/strong&gt;. A cada centímetro de altura, a pressão que efetivamente chega ao encéfalo é menor do que a exibida no monitor, de modo que uma pressão arterial média aparentemente aceitável no braço pode coexistir com &lt;strong&gt;pressão de perfusão cerebral&lt;/strong&gt; insuficiente. Estudos com Doppler transcraniano nessa posição documentam redução da velocidade de fluxo na artéria cerebral média, queda da pressão arterial média, diminuição da pressão de perfusão cerebral e elevação do índice de pulsatilidade.&lt;/p&gt;&lt;p&gt;O paciente descrito acumula dois agravantes. A &lt;strong&gt;hipertensão arterial crônica&lt;/strong&gt; desvia a curva de &lt;strong&gt;autorregulação cerebral&lt;/strong&gt; para a direita, elevando o limite inferior de pressão tolerado: valores que seriam seguros em um normotenso já se situam abaixo do platô de autorregulação. O &lt;strong&gt;diabetes&lt;/strong&gt; soma disfunção vascular. Nesse contexto, a conduta que efetivamente responde à pergunta não é manipular às cegas a pressão arterial, e sim &lt;strong&gt;medir a variável de interesse&lt;/strong&gt;. A &lt;strong&gt;oximetria cerebral&lt;/strong&gt; por espectroscopia de luz próxima ao infravermelho estima a saturação regional de oxigênio no córtex frontal e traduz o &lt;strong&gt;balanço entre oferta e consumo&lt;/strong&gt; de oxigênio; obtém-se um valor basal com o paciente acordado em ar ambiente, e desvios superiores a 20% abaixo desse basal configuram evento de dessaturação significativo.&lt;/p&gt;&lt;p&gt;O corolário prático é que, sob anestesia geral com o paciente sentado, o alvo pressórico deve ser individualizado e corrigido para o nível do encéfalo, com a perfusão sendo verificada e não presumida.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Avaliação da perfusão cerebral pela oximetria cerebral&lt;/strong&gt;: correta. Fornece medida direta do balanço entre oferta e consumo de oxigênio no território mais vulnerável, permitindo detectar dessaturação antes da lesão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipocapnia&lt;/strong&gt;: incorreta. A redução da PaCO2 causa vasoconstrição cerebral e diminui o fluxo, somando-se à queda de perfusão já imposta pela posição.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Uso precoce de fenilefrina&lt;/strong&gt;: incorreta. Corrige o número exibido no monitor sem assegurar oxigenação encefálica, e a elevação da pós-carga não garante melhora do fluxo cerebral.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumentar para 30 cm a distância entre o manguito e o polígono de Willis&lt;/strong&gt;: incorreta, e no sentido inverso do desejado. Quanto maior essa distância, maior o gradiente hidrostático e maior a superestimativa da pressão que chega ao encéfalo; o ajuste correto é referenciar a medida ao nível do meato acústico externo.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A mancha macular vermelho-cereja, associada a defeito pupilar aferente e nervo óptico inicialmente normal, é típica de oclusão da artéria central da retina. Essa entidade difere da neuropatia óptica isquêmica, em que o achado fundoscópico é distinto.</t>
+          <t>&lt;p&gt;A perda visual perioperatória tem duas causas dominantes: a &lt;strong&gt;neuropatia óptica isquêmica&lt;/strong&gt; e a &lt;strong&gt;oclusão arterial retiniana&lt;/strong&gt;. Distingui-las é um exercício de fundoscopia e de lateralidade, e o caso descrito oferece os dois elementos decisivos.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;oclusão da artéria central da retina&lt;/strong&gt; resulta tipicamente de &lt;strong&gt;compressão externa do globo ocular&lt;/strong&gt; por posicionamento inadequado, que eleva a pressão intraocular a ponto de interromper o fluxo na artéria central, cenário que ocorre com maior frequência justamente em &lt;strong&gt;cirurgia de coluna em decúbito ventral&lt;/strong&gt;, como no caso. O quadro é de perda visual indolor, &lt;strong&gt;reatividade pupilar anormal&lt;/strong&gt;, opacificação esbranquiçada da retina isquêmica e afilamento das arteríolas. O sinal clássico é a &lt;strong&gt;mancha macular vermelho-cereja&lt;/strong&gt; sobre retina de aspecto vidro-fosco: a palidez da retina interna isquêmica deixa transparecer a coloração vermelha da circulação coroidea íntegra subjacente, que na fóvea não é encoberta por células retinianas internas. Por depender de um mecanismo compressivo focal, a apresentação é caracteristicamente &lt;strong&gt;unilateral&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A neuropatia óptica isquêmica segue outra lógica. Na forma &lt;strong&gt;anterior&lt;/strong&gt; há edema de disco óptico e hemorragias já no início dos sintomas; na forma &lt;strong&gt;posterior&lt;/strong&gt;, o disco aparece normal apesar da perda visual referida. Ambas relacionam-se a fatores sistêmicos (anemia, hipotensão, tempo prolongado em pronação, grande volume de cristaloide) e, após cirurgia de coluna, a maioria dos casos é &lt;strong&gt;bilateral&lt;/strong&gt;. A prevenção da oclusão arterial é mecânica: apoios de cabeça com recorte para os olhos e verificação periódica de que não há contato sobre o globo.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Oclusão da artéria central da retina&lt;/strong&gt;: correta. Reúne perda unilateral, alteração pupilar e a mancha macular vermelho-cereja, no contexto clássico de pronação prolongada para artrodese lombar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Isquemia anterior do nervo óptico&lt;/strong&gt;: incorreta. Cursaria com edema e hemorragias de disco óptico, sem achado macular vermelho-cereja, e tipicamente de forma bilateral após cirurgia de coluna.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Isquemia posterior do nervo óptico&lt;/strong&gt;: incorreta. O disco óptico permanece normal ao exame inicial e não há a alteração macular descrita.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Acidente vascular encefálico isquêmico&lt;/strong&gt;: incorreta. Produziria déficit de campo com fundoscopia normal e reflexo fotomotor preservado, o que contraria os achados oftalmológicos apresentados.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Analisadores sidestream aspiram pequena amostra de gás para uma câmara remota e permitem medir simultaneamente CO2, N2O e agentes halogenados. A linha de amostragem, porém, pode sofrer atraso e obstrução por secreções ou condensado.</t>
+          <t>&lt;p&gt;A análise de gases anestésicos apoia-se na &lt;strong&gt;absorção de luz infravermelha&lt;/strong&gt;: cada gás absorve em uma faixa característica (o CO&lt;sub&gt;2&lt;/sub&gt;, por exemplo, em banda estreita centrada em 4,26 μm), e a queda de intensidade detectada é proporcional à concentração. O que diferencia os sistemas é &lt;em&gt;onde&lt;/em&gt; a amostra é analisada.&lt;/p&gt;&lt;p&gt;No sistema &lt;strong&gt;mainstream&lt;/strong&gt;, a célula de medida fica diretamente no circuito, e os gases inspirados e expirados atravessam o feixe infravermelho no próprio trajeto. Daí sua principal virtude: &lt;strong&gt;não há tempo de retardo&lt;/strong&gt; e o tempo de subida da curva é mais rápido. Em contrapartida, acrescenta peso e potencial espaço morto junto à via aérea, e a célula precisa ser &lt;strong&gt;aquecida a cerca de 40 °C&lt;/strong&gt; exatamente para impedir a condensação de vapor d'água sobre a janela óptica, aquecimento que, pela proximidade com a face, traz risco de queimadura.&lt;/p&gt;&lt;p&gt;No sistema &lt;strong&gt;sidestream&lt;/strong&gt;, uma alíquota é aspirada por um tubo fino a partir de um conector junto ao dispositivo de via aérea e conduzida até a câmara de análise no interior do monitor, a taxas da ordem de 30 a 500 mL/min. Isso impõe um &lt;strong&gt;retardo&lt;/strong&gt; proporcional ao trajeto e à velocidade de aspiração, e a desvantagem prática mais conhecida é a &lt;strong&gt;obstrução do tubo coletor&lt;/strong&gt; por umidade condensada e secreções. A vantagem que consagrou a técnica é outra: como a amostra chega a um console, é possível acoplar vários analisadores em série e obter a &lt;strong&gt;análise simultânea de diversos gases&lt;/strong&gt; (CO&lt;sub&gt;2&lt;/sub&gt;, O&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt;O e halogenados) com um único conector leve no circuito.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sistemas sidestream possibilitam a análise de diversos gases simultaneamente&lt;/strong&gt;: correta. É precisamente o motivo do crescimento dessa modalidade nos monitores modernos.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Monitor resfriado para estabilizar a câmara de medição&lt;/strong&gt;: incorreta, e no sentido inverso. A célula é aquecida, não resfriada, para evitar condensação.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Coleta diferente para halogenados e óxido nitroso&lt;/strong&gt;: incorreta. A amostragem é a mesma; o que muda é a faixa de absorção infravermelha usada para quantificar cada gás.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Mainstream com medição lenta e obstrução por umidade&lt;/strong&gt;: incorreta. Essas são características do sidestream; o mainstream é o sistema sem retardo e de resposta mais rápida.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A oximetria convencional utiliza dois comprimentos de onda e não diferencia adequadamente carboxi-hemoglobina de oxi-hemoglobina. Por isso, na intoxicação por monóxido de carbono, a SpO2 pode parecer falsamente normal.</t>
+          <t>&lt;p&gt;A oximetria de pulso convencional repousa sobre a &lt;strong&gt;lei de Beer-Lambert&lt;/strong&gt; e sobre uma premissa simplificadora: a de que as únicas espécies capazes de absorver luz nos &lt;strong&gt;dois comprimentos de onda&lt;/strong&gt; empregados (&lt;strong&gt;660 nm&lt;/strong&gt;, no vermelho, e &lt;strong&gt;940 nm&lt;/strong&gt;, no infravermelho) são a oxiemoglobina e a desoxiemoglobina. A razão entre as absorções pulsáteis nesses dois comprimentos gera o valor R, que é convertido em SpO&lt;sub&gt;2&lt;/sub&gt; por uma curva de calibração empírica. Toda limitação do método decorre de alguma violação dessa premissa; daí também a imprecisão quando a &lt;strong&gt;pulsatilidade&lt;/strong&gt; está reduzida ou ausente.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;carboxiemoglobina&lt;/strong&gt; é o exemplo mais didático. Sua absorção em 660 nm é &lt;strong&gt;semelhante à da oxiemoglobina&lt;/strong&gt;, ao passo que em 940 nm ela praticamente não absorve luz. O aparelho, incapaz de distinguir as duas espécies, contabiliza a carboxiemoglobina como se fosse hemoglobina oxigenada: na intoxicação por monóxido de carbono a &lt;strong&gt;SpO&lt;sub&gt;2&lt;/sub&gt; é falsamente elevada&lt;/strong&gt;, podendo exibir valores tranquilizadores diante de hipóxia tecidual grave. Só a co-oximetria de múltiplos comprimentos de onda resolve a ambiguidade.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;metemoglobina&lt;/strong&gt; comporta-se de modo distinto: absorve intensamente em &lt;strong&gt;ambos&lt;/strong&gt; os comprimentos de onda, empurrando o valor R para próximo de 1. Como R igual a 1 corresponde, na calibração, a concentrações iguais de oxi e desoxiemoglobina, a leitura tende a se &lt;strong&gt;fixar entre 80% e 85%&lt;/strong&gt;, e permanece ali &lt;em&gt;independentemente&lt;/em&gt; da saturação arterial real e da PaO&lt;sub&gt;2&lt;/sub&gt;: a SpO&lt;sub&gt;2&lt;/sub&gt; deixa de acompanhar a oxigenação em qualquer direção.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Incapaz de diferenciar carboxiemoglobina de oxiemoglobina&lt;/strong&gt;: correta. A absorção quase idêntica em 660 nm torna as duas espécies indistinguíveis para o aparelho, com superestimativa da saturação.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aplicação da lei de Bernoulli&lt;/strong&gt;: incorreta. O princípio aplicável é a lei de Beer-Lambert, de absorção de luz.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Emissão de um único comprimento de onda de luz vermelha&lt;/strong&gt;: incorreta. São dois comprimentos de onda, 660 nm e 940 nm, e é justamente a razão entre eles que permite o cálculo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;SpO&lt;sub&gt;2&lt;/sub&gt; tanto menor quanto maior a PaO&lt;sub&gt;2&lt;/sub&gt; na metemoglobinemia&lt;/strong&gt;: incorreta. A leitura estaciona em torno de 80% a 85% de forma independente da PaO&lt;sub&gt;2&lt;/sub&gt;, sem a relação inversa descrita.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Quando a curva de capnografia não retorna à linha de base durante a inspiração, há reinalação de CO2. Uma causa frequente é fluxo de gases frescos insuficiente ou falha do sistema de absorção/valvas.</t>
+          <t>&lt;p&gt;A leitura do capnograma começa por uma pergunta simples: &lt;strong&gt;a curva retorna a zero durante a inspiração?&lt;/strong&gt; Em condições normais, o gás inspirado é isento de CO&lt;sub&gt;2&lt;/sub&gt; e o traçado desce até a linha de base. Quando a linha de base permanece &lt;strong&gt;consistentemente acima de zero&lt;/strong&gt;, existe apenas uma explicação fisiológica: o paciente está &lt;strong&gt;reinalando CO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt;. Trata-se, portanto, de um problema do sistema ventilatório, e não do pulmão do paciente.&lt;/p&gt;&lt;p&gt;As causas se agrupam por mecanismo. Há falha de componente do circuito: &lt;strong&gt;válvula expiratória defeituosa&lt;/strong&gt;, que permite o retorno de gás expirado ao ramo inspiratório, ou &lt;strong&gt;absorvedor de cal sodada exaurido&lt;/strong&gt;, incapaz de sequestrar o CO&lt;sub&gt;2&lt;/sub&gt; que retorna. E há falha de lavagem: sistemas cuja depuração de CO&lt;sub&gt;2&lt;/sub&gt; depende do &lt;strong&gt;fluxo de gases frescos&lt;/strong&gt; exigem fluxo suficiente para expulsar o gás expirado antes da próxima inspiração; quando esse fluxo é insuficiente, parte do gás alveolar é reinalada e a linha de base se eleva. Entre as opções apresentadas, essa é a única que produz reinalação.&lt;/p&gt;&lt;p&gt;Vale contrastar com o que a &lt;strong&gt;videolaparoscopia&lt;/strong&gt; de fato provoca. A insuflação de CO&lt;sub&gt;2&lt;/sub&gt; no peritônio aumenta a carga absorvida e eleva a &lt;strong&gt;EtCO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt; (isto é, desloca o topo da curva para cima), mas a fase inspiratória continua zerando normalmente. Elevação do platô e elevação da linha de base são achados distintos, com significados distintos.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Baixo fluxo de gases frescos&lt;/strong&gt;: correta. É o único mecanismo listado capaz de gerar reinalação de CO&lt;sub&gt;2&lt;/sub&gt; e, com ela, uma fase inspiratória que não retorna a zero.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipoperfusão pulmonar&lt;/strong&gt;: incorreta. Reduz a entrega de CO&lt;sub&gt;2&lt;/sub&gt; ao alvéolo e diminui a EtCO&lt;sub&gt;2&lt;/sub&gt;, alargando o gradiente com a PaCO&lt;sub&gt;2&lt;/sub&gt;, sem afetar a linha de base.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Insuflação do pneumoperitônio&lt;/strong&gt;: incorreta. Eleva a EtCO&lt;sub&gt;2&lt;/sub&gt; por absorção peritoneal de CO&lt;sub&gt;2&lt;/sub&gt;, mas o traçado segue retornando a zero na inspiração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Posicionamento incorreto do tubo endotraqueal&lt;/strong&gt;: incorreta. A intubação seletiva ou esofágica altera amplitude e morfologia da curva, não o nível da linha de base inspiratória.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Na maioria das terminações pós-ganglionares simpáticas, o neurotransmissor é a norepinefrina. Exceções importantes incluem as glândulas sudoríparas, que utilizam acetilcolina.</t>
+          <t>&lt;p&gt;A organização química do sistema nervoso autônomo é mais simples do que a memorização por listas sugere, desde que se fixem dois eixos: &lt;strong&gt;onde&lt;/strong&gt; está a sinapse e &lt;strong&gt;qual&lt;/strong&gt; transmissor ela usa.&lt;/p&gt;&lt;p&gt;Todas as fibras &lt;strong&gt;pré-ganglionares&lt;/strong&gt;, tanto simpáticas quanto parassimpáticas, são &lt;strong&gt;colinérgicas&lt;/strong&gt;: liberam &lt;strong&gt;acetilcolina&lt;/strong&gt; sobre receptores nicotínicos ganglionares. A divergência aparece depois do gânglio. No parassimpático, praticamente todos os neurônios &lt;strong&gt;pós-ganglionares&lt;/strong&gt; permanecem colinérgicos. No simpático, a maioria dos neurônios pós-ganglionares é &lt;strong&gt;adrenérgica&lt;/strong&gt;, secretando &lt;strong&gt;noradrenalina&lt;/strong&gt;. Por isso a acetilcolina é chamada de transmissor parassimpático e a noradrenalina, de transmissor simpático.&lt;/p&gt;&lt;p&gt;Duas exceções merecem registro por seu peso clínico. As fibras simpáticas pós-ganglionares destinadas às &lt;strong&gt;glândulas sudoríparas&lt;/strong&gt; (e possivelmente a alguns poucos vasos) são colinérgicas, o que explica por que a sudorese de origem simpática responde a antagonistas muscarínicos. E a &lt;strong&gt;medula adrenal&lt;/strong&gt; comporta-se como um gânglio simpático modificado, inervada por fibras pré-ganglionares colinérgicas, convertendo cerca de 80% da noradrenalina em &lt;strong&gt;adrenalina&lt;/strong&gt; antes de lançá-la na circulação. A ação da noradrenalina liberada termina sobretudo por &lt;strong&gt;recaptação&lt;/strong&gt; nas terminações adrenérgicas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Norepinefrina&lt;/strong&gt;: correta. É o transmissor da maioria das fibras simpáticas pós-ganglionares e, por isso, o transmissor simpático por definição.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Acetilcolina&lt;/strong&gt;: incorreta neste contexto. Domina a transmissão pré-ganglionar de ambas as divisões e a pós-ganglionar parassimpática, restando no simpático pós-ganglionar apenas as fibras sudomotoras.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dopamina&lt;/strong&gt;: incorreta. É precursora na síntese da noradrenalina e tem papel de neurotransmissor em outros territórios, mas não é o mediador pós-ganglionar simpático predominante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Serotonina&lt;/strong&gt;: incorreta. Não integra a transmissão pós-ganglionar do sistema nervoso autônomo descrita.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Com doses crescentes de barbitúricos, a atividade eletroencefalográfica e o metabolismo cerebral diminuem até um limite aproximado de 60% do basal. Após EEG isoelétrico, aumentos adicionais da dose não reduzem substancialmente o consumo energético necessário à homeostase celular.</t>
+          <t>&lt;p&gt;O consumo cerebral de oxigênio não é uma grandeza única: divide-se em &lt;strong&gt;dois componentes funcionalmente independentes&lt;/strong&gt;. O primeiro sustenta a &lt;strong&gt;atividade eletrofisiológica neuronal&lt;/strong&gt; (geração de potenciais de ação e tráfego sináptico), e responde pela maior fração do consumo no cérebro desperto. O segundo mantém a &lt;strong&gt;integridade celular&lt;/strong&gt;: bombas iônicas, gradientes de membrana, síntese proteica, tudo aquilo de que a célula depende para permanecer viva, independentemente de estar processando informação.&lt;/p&gt;&lt;p&gt;Essa partição é a chave de toda a curva. Os &lt;strong&gt;anestésicos deprimem apenas o componente funcional&lt;/strong&gt;. À medida que a dose aumenta, o EEG passa de ritmos rápidos a ondas lentas, depois a &lt;strong&gt;surto-supressão&lt;/strong&gt; e finalmente a traçado &lt;strong&gt;isoelétrico&lt;/strong&gt;, com queda progressiva do consumo. Com a indução, fluxo e consumo caem cerca de 30%; alcançada a supressão eletroencefalográfica completa, a redução chega a aproximadamente 50%. E então a curva atinge um &lt;strong&gt;platô&lt;/strong&gt;: &lt;strong&gt;doses adicionais não produzem qualquer redução extra do metabolismo&lt;/strong&gt;, porque o que resta é exatamente a energia destinada à homeostase celular, sobre a qual o anestésico não age. É também por isso que aprofundar o plano além do EEG isoelétrico não confere proteção cerebral adicional, apenas efeitos hemodinâmicos indesejados.&lt;/p&gt;&lt;p&gt;O contraste com a &lt;strong&gt;hipotermia&lt;/strong&gt; ilumina o conceito: ela reduz &lt;strong&gt;ambos&lt;/strong&gt; os componentes, funcional e de integridade, e por isso continua diminuindo o consumo mesmo depois de o EEG já estar isoelétrico. Essa é a razão fisiológica pela qual a hipotermia protege em cenários de parada circulatória de um modo que o anestésico não reproduz.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Utilização energética para homeostase celular permanece inalterada no ponto de platô&lt;/strong&gt;: correta. Os anestésicos suprimem apenas o componente funcional; a fração destinada à manutenção da integridade celular é preservada e define o piso da curva.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Plano anestésico ideal no ponto inicial da curva&lt;/strong&gt;: incorreta. Nessa região a atividade eletrofisiológica ainda é ampla, sem correspondência com o alvo clínico proposto.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;EEG isoelétrico no ponto intermediário&lt;/strong&gt;: incorreta. A isoeletricidade coincide com o início do platô metabólico, e não com a porção descendente da curva.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofrimento cerebral com surto-supressão precoce&lt;/strong&gt;: incorreta. O surto-supressão farmacologicamente induzido é etapa esperada da depressão dose-dependente do EEG, e não marcador de isquemia.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Anti-inflamatórios não esteroidais podem reduzir o efeito de anti-hipertensivos, inclusive betabloqueadores, por retenção de sódio e interferência na síntese de prostaglandinas renais. Isso pode contribuir para controle pressórico inadequado.</t>
+          <t>&lt;p&gt;O caso reúne três classes farmacológicas em um paciente que chega à sala com &lt;strong&gt;170 × 100 mmHg&lt;/strong&gt;, e a questão cobra qual delas explica o descontrole pressórico.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;anti-inflamatórios não esteroidais&lt;/strong&gt; inibem a ciclo-oxigenase e, com ela, a síntese de &lt;strong&gt;prostaglandinas vasodilatadoras&lt;/strong&gt; renais. O resultado é retenção de sódio e água, expansão do volume intravascular e perda de um mecanismo que contrabalança a vasoconstrição, combinação que &lt;strong&gt;atenua o efeito de praticamente todas as classes anti-hipertensivas&lt;/strong&gt;. É uma interferência documentada de forma explícita para bloqueadores alfa-adrenérgicos e que se estende, pelo mesmo mecanismo, ao betabloqueio. Uma semana de uso contínuo, como no caso, é tempo mais que suficiente para o fenômeno se instalar, e é o dado clínico que o enunciado planta deliberadamente.&lt;/p&gt;&lt;p&gt;Quanto ao &lt;strong&gt;labetalol&lt;/strong&gt;, ele é de fato uma escolha adequada para hipertensão pré e perioperatória, mas sua caracterização farmacológica não é a de bloqueador β1 seletivo: trata-se de um &lt;strong&gt;bloqueador combinado α/β&lt;/strong&gt;, da mesma família do carvedilol. Essa combinação é justamente o que lhe confere redução de pós-carga sem taquicardia reflexa. Já a interrupção abrupta de betabloqueadores no perioperatório é reconhecida como fator de risco, inclusive para fibrilação atrial pós-operatória, razão pela qual a orientação é &lt;strong&gt;manter&lt;/strong&gt; a medicação.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Efeito anti-hipertensivo dos betabloqueadores atenuado pelos AINEs&lt;/strong&gt;: correta. A inibição das prostaglandinas vasodilatadoras renais promove retenção hidrossalina e reduz a eficácia do anti-hipertensivo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Insulina regular dificultando o controle pressórico&lt;/strong&gt;: incorreta. Não há relação estabelecida entre a insulinoterapia e piora do controle pressórico pré-operatório.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Labetalol como bloqueador seletivo β1&lt;/strong&gt;: incorreta na farmacologia. O fármaco é adequado ao caso, mas é um bloqueador combinado α/β, e não β1 seletivo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipotensão importante pós-indução por betabloqueio&lt;/strong&gt;: incorreta. A recomendação é manter o betabloqueador no perioperatório; a hipotensão pós-indução associa-se de modo mais consistente aos bloqueadores do sistema renina-angiotensina.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Em fibrilação atrial com estabilidade hemodinâmica, o controle da frequência ventricular pode ser feito com bloqueadores dos canais de cálcio não di-hidropiridínicos, como verapamil, que reduzem a condução pelo nó AV.</t>
+          <t>&lt;p&gt;Diante de &lt;strong&gt;fibrilação atrial crônica&lt;/strong&gt; em paciente idoso, estável, com sinais vitais normais e queixa de palpitações, o objetivo terapêutico é o &lt;strong&gt;controle da frequência ventricular&lt;/strong&gt;, e não a restauração do ritmo sinusal. Essa definição de objetivo resolve a questão inteira.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;verapamil&lt;/strong&gt; é um bloqueador dos &lt;strong&gt;canais lentos de cálcio&lt;/strong&gt; cujo sítio primário de ação é o &lt;strong&gt;nó atrioventricular&lt;/strong&gt;, tecido cuja despolarização depende justamente da corrente lenta de cálcio. Ao inibir o influxo normal de cálcio nessas células, prolonga o tempo de condução e o período refratário nodal, reduzindo o número de impulsos atriais caóticos que alcançam o ventrículo, exatamente o efeito desejado no controle de frequência das &lt;strong&gt;taquiarritmias supraventriculares&lt;/strong&gt;. Duas cautelas acompanham o fármaco: os efeitos inotrópico e cronotrópico negativos são &lt;strong&gt;potencializados pelo uso concomitante de betabloqueadores&lt;/strong&gt;, e ele pode precipitar arritmias ventriculares na síndrome de Wolff-Parkinson-White.&lt;/p&gt;&lt;p&gt;Sobre a estratégia de reversão, a fibrilação atrial &lt;strong&gt;crônica&lt;/strong&gt; impõe considerar o trombo atrial já potencialmente formado: restaurar a contração atrial (por choque ou por fármaco) sem preparo antitrombótico adequado expõe o paciente à embolização sistêmica. Um paciente estável não oferece justificativa para correr esse risco de imediato.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Verapamil para controle da frequência, por ação nos canais lentos de cálcio&lt;/strong&gt;: correta. Descreve com precisão o mecanismo e o alvo terapêutico apropriado ao cenário.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Reversão imediata, elétrica ou química&lt;/strong&gt;: incorreta. O paciente está estável, e a reversão em fibrilação atrial crônica sem preparo antitrombótico carrega risco de embolização.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Lidocaína atuando na fase 4 das fibras de Purkinje&lt;/strong&gt;: incorreta. Antiarrítmico de classe IB, atua sobre tecido ventricular e sistema His-Purkinje, sendo ineficaz em arritmia de origem atrial.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Amiodarona como droga de escolha&lt;/strong&gt;: incorreta. A descrição do mecanismo está correta, mas a indicação não: promoveria reversão química, com o mesmo risco embólico que se deseja evitar neste momento.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A curva D apresenta baixo volume para grande variação de pressão, padrão compatível com complacência pulmonar reduzida. Isso é observado em condições como edema pulmonar, fibrose e síndrome do desconforto respiratório.</t>
+          <t>&lt;p&gt;A curva &lt;strong&gt;pressão-volume&lt;/strong&gt; é a representação gráfica da complacência do sistema respiratório, definida como a variação de volume obtida por unidade de variação de pressão (&lt;strong&gt;C = ΔV/ΔP&lt;/strong&gt;). Em termos gráficos, a complacência é a &lt;strong&gt;inclinação da curva&lt;/strong&gt;: quanto mais inclinada, maior o volume ganho por cada centímetro de água aplicado, e portanto maior a complacência.&lt;/p&gt;&lt;p&gt;Daí decorre toda a leitura clínica. Uma curva &lt;strong&gt;deslocada para a direita e achatada&lt;/strong&gt;, com menor inclinação, indica &lt;strong&gt;redução da complacência&lt;/strong&gt;: é preciso mais pressão para mobilizar o mesmo volume. Esse é o padrão de pulmões enrijecidos (edema pulmonar, síndrome do desconforto respiratório agudo, fibrose, atelectasia extensa) e também de condições que restringem a caixa torácica, como obesidade, pneumoperitônio e decúbito ventral mal acomodado. Uma curva &lt;strong&gt;mais inclinada e deslocada para cima e à esquerda&lt;/strong&gt; indica o oposto: complacência aumentada, situação do &lt;strong&gt;enfisema&lt;/strong&gt; e do pulmão senil, nos quais a destruição ou o desgaste das fibras elásticas reduz a retração elástica e o pulmão se enche com facilidade, ao custo de dificuldade para esvaziar.&lt;/p&gt;&lt;p&gt;Convém não confundir dois conceitos que a curva separa nitidamente. A &lt;strong&gt;complacência&lt;/strong&gt; é propriedade estática, avaliada em condições de fluxo zero, e informa sobre o parênquima e a parede torácica. A &lt;strong&gt;resistência&lt;/strong&gt; é propriedade dinâmica, dependente de fluxo, e informa sobre o calibre das vias aéreas, não sendo, portanto, extraída da curva pressão-volume estática. Vale ainda lembrar que a complacência do sistema respiratório do adulto situa-se tipicamente em torno de 50 a 100 mL/cmH&lt;sub&gt;2&lt;/sub&gt;O, de modo que valores de ordem muito superior a essa faixa não têm correspondência fisiológica.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Curva que identifica redução da complacência pulmonar&lt;/strong&gt;: correta. Corresponde ao traçado de menor inclinação, no qual maior pressão é necessária para o mesmo ganho de volume.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Curva atribuída à complacência do paciente idoso&lt;/strong&gt;: incorreta. O pulmão senil perde retração elástica e exibe complacência aumentada, com curva mais inclinada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumento da complacência acima de 0,6 L/cmH&lt;sub&gt;2&lt;/sub&gt;O&lt;/strong&gt;: incorreta. Esse valor extrapola em muito a faixa fisiológica do sistema respiratório adulto.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Queda simultânea da resistência das vias aéreas e da complacência&lt;/strong&gt;: incorreta. A resistência é grandeza dinâmica, dependente de fluxo, e não é avaliada na curva pressão-volume estática.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>O espaço morto fisiológico aumenta quando há regiões ventiladas com pouca ou nenhuma perfusão. Assim, ventilação excessiva em relação à perfusão, como pode ocorrer na embolia pulmonar, eleva o espaço morto fisiológico.</t>
+          <t>&lt;p&gt;O &lt;strong&gt;espaço morto&lt;/strong&gt; é a fração da ventilação que não participa da troca gasosa, e todo o tema se organiza a partir de uma divisão hierárquica precisa. O &lt;strong&gt;espaço morto fisiológico&lt;/strong&gt; subdivide-se em &lt;strong&gt;espaço morto de vias aéreas&lt;/strong&gt; (também chamado &lt;strong&gt;anatômico&lt;/strong&gt;) e &lt;strong&gt;espaço morto alveolar&lt;/strong&gt;. Há ainda o espaço morto de aparelho, que só existe quando o paciente está conectado a um circuito ventilatório.&lt;/p&gt;&lt;p&gt;O componente &lt;strong&gt;anatômico&lt;/strong&gt; é a porção da respiração que ocupa boca, faringe e árvore traqueobrônquica sem alcançar os alvéolos. É determinado pelo &lt;strong&gt;volume das vias condutoras&lt;/strong&gt;, e por isso só se altera quando esse volume muda, daí a importância de reconhecer que &lt;strong&gt;bronquiectasias&lt;/strong&gt;, ao dilatarem brônquios, o aumentam.&lt;/p&gt;&lt;p&gt;O componente &lt;strong&gt;alveolar&lt;/strong&gt; obedece a outra lógica: é a porção da respiração que &lt;em&gt;chega&lt;/em&gt; aos alvéolos, mas encontra unidades &lt;strong&gt;ventiladas e não perfundidas&lt;/strong&gt;, a &lt;strong&gt;zona 1 de West&lt;/strong&gt;. Aqui entra o conceito central da questão: sempre que a &lt;strong&gt;ventilação alveolar se torna excessiva em relação à perfusão&lt;/strong&gt;, cria-se ventilação desperdiçada e o espaço morto fisiológico aumenta. É o que ocorre na &lt;strong&gt;embolia pulmonar&lt;/strong&gt;, na hipovolemia, no baixo débito cardíaco e na PEEP excessiva, todos mecanismos que reduzem ou redistribuem o fluxo capilar diante de alvéolos que continuam sendo ventilados. Clinicamente, isso se traduz no alargamento do gradiente entre a PaCO&lt;sub&gt;2&lt;/sub&gt; e a EtCO&lt;sub&gt;2&lt;/sub&gt;.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ventilação alveolar excessiva em relação à perfusão aumenta o espaço morto fisiológico&lt;/strong&gt;: correta. É a própria definição do componente alveolar do espaço morto: unidades ventiladas e não perfundidas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Embolia pulmonar aumentando o espaço morto anatômico&lt;/strong&gt;: incorreta. A embolia aumenta o componente alveolar; o anatômico depende do volume das vias condutoras e não se altera.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bronquiectasias reduzindo o espaço morto anatômico e fisiológico&lt;/strong&gt;: incorreta e no sentido inverso, pois a dilatação das vias condutoras aumenta o espaço morto anatômico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Espaço morto fisiológico como fração que permanece nas vias condutoras&lt;/strong&gt;: incorreta. Essa é a definição do anatômico; o fisiológico é a soma do anatômico com o alveolar.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Na fase II do metabolismo, o fármaco ou seu metabólito sofre conjugação, formando composto mais hidrossolúvel e geralmente mais fácil de excretar. Exemplos incluem glicuronidação, sulfatação e acetilação.</t>
+          <t>&lt;p&gt;Três princípios estruturam a farmacocinética básica cobrada aqui: para onde o fármaco vai, como ele é transformado e como sai.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;distribuição&lt;/strong&gt; inicial, no primeiro minuto após o bolus, ocorre no &lt;strong&gt;compartimento central&lt;/strong&gt;: sangue venoso do braço, grandes vasos, coração, pulmão e aorta proximal. Esses volumes são praticamente fixos, com uma exceção importante: o &lt;strong&gt;pulmão&lt;/strong&gt;. Fármacos muito lipossolúveis sofrem &lt;strong&gt;captação ávida na primeira passagem pulmonar&lt;/strong&gt;, o que reduz a concentração medida no sangue arterial. Como o volume é calculado dividindo a dose pela concentração medida, uma concentração menor implica um volume aparentemente &lt;strong&gt;maior&lt;/strong&gt;; daí o aumento aparente do compartimento central. Lidocaína, propranolol, meperidina, fentanil, sufentanil e alfentanil exibem captação pulmonar de primeira passagem expressiva.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;metabolismo&lt;/strong&gt; tem um sentido bem definido: converter fármacos &lt;strong&gt;lipossolúveis e ativos&lt;/strong&gt; em metabólitos &lt;strong&gt;hidrossolúveis&lt;/strong&gt;, em geral inativos, aptos à excreção renal (com exceções conhecidas, como diazepam, propranolol e morfina, que geram compostos ativos). As reações de &lt;strong&gt;fase I&lt;/strong&gt; (oxidação, redução, hidrólise, majoritariamente via citocromo P450) introduzem ou expõem um grupo funcional. As de &lt;strong&gt;fase II&lt;/strong&gt; promovem &lt;strong&gt;conjugação&lt;/strong&gt; desse fármaco ou de seu metabólito com uma molécula endógena (glicuronidação, sulfatação, acetilação, conjugação com glutationa), aumentando decisivamente a &lt;strong&gt;hidrossolubilidade&lt;/strong&gt; e viabilizando a excreção. A imaturidade da capacidade de conjugação no neonato explica a maior toxicidade de fármacos que dependem da glicuronidação.&lt;/p&gt;&lt;p&gt;Por fim, a &lt;strong&gt;depuração hepática&lt;/strong&gt; parte de um balanço de massa simples: o que sai do fígado equivale ao que entra menos o que foi metabolizado, sendo a taxa de metabolismo o produto do fluxo sanguíneo hepático pela diferença de concentração entre entrada e saída.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Na fase II ocorre conjugação, tornando o fármaco mais hidrossolúvel para excreção&lt;/strong&gt;: correta. É a definição da segunda fase do metabolismo e a etapa que viabiliza a eliminação renal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Alta lipossolubilidade causando diminuição aparente do compartimento central&lt;/strong&gt;: incorreta. A captação pulmonar de primeira passagem reduz a concentração arterial e aumenta o volume aparente.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Conversão de fármacos hidrossolúveis ativos em metabólitos lipossolúveis inativos&lt;/strong&gt;: incorreta. A direção é a oposta: de lipossolúvel ativo para hidrossolúvel inativo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Igualdade entre o que entra no fígado e o que sai somado ao que é metabolizado&lt;/strong&gt;: enunciada como incorreta pela banca; do ponto de vista do balanço de massa, porém, a formulação é equivalente à consagrada. Guarde o conceito: a diferença entre entrada e saída, multiplicada pelo fluxo hepático, é a taxa de metabolismo.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>O gabarito oficial indica a alternativa D. Midazolam e propofol apresentam interação sinérgica, reduzindo a necessidade de propofol e podendo prolongar a recuperação; a afirmação sobre aumento da concentração plasmática deve ser interpretada no contexto do modelo farmacocinético/farmacodinâmico e merece revisão editorial.</t>
+          <t>&lt;p&gt;O caso descreve um despertar mais lento que o esperado após uma cirurgia de apenas uma hora, e a resposta está numa &lt;strong&gt;interação farmacocinética&lt;/strong&gt; frequentemente subestimada, agravada pelo fato de o paciente ter &lt;strong&gt;78 anos e 60 kg&lt;/strong&gt; e ter recebido &lt;strong&gt;7 mg de midazolam&lt;/strong&gt;, dose alta para esse perfil.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;midazolam altera a farmacocinética do propofol&lt;/strong&gt; de maneira quantificada: na presença de concentração sedativa de midazolam da ordem de 200 ng/mL, as concentrações sanguíneas de propofol tornam-se cerca de &lt;strong&gt;25% mais elevadas&lt;/strong&gt;. O mecanismo é a redução das depurações: a metabólica cai de 1,94 para 1,61 L/min, e as depurações intercompartimentais também diminuem. Há ainda inibição competitiva do &lt;strong&gt;CYP3A4&lt;/strong&gt;, que se instala de forma praticamente instantânea quando os dois fármacos disputam o sítio ativo da enzima. O fenômeno é recíproco: na presença de propofol, as concentrações plasmáticas de midazolam sobem cerca de 27%.&lt;/p&gt;&lt;p&gt;A consequência prática é decisiva em anestesia alvo-controlada. O sistema calcula a concentração-alvo a partir de um modelo populacional que &lt;strong&gt;desconhece&lt;/strong&gt; a presença do midazolam; a concentração real de propofol excede a estimada, e a esse excesso soma-se a &lt;strong&gt;sinergia farmacodinâmica&lt;/strong&gt; entre hipnóticos e benzodiazepínicos. O índice bispectral pode permanecer na faixa desejada durante o procedimento e ainda assim o despertar se prolongar, porque o fármaco efetivamente presente é maior do que o previsto.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Aumento da concentração plasmática do propofol pela administração do midazolam&lt;/strong&gt;: correta. A redução das depurações metabólica e intercompartimentais eleva em cerca de 25% a concentração de propofol, prolongando o despertar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Duração da infusão contínua do remifentanil&lt;/strong&gt;: incorreta. Sua meia-vida contexto-dependente permanece em torno de 3 a 4 minutos graças à hidrólise por esterases, sem acúmulo relevante em uma hora.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Modelo farmacocinético inadequado&lt;/strong&gt;: incorreta. O modelo de Schnider já incorpora idade, peso, altura e massa magra, contemplando o perfil do paciente.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Absorção errática do anestésico local&lt;/strong&gt;: incorreta. A ropivacaína a 0,2% no plano do eretor da espinha não deprime a consciência; excesso sistêmico se manifestaria como toxicidade neurológica e cardiovascular.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>O propofol é um alquilfenol altamente lipossolúvel, formulado em emulsão lipídica para uso intravenoso. As demais alternativas descrevem incorretamente os mecanismos do etomidato, benzodiazepínicos e barbitúricos.</t>
+          <t>&lt;p&gt;Quase todos os anestésicos venosos clássicos convergem para um mesmo alvo molecular, o receptor &lt;strong&gt;GABA&lt;sub&gt;A&lt;/sub&gt;&lt;/strong&gt;, principal mediador inibitório do sistema nervoso central, e diferem no &lt;em&gt;sítio&lt;/em&gt; e no &lt;em&gt;modo&lt;/em&gt; como o modulam. Compreender essa convergência evita a maioria das armadilhas deste tipo de questão.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;propofol&lt;/strong&gt; é um &lt;strong&gt;alquilfenol&lt;/strong&gt; (também grafado alcalifenol), líquido oleoso e &lt;strong&gt;altamente lipossolúvel&lt;/strong&gt; à temperatura ambiente, praticamente insolúvel em água, razão pela qual é apresentado em &lt;strong&gt;emulsão lipídica&lt;/strong&gt; e pela qual foi necessário desenvolver o fospropofol, um pró-fármaco hidrossolúvel. Essa lipossolubilidade é o que lhe confere início de ação rápido e redistribuição veloz. Seu efeito hipnótico decorre da potencialização da corrente de cloreto induzida pelo GABA, por ligação à &lt;strong&gt;subunidade β&lt;/strong&gt; do receptor GABA&lt;sub&gt;A&lt;/sub&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;etomidato&lt;/strong&gt; segue a mesma lógica de &lt;strong&gt;modulação alostérica positiva&lt;/strong&gt;: não disputa o sítio do GABA, mas amplifica sua ação; competir com o neurotransmissor produziria o efeito oposto, isto é, antagonismo. Os &lt;strong&gt;benzodiazepínicos&lt;/strong&gt; ocupam um sítio próprio no mesmo receptor, aumentando a &lt;strong&gt;frequência de abertura&lt;/strong&gt; do canal de cloreto, e nada têm a ver com bloqueio glutamatérgico: esse é o mecanismo da &lt;strong&gt;cetamina&lt;/strong&gt;, antagonista de receptores NMDA. Os &lt;strong&gt;barbitúricos&lt;/strong&gt;, por sua vez, prolongam o &lt;strong&gt;tempo de abertura&lt;/strong&gt; do canal e são igualmente lipossolúveis, atravessando a barreira hematoencefálica em um tempo de circulação braço-cérebro.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Propofol como alquilfenol altamente lipossolúvel à temperatura ambiente&lt;/strong&gt;: correta. É a característica físico-química que impõe a formulação em emulsão lipídica e explica seu perfil de início e término rápidos.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Etomidato competindo com o GABA pelo receptor&lt;/strong&gt;: incorreta. Atua como modulador alostérico positivo, potencializando o efeito do GABA em vez de disputá-lo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Benzodiazepínicos bloqueando receptores glutamatérgicos&lt;/strong&gt;: incorreta. Ligam-se a sítio específico do receptor GABA&lt;sub&gt;A&lt;/sub&gt;; o antagonismo glutamatérgico caracteriza a cetamina.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Barbitúricos com dificuldade de atravessar a barreira hematoencefálica por hidrossolubilidade&lt;/strong&gt;, incorreta em ambos os termos: são lipossolúveis e atravessam a barreira rapidamente.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>O propofol potencializa a neurotransmissão inibitória mediada pelo receptor GABA_A, aumentando a corrente de cloro e a hiperpolarização neuronal. Esse efeito explica sua ação hipnótica.</t>
+          <t>&lt;p&gt;O &lt;strong&gt;propofol&lt;/strong&gt; produz hipnose atuando sobre o receptor &lt;strong&gt;GABA&lt;sub&gt;A&lt;/sub&gt;&lt;/strong&gt;, o canal iônico responsável pela principal via inibitória rápida do sistema nervoso central. Ao ligar-se a sítios localizados nos domínios transmembrana da &lt;strong&gt;subunidade β&lt;/strong&gt; (com contribuição das subunidades β1, β2 e β3, e participação moduladora das subunidades α e γ2), o fármaco &lt;strong&gt;potencializa a corrente de cloreto induzida pelo GABA&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Vale distinguir os dois modos descritos para esse efeito. No modo &lt;strong&gt;indireto&lt;/strong&gt;, predominante em concentrações clínicas, o propofol atua como &lt;strong&gt;modulador alostérico positivo&lt;/strong&gt;: não abre o canal por conta própria, mas desloca a relação concentração-resposta do GABA para a esquerda, de modo que a mesma quantidade de neurotransmissor produz maior influxo de cloreto. Em concentrações mais altas, exerce também efeito &lt;strong&gt;direto&lt;/strong&gt;, ativando o canal na ausência de GABA. O influxo de cloreto &lt;strong&gt;hiperpolariza&lt;/strong&gt; o neurônio pós-sináptico e eleva o limiar de disparo, traduzindo-se clinicamente em sedação, hipnose e amnésia, com depressão dose-dependente do eletroencefalograma.&lt;/p&gt;&lt;p&gt;Esse mecanismo também explica os efeitos adversos característicos: a inibição generalizada do tônus simpático e a vasodilatação produzem &lt;strong&gt;hipotensão&lt;/strong&gt;, e a depressão dos centros respiratórios bulbares produz &lt;strong&gt;apneia&lt;/strong&gt; na indução. Convém fixar o contraste com os demais alvos anestésicos (antagonismo NMDA para a &lt;strong&gt;cetamina&lt;/strong&gt;, bloqueio de canais de sódio voltagem-dependentes para os &lt;strong&gt;anestésicos locais&lt;/strong&gt;), pois é sobre essa separação que a maioria dos distratores é construída.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Agonista dos receptores GABA&lt;sub&gt;A&lt;/sub&gt;&lt;/strong&gt;: correta. Potencializa a corrente de cloreto induzida pelo GABA por ligação à subunidade β, com hiperpolarização neuronal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Antagonismo de receptores NMDA&lt;/strong&gt;: incorreta. É o mecanismo da cetamina, e parcialmente do óxido nitroso e do xenônio.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Inibição da recaptação de serotonina&lt;/strong&gt;: incorreta. Corresponde a antidepressivos, sem relação com a hipnose do propofol.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bloqueio de canais de sódio voltagem-dependentes&lt;/strong&gt;: incorreta. É o mecanismo dos anestésicos locais e dos antiarrítmicos de classe I.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A solubilidade sanguínea dos anestésicos inalatórios tende a diminuir em estados de hipoproteinemia, como desnutrição. Menor solubilidade sanguínea favorece elevação mais rápida da fração alveolar.</t>
+          <t>&lt;p&gt;A solubilidade de um anestésico inalatório é expressa por &lt;strong&gt;coeficientes de partição&lt;/strong&gt;, que traduzem a capacidade relativa de cada fase de aceitar o agente. O coeficiente &lt;strong&gt;sangue:gás&lt;/strong&gt; é o determinante da velocidade de indução: quanto &lt;strong&gt;menor&lt;/strong&gt; a solubilidade sanguínea, mais rapidamente a pressão parcial alveolar se eleva em direção à inspirada, e mais rápidas são indução e despertar. Por isso &lt;strong&gt;desflurano&lt;/strong&gt; (0,42), &lt;strong&gt;óxido nitroso&lt;/strong&gt; (0,46) e &lt;strong&gt;sevoflurano&lt;/strong&gt; (0,69) são agentes de cinética rápida, enquanto o halotano (2,54) é lento.&lt;/p&gt;&lt;p&gt;Duas variáveis modificam esses coeficientes e são cobradas com frequência. A primeira é a &lt;strong&gt;temperatura&lt;/strong&gt;: a solubilidade de um gás em um líquido &lt;strong&gt;diminui quando a temperatura do líquido aumenta&lt;/strong&gt;, a mesma física que faz a bebida gelada reter mais gás carbônico do que a morna. Isso vale para os anestésicos e igualmente para O&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt; e CO&lt;sub&gt;2&lt;/sub&gt;, com implicação direta na interpretação de gasometrias corrigidas para a temperatura do paciente hipotérmico.&lt;/p&gt;&lt;p&gt;A segunda é a &lt;strong&gt;composição do sangue&lt;/strong&gt;. Como a maioria dos anestésicos é &lt;strong&gt;hidrofóbica&lt;/strong&gt;, eles se dissolvem preferencialmente em lipídios e se ligam a proteínas que formam bolsões hidrofóbicos. Consequentemente, a partição para o sangue &lt;strong&gt;aumenta após ingestão de alimentos gordurosos&lt;/strong&gt; e pode &lt;strong&gt;diminuir em pacientes anêmicos ou desnutridos&lt;/strong&gt;, nos quais o conteúdo de lipídios e de proteínas circulantes está reduzido. O mesmo caráter hidrofóbico explica a elevada afinidade pelo &lt;strong&gt;tecido adiposo&lt;/strong&gt;, responsável pelo acúmulo em anestesias prolongadas e pelo despertar retardado no paciente obeso.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Solubilidade sanguínea dos anestésicos inalatórios diminui em pacientes desnutridos&lt;/strong&gt;: correta. A redução de lipídios e proteínas plasmáticas diminui a partição do agente para o sangue.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Solubilidade sanguínea do CO&lt;sub&gt;2&lt;/sub&gt; aumenta com a elevação da temperatura&lt;/strong&gt;: incorreta. A relação é inversa: aquecer o líquido reduz a solubilidade do gás.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Solubilidade dos anestésicos inalatórios aumenta com a temperatura&lt;/strong&gt;: incorreta, pelo mesmo princípio físico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anestésicos hidrofóbicos com baixa solubilidade em tecido adiposo&lt;/strong&gt;: incorreta na conclusão. A hidrofobicidade implica justamente alta solubilidade nos tecidos ricos em lipídios.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Os efeitos da concentração e do segundo gás são mais relevantes com gases administrados em altas concentrações, especialmente o N2O, e têm menor importância clínica para agentes pouco solúveis como sevoflurano e desflurano.</t>
+          <t>&lt;p&gt;Os dois fenômenos nascem do mesmo evento: a &lt;strong&gt;captação de grande volume&lt;/strong&gt; de um gás administrado em alta concentração inspirada, papel historicamente do &lt;strong&gt;óxido nitroso&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;efeito da concentração&lt;/strong&gt; resulta de dois componentes simultâneos. O primeiro é o &lt;strong&gt;efeito concentrador&lt;/strong&gt;: quando um volume expressivo de gás é absorvido pelo sangue, o que resta no alvéolo passa a ocupar um volume pulmonar menor, e a fração dos gases remanescentes sobe automaticamente. O segundo é o &lt;strong&gt;aumento do influxo traqueal&lt;/strong&gt;: o vazio criado pela absorção é preenchido por gás fresco, que traz consigo mais anestésico. Um exemplo numérico torna o mecanismo transparente: partindo de 66% de N&lt;sub&gt;2&lt;/sub&gt;O, 33% de O&lt;sub&gt;2&lt;/sub&gt; e 1% de isoflurano, a captação de metade do N&lt;sub&gt;2&lt;/sub&gt;O reduz o volume gasoso em cerca de um terço, e a mistura alveolar passa a conter aproximadamente 49% de N&lt;sub&gt;2&lt;/sub&gt;O, 49% de O&lt;sub&gt;2&lt;/sub&gt; e &lt;strong&gt;1,5% de isoflurano&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;efeito do segundo gás&lt;/strong&gt; é a projeção desse fenômeno sobre o agente acompanhante: a captação volumosa do primeiro gás &lt;strong&gt;acelera&lt;/strong&gt; a elevação da pressão alveolar do segundo. O ponto que a questão cobra é a &lt;strong&gt;magnitude&lt;/strong&gt;. Como tudo depende do volume captado, o fenômeno exige um primeiro gás administrado em concentração muito alta, e sua repercussão é mais visível sobre um segundo gás &lt;strong&gt;solúvel&lt;/strong&gt;, cuja curva FA/FI subiria lentamente por conta própria e por isso tem mais a ganhar. Nos agentes &lt;strong&gt;pouco solúveis&lt;/strong&gt;, como &lt;strong&gt;desflurano&lt;/strong&gt; e &lt;strong&gt;sevoflurano&lt;/strong&gt;, a captação sanguínea é pequena e a razão FA/FI já se eleva rapidamente sem qualquer auxílio: sobra pouca margem para acelerar, e os efeitos tornam-se proporcionalmente &lt;strong&gt;menores&lt;/strong&gt;.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Efeitos menores nos gases pouco solúveis, como desflurano e sevoflurano, na comparação com gases mais solúveis&lt;/strong&gt;: correta. Nos agentes de baixa solubilidade a curva FA/FI já é rápida, restando pouca margem de aceleração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Óxido nitroso associado a gases muito solúveis reduzindo a velocidade de indução&lt;/strong&gt;: incorreta e no sentido inverso, pois é justamente nesses agentes que a aceleração é mais evidente.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Segundo gás atribuído ao óxido nitroso e efeito da concentração ao xenônio&lt;/strong&gt;: incorreta. Os dois fenômenos compartilham o mesmo mecanismo e dependem do mesmo primeiro gás em alta concentração inspirada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Halotano com FA/FI rápida por ser pouco solúvel&lt;/strong&gt;: incorreta na justificativa. O halotano é altamente solúvel, com coeficiente sangue:gás de 2,54; a aceleração observada decorre do efeito do segundo gás.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Quanto mais próximo o pKa do anestésico local estiver do pH fisiológico, maior a fração não ionizada disponível para atravessar a membrana neural, acelerando o início de ação.</t>
+          <t>&lt;p&gt;Três propriedades físico-químicas comandam o comportamento clínico de um anestésico local, e cada uma responde por um atributo distinto.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;pKa&lt;/strong&gt; determina a &lt;strong&gt;latência&lt;/strong&gt;. Como são &lt;strong&gt;bases fracas&lt;/strong&gt;, esses fármacos coexistem em solução sob duas formas: a base não ionizada, lipossolúvel, capaz de atravessar a bainha nervosa e a membrana axonal, e o cátion protonado, que é a forma efetivamente ativa no sítio interno do canal de sódio. O bloqueio exige as duas: penetração pela forma neutra, ligação pela forma ionizada. Por isso a latência é menor quanto &lt;strong&gt;mais próximo o pKa estiver do pH fisiológico&lt;/strong&gt;: essa é a condição que oferece a proporção ótima entre as frações ionizada e não ionizada. O corolário clínico é conhecido: em &lt;strong&gt;tecido infectado e acidótico&lt;/strong&gt;, a fração ionizada aumenta, sobra pouca base livre para penetrar o nervo e a qualidade do bloqueio se deteriora.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;lipossolubilidade&lt;/strong&gt; determina a &lt;strong&gt;potência&lt;/strong&gt;, e a &lt;strong&gt;ligação proteica&lt;/strong&gt;, a duração. A tetracaína ilustra bem o primeiro par: mais lipossolúvel que a procaína, é cerca de dez vezes mais potente. Atenção à classificação, porém: a divisão entre &lt;strong&gt;ésteres&lt;/strong&gt; e &lt;strong&gt;amidas&lt;/strong&gt; depende da ligação entre a cadeia intermediária e o anel aromático, e a tetracaína é um &lt;strong&gt;éster&lt;/strong&gt;, ao lado de procaína, cloroprocaína, benzocaína e cocaína.&lt;/p&gt;&lt;p&gt;Quanto à &lt;strong&gt;toxicidade sistêmica&lt;/strong&gt;, a &lt;strong&gt;emulsão lipídica&lt;/strong&gt; é o tratamento específico, em bolus seguido de infusão, e deve ser iniciada aos primeiros sinais. O &lt;strong&gt;propofol não é alternativa&lt;/strong&gt;: a fração lipídica de sua formulação é pequena demais para produzir sequestro do anestésico, e seu efeito inotrópico negativo e vasodilatador agrava justamente o colapso que se pretende tratar.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Início de ação mais rápido quando o pKa está próximo do pH fisiológico&lt;/strong&gt;: correta. Essa proximidade gera a razão ótima entre as frações ionizada e não ionizada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bases fortes, insolúveis em água&lt;/strong&gt;: incorreta. São bases fracas; a baixa hidrossolubilidade da base livre é o motivo de serem comercializadas como sais de cloridrato.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bupivacaína e tetracaína como amidas mais potentes&lt;/strong&gt;: incorreta na classificação. A tetracaína é éster; a associação entre lipossolubilidade e potência, essa sim, é válida.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Propofol como opção na ausência de emulsão lipídica&lt;/strong&gt;: incorreta e potencialmente perigosa. Não produz sequestro lipídico eficaz e aprofunda a depressão cardiovascular da intoxicação.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A dexametasona, quando usada como adjuvante em bloqueios periféricos, prolonga a duração da analgesia. A via perineural deve ser avaliada conforme formulação, dose e protocolos locais.</t>
+          <t>&lt;p&gt;Os adjuvantes buscam prolongar o bloqueio sem acrescentar toxicidade, e cada classe tem um perfil próprio de risco.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;dexametasona&lt;/strong&gt; tornou-se o adjuvante de melhor relação entre benefício e segurança. Prolonga de forma consistente a duração do bloqueio de nervos periféricos, com &lt;strong&gt;efeitos colaterais mínimos&lt;/strong&gt; nas doses habituais de &lt;strong&gt;4 a 10 mg&lt;/strong&gt; no adulto. A administração perineural parece mais eficaz que a sistêmica, embora muitos serviços prefiram a via sistêmica por evitar a mistura de fármacos não formulados para uso conjunto, contornar o uso off-label perineural e aproveitar o efeito antiemético. Duas ressalvas honestas devem acompanhar o conceito: o mecanismo preciso não está esclarecido, e o potencial neurotóxico não foi adequadamente estudado.&lt;/p&gt;&lt;p&gt;Entre os &lt;strong&gt;opioides neuroaxiais&lt;/strong&gt;, a variável decisiva é a &lt;strong&gt;lipossolubilidade&lt;/strong&gt;. &lt;strong&gt;Fentanil&lt;/strong&gt; e &lt;strong&gt;sufentanil&lt;/strong&gt;, muito lipossolúveis, são captados rapidamente pela medula e pela gordura epidural, permanecem pouco tempo livres no líquido cefalorraquidiano e por isso apresentam &lt;strong&gt;difusão rostral limitada&lt;/strong&gt;; daí início rápido, duração curta e baixo risco de depressão respiratória tardia. A &lt;strong&gt;morfina&lt;/strong&gt;, hidrofílica, faz o oposto: permanece no líquido cefalorraquidiano, migra em sentido cefálico e responde pela depressão respiratória de aparecimento tardio.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;dexmedetomidina&lt;/strong&gt;, agonista alfa-2, prolonga os bloqueios sensorial e motor; o ponto de atenção é a bradicardia e a hipotensão, dose-dependentes. A &lt;strong&gt;adrenalina&lt;/strong&gt; atua por vasoconstrição local, reduzindo a absorção sistêmica do anestésico e prolongando o bloqueio.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dexametasona prolonga a duração do bloqueio com mínimo efeito colateral&lt;/strong&gt;: correta. É o adjuvante com melhor perfil de segurança nas doses usuais, embora o mecanismo exato permaneça em aberto.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Adrenalina reduzindo o fluxo sanguíneo medular&lt;/strong&gt;: incorreta como efeito esperado. A finalidade da adição é a vasoconstrição local com prolongamento do bloqueio, e a dose citada não encontra respaldo na literatura padrão para essa via.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Maior difusão rostral do fentanil e do sufentanil&lt;/strong&gt;: incorreta, e no sentido inverso. Por serem lipossolúveis, difundem-se pouco no sentido rostral; essa é característica da morfina.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dexmedetomidina intratecal em dose baixa com alterações hemodinâmicas&lt;/strong&gt;: incorreta. O prolongamento do bloqueio ocorre, mas sem repercussão hemodinâmica relevante nessa faixa de dose.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>O lítio pode prolongar o bloqueio neuromuscular por interferir na transmissão neuromuscular e na liberação/ação da acetilcolina. A monitorização quantitativa é recomendada.</t>
+          <t>&lt;p&gt;A questão testa a capacidade de separar fármacos que &lt;strong&gt;potencializam&lt;/strong&gt; daqueles que produzem &lt;strong&gt;resistência&lt;/strong&gt; ao bloqueio neuromuscular adespolarizante, distinção que se resolve pelo mecanismo de cada um sobre a junção neuromuscular.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;carbonato de lítio&lt;/strong&gt; é o potencializador. Por sua semelhança com os íons sódio e potássio, interfere no transporte iônico transmembrana e na transmissão neuromuscular, de modo que as respostas tanto aos bloqueadores &lt;strong&gt;despolarizantes&lt;/strong&gt; quanto aos &lt;strong&gt;adespolarizantes&lt;/strong&gt; podem ser &lt;strong&gt;prolongadas&lt;/strong&gt; em sua presença. O lítio ainda reduz a necessidade de anestésicos injetáveis e inalatórios pela sedação associada, e pode retardar a recuperação do efeito depressor central dos barbitúricos, o que amplifica, na prática, a impressão de bloqueio residual. Atenção adicional ao paciente em uso concomitante de &lt;strong&gt;diuréticos tiazídicos&lt;/strong&gt; ou &lt;strong&gt;anti-inflamatórios não esteroidais&lt;/strong&gt;, que elevam a concentração plasmática de lítio por redução da depuração renal.&lt;/p&gt;&lt;p&gt;Do outro lado estão os indutores de &lt;strong&gt;resistência&lt;/strong&gt;. &lt;strong&gt;Anticonvulsivantes&lt;/strong&gt; em uso crônico, como fenitoína e carbamazepina, induzem enzimas hepáticas e promovem proliferação de receptores de acetilcolina, exigindo doses maiores de bloqueador. &lt;strong&gt;Corticosteroides&lt;/strong&gt; em uso prolongado também cursam com resistência, além do risco de miopatia quando combinados a bloqueadores em terapia intensiva. O &lt;strong&gt;cálcio&lt;/strong&gt; segue lógica ainda mais direta: aumenta a liberação de acetilcolina na fenda sináptica e, portanto, &lt;strong&gt;antagoniza&lt;/strong&gt; o bloqueio.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Carbonato de lítio&lt;/strong&gt;: correta. Prolonga a resposta tanto a despolarizantes quanto a adespolarizantes por interferência no transporte iônico da transmissão neuromuscular.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Esteroide&lt;/strong&gt;: incorreta. O uso crônico associa-se a resistência ao bloqueio e a miopatia, não a potencialização.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anticonvulsivante&lt;/strong&gt;: incorreta. Induz resistência, com necessidade de doses maiores e duração encurtada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gluconato de cálcio&lt;/strong&gt;: incorreta, e no sentido oposto. O cálcio antagoniza o bloqueio ao facilitar a liberação de acetilcolina.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Na miastenia gravis há redução de receptores nicotínicos, gerando resistência relativa à succinilcolina; doses maiores podem ser necessárias. Em contraste, há grande sensibilidade aos bloqueadores não despolarizantes.</t>
+          <t>&lt;p&gt;A doença descrita é a &lt;strong&gt;miastenia gravis&lt;/strong&gt;: autoanticorpos dirigidos contra as &lt;strong&gt;subunidades alfa do receptor nicotínico de acetilcolina&lt;/strong&gt; na membrana pós-sináptica, com destruição e redução do número de receptores funcionantes. Toda a conduta anestésica decorre dessa única alteração.&lt;/p&gt;&lt;p&gt;Menos receptores disponíveis significa &lt;strong&gt;margem de segurança reduzida&lt;/strong&gt; na transmissão neuromuscular. Daí a &lt;strong&gt;sensibilidade exagerada aos bloqueadores adespolarizantes&lt;/strong&gt;, que competem por receptores já escassos: doses convencionais produzem bloqueio profundo e prolongado, e a titulação com monitorização quantitativa é obrigatória.&lt;/p&gt;&lt;p&gt;Com a &lt;strong&gt;succinilcolina&lt;/strong&gt; ocorre o inverso, e este é o ponto central da questão. Como o fármaco precisa ocupar um número suficiente de receptores para despolarizar a placa motora, a escassez de receptores gera &lt;strong&gt;resistência&lt;/strong&gt;: a dose habitual pode não produzir condições adequadas de intubação, e a orientação clássica é &lt;strong&gt;aumentar a dose&lt;/strong&gt;, na faixa de &lt;strong&gt;1,5 a 2 mg/kg&lt;/strong&gt;. Some-se a isso o uso crônico de &lt;strong&gt;anticolinesterásicos&lt;/strong&gt; como a piridostigmina, que inibem também a butirilcolinesterase e retardam a hidrólise da succinilcolina, prolongando seu efeito e elevando o risco de &lt;strong&gt;bloqueio de fase II&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Sobre as demais condutas: o &lt;strong&gt;sugamadex&lt;/strong&gt; é plenamente eficaz e mudou o paradigma, permitindo o uso criterioso de rocurônio; a &lt;strong&gt;manutenção do anticolinesterásico&lt;/strong&gt; é a regra, já que a suspensão precipita fraqueza; e os &lt;strong&gt;agentes inalatórios&lt;/strong&gt; não só são permitidos como úteis, por oferecerem relaxamento cirúrgico com pouca ou nenhuma necessidade de bloqueador.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dose de succinilcolina de 1,5 a 2 mg/kg&lt;/strong&gt;: correta. A redução do número de receptores nicotínicos torna o paciente resistente ao fármaco, exigindo dose superior à habitual.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sugamadex ineficaz na reversão de rocurônio ou vecurônio&lt;/strong&gt;: incorreta. É eficaz, e sua disponibilidade viabiliza o uso seguro de bloqueadores esteroidais nesses pacientes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Suspensão do anticolinesterásico cinco dias antes&lt;/strong&gt;: incorreta. A retirada expõe a piora da fraqueza e a crise miastênica; a orientação é manter a medicação.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Contraindicação de agentes inalatórios potentes&lt;/strong&gt;: incorreta. São permitidos e vantajosos por reduzirem a necessidade de bloqueio neuromuscular.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Durante a ressuscitação cardiopulmonar, recomenda-se a maior fração inspirada de oxigênio disponível. Após retorno da circulação espontânea, a oferta deve ser titulada para evitar hiperóxia.</t>
+          <t>&lt;p&gt;O caso reúne duas decisões independentes: como abrir a via aérea de um paciente com &lt;strong&gt;suspeita de trauma cervical&lt;/strong&gt; e com que fração de oxigênio ventilar durante a ressuscitação.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;mergulho em água rasa&lt;/strong&gt; é mecanismo clássico de &lt;strong&gt;lesão da coluna cervical&lt;/strong&gt;, e o paciente chega imobilizado precisamente por isso. Nesse cenário, a &lt;strong&gt;extensão da cabeça&lt;/strong&gt; deve ser evitada: a manobra de escolha é a &lt;strong&gt;tração da mandíbula&lt;/strong&gt;, com estabilização manual da coluna realizada por um auxiliar. Os colares cervicais, vale notar, dificultam de modo importante as manobras de desobstrução e não substituem a estabilização manual durante o manejo da via aérea.&lt;/p&gt;&lt;p&gt;Quanto à oxigenação, a orientação é administrar &lt;strong&gt;oxigênio a 100%&lt;/strong&gt; durante as manobras de ressuscitação, &lt;strong&gt;independentemente do dispositivo&lt;/strong&gt; empregado para controlar a via aérea. A justificativa merece ser compreendida, e não apenas memorizada: durante a parada, o débito cardíaco gerado pelas compressões é uma fração do normal, e maximizar o conteúdo arterial de oxigênio é a única alavanca disponível para sustentar a oferta tecidual. O preço potencial dessa escolha é conhecido (&lt;strong&gt;geração de radicais livres de oxigênio&lt;/strong&gt;, &lt;strong&gt;vasoconstrição cerebral&lt;/strong&gt; e &lt;strong&gt;toxicidade pulmonar&lt;/strong&gt;), motivo pelo qual a fração inspirada deve ser titulada para baixo assim que houver retorno da circulação espontânea e monitorização confiável da saturação.&lt;/p&gt;&lt;p&gt;Por fim, a &lt;strong&gt;ventilação boca a boca&lt;/strong&gt; perde sentido em ambiente hospitalar, onde estão disponíveis o sistema balão-válvula-máscara e o circuito circular com alta fração de oxigênio.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Oxigênio a 100% independentemente do dispositivo, com risco de radicais livres, vasoconstrição cerebral e toxicidade pulmonar&lt;/strong&gt;: correta. Reproduz a recomendação e os efeitos indesejáveis que a justificam.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Extensão da cabeça e elevação do mento&lt;/strong&gt;: incorreta. Com suspeita de trauma cervical, a extensão é contraindicada; a manobra indicada é a tração da mandíbula com estabilização manual.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dispositivos supraglóticos como os mais adequados por facilidade de colocação&lt;/strong&gt;: incorreta. A facilidade de inserção não define isoladamente a melhor via aérea neste contexto.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ventilação boca a boca com obstrução das narinas e extensão da cabeça&lt;/strong&gt;: incorreta em dois pontos, pois é dispensável em ambiente hospitalar e emprega manobra contraindicada na suspeita de lesão cervical.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Diante de aparente assistolia, deve-se primeiro confirmar o ritmo, verificando cabos, ganho e derivação, para excluir fibrilação ventricular fina ou falha técnica. Em seguida, prossegue-se com RCP e adrenalina conforme o algoritmo.</t>
+          <t>&lt;p&gt;Diante de uma &lt;strong&gt;linha isoelétrica&lt;/strong&gt; no monitor, a primeira obrigação não é tratar: é &lt;strong&gt;confirmar o ritmo&lt;/strong&gt;. Uma linha reta pode representar assistolia verdadeira, mas pode igualmente resultar de &lt;strong&gt;cabo desconectado&lt;/strong&gt;, &lt;strong&gt;eletrodo mal aderido&lt;/strong&gt;, &lt;strong&gt;ganho de amplitude reduzido&lt;/strong&gt; ou &lt;strong&gt;derivação inadequada&lt;/strong&gt;. Verificar cabos, ganho e derivação (e checar o traçado em uma segunda derivação) é o passo que distingue assistolia de &lt;strong&gt;fibrilação ventricular fina&lt;/strong&gt;, e essa distinção muda inteiramente a conduta: a fibrilação ventricular é ritmo &lt;strong&gt;chocável&lt;/strong&gt;, a assistolia não é.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;assistolia&lt;/strong&gt; caracteriza-se pela ausência completa e sustentada de atividade elétrica e carrega prognóstico reservado. Uma vez confirmada, o tratamento é ressuscitação de alta qualidade com &lt;strong&gt;adrenalina&lt;/strong&gt; o mais precocemente possível e busca ativa das causas reversíveis; no caso de &lt;strong&gt;afogamento&lt;/strong&gt;, a hipóxia é a causa dominante, o que confere peso especial à ventilação e à oxigenação, ao contrário da parada de origem primariamente cardíaca.&lt;/p&gt;&lt;p&gt;Dois erros conceituais merecem registro. &lt;strong&gt;Desfibrilar assistolia&lt;/strong&gt; não produz benefício algum e ainda interrompe as compressões, derrubando a pressão de perfusão coronariana justamente quando ela é mais crítica. E a dose de adrenalina deve respeitar o peso do &lt;strong&gt;adolescente&lt;/strong&gt;, calculada em &lt;strong&gt;0,01 mg/kg&lt;/strong&gt;, e não a dose fixa do adulto.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Verificar os cabos, ganho e derivação&lt;/strong&gt;: correta. Confirmar que a linha isoelétrica corresponde ao ritmo real, e não a artefato ou fibrilação ventricular fina, precede qualquer decisão terapêutica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aplicar um choque de 200 J&lt;/strong&gt;: incorreta. A assistolia é ritmo não chocável; o choque não beneficia e interrompe as compressões.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Administrar 1 mg de adrenalina por via intravenosa&lt;/strong&gt;: incorreta neste momento e nesta dose. A adrenalina vem após a confirmação do ritmo, e a dose pediátrica é calculada por peso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Transferir o paciente para uma unidade hospitalar&lt;/strong&gt;: incorreta. A ressuscitação não é interrompida para transporte; o atendimento prossegue no local.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>O bloqueio peridural torácico reduz o tônus simpático, podendo causar vasodilatação e diminuição da pressão arterial sistólica. O efeito depende da extensão do bloqueio e da reserva cardiovascular.</t>
+          <t>&lt;p&gt;A peridural torácica oferece analgesia de excelente qualidade após toracotomia, mas o preço fisiológico é um &lt;strong&gt;bloqueio simpático segmentar&lt;/strong&gt;, e é dele que decorrem todas as alterações esperadas.&lt;/p&gt;&lt;p&gt;O bloqueio das fibras simpáticas pré-ganglionares nos segmentos atingidos produz &lt;strong&gt;vasodilatação arteriolar e venosa&lt;/strong&gt; no território correspondente. A vasodilatação arteriolar &lt;strong&gt;reduz a resistência vascular sistêmica&lt;/strong&gt;; a venodilatação represa sangue no leito de capacitância e &lt;strong&gt;reduz o retorno venoso&lt;/strong&gt; e, portanto, a pré-carga. O resultado combinado é &lt;strong&gt;queda da pressão arterial&lt;/strong&gt;, achado mais previsível e mais precoce do procedimento.&lt;/p&gt;&lt;p&gt;Há um agravante próprio do bloqueio &lt;strong&gt;torácico alto&lt;/strong&gt;: quando o nível alcança os segmentos de &lt;strong&gt;T1 a T4&lt;/strong&gt;, são atingidas as &lt;strong&gt;fibras aceleradoras cardíacas&lt;/strong&gt;. O paciente perde a capacidade de responder à hipotensão com taquicardia compensatória, e a frequência cardíaca tende a permanecer inalterada ou a &lt;strong&gt;diminuir&lt;/strong&gt;. Some-se a redução da pré-carga à perda do estímulo cronotrópico e inotrópico simpático e o &lt;strong&gt;débito cardíaco cai&lt;/strong&gt;, em vez de subir.&lt;/p&gt;&lt;p&gt;A consequência prática é dupla. Primeiro, a &lt;strong&gt;taquicardia deixa de ser sinal confiável&lt;/strong&gt; de hipovolemia ou anemia nesse paciente; a leitura hemodinâmica precisa apoiar-se em outros parâmetros. Segundo, durante a &lt;strong&gt;ventilação monopulmonar&lt;/strong&gt;, a peridural torácica não interfere diretamente na vasoconstrição pulmonar hipóxica, que é resposta química local, mas pode piorar a oxigenação de modo &lt;strong&gt;indireto&lt;/strong&gt;, caso se permita hipotensão e queda do débito cardíaco.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Diminuição da pressão arterial sistólica&lt;/strong&gt;: correta. Decorre diretamente da vasodilatação arteriolar e da redução do retorno venoso provocadas pelo bloqueio simpático.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumento da resistência vascular sistêmica&lt;/strong&gt;: incorreta. O bloqueio simpático reduz a resistência vascular sistêmica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumento da frequência cardíaca&lt;/strong&gt;: incorreta. O bloqueio das fibras aceleradoras cardíacas de T1 a T4 impede a resposta taquicárdica compensatória.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumento do débito cardíaco&lt;/strong&gt;: incorreta. Menor pré-carga e menor estímulo simpático cardíaco reduzem o débito.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A artéria de Adamkiewicz é a principal artéria radiculomedular anterior e contribui para a irrigação da medula toracolombar. Sua lesão pode causar isquemia medular e paraplegia.</t>
+          <t>&lt;p&gt;A medula espinhal é irrigada por um sistema deliberadamente assimétrico, e essa assimetria explica a vulnerabilidade isquêmica que a questão cobra.&lt;/p&gt;&lt;p&gt;Existe uma única &lt;strong&gt;artéria espinhal anterior&lt;/strong&gt;, formada pela confluência de ramos das artérias vertebrais e reforçada ao longo do trajeto por artérias radiculares segmentares. Ela supre os &lt;strong&gt;dois terços anteriores&lt;/strong&gt; da medula, território que inclui os &lt;strong&gt;tratos corticoespinhais&lt;/strong&gt;, responsáveis pela motricidade, e os &lt;strong&gt;tratos espinotalâmicos&lt;/strong&gt;, responsáveis pela sensibilidade térmica e dolorosa. Em contrapartida, existem &lt;strong&gt;duas artérias espinhais posteriores&lt;/strong&gt;, que suprem o terço posterior, onde trafegam os &lt;strong&gt;funículos posteriores&lt;/strong&gt; de propriocepção e sensibilidade vibratória, e que contam com rede anastomótica bem mais rica.&lt;/p&gt;&lt;p&gt;O ponto crítico é o reforço da circulação anterior na região toracolombar. A &lt;strong&gt;artéria radicular magna&lt;/strong&gt;, ou &lt;strong&gt;artéria de Adamkiewicz&lt;/strong&gt;, é o principal vaso nutridor desse segmento, origina-se em geral entre T9 e T12 e, na maioria das pessoas, à &lt;strong&gt;esquerda&lt;/strong&gt;. Sua lesão (em cirurgia de aorta toracoabdominal, com clampeamento prolongado, ou por hipotensão grave) produz a &lt;strong&gt;síndrome da artéria espinhal anterior&lt;/strong&gt;: &lt;strong&gt;paraplegia&lt;/strong&gt; com perda da sensibilidade térmica e dolorosa abaixo da lesão, e &lt;strong&gt;preservação característica da propriocepção e da sensibilidade vibratória&lt;/strong&gt;, cujos tratos permanecem irrigados pelo território posterior. É essa dissociação sensitiva que confirma o diagnóstico topográfico à beira do leito.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Artéria radicular magna (de Adamkiewicz)&lt;/strong&gt;: é a resposta correta em termos anatômicos. Principal reforço da artéria espinhal anterior na região toracolombar, sua lesão produz a síndrome da artéria espinhal anterior com paraplegia.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Demais vasos assinalados na figura&lt;/strong&gt;: as artérias espinhais posteriores e os ramos segmentares acessórios contam com rede anastomótica mais rica e não respondem, isoladamente, pelo quadro clássico de paraplegia.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>O quadro é típico de bloqueio neuromuscular residual, apesar de sinais clínicos aparentemente satisfatórios. Idade avançada, dose elevada de rocurônio, magnésio e reversão sem monitorização quantitativa aumentam o risco.</t>
+          <t>&lt;p&gt;O caso é uma construção didática: cada fármaco administrado soma um fator de potencialização sobre o mesmo bloqueador neuromuscular, e os testes clínicos usados para liberar a extubação são justamente os menos sensíveis.&lt;/p&gt;&lt;p&gt;Comece pela dose. Foram &lt;strong&gt;84 mg de rocurônio&lt;/strong&gt; em uma paciente de 70 kg, ou seja, &lt;strong&gt;1,2 mg/kg&lt;/strong&gt;, dose de sequência rápida, cerca do dobro da dose habitual de intubação, para uma cirurgia que durou apenas &lt;strong&gt;30 minutos&lt;/strong&gt;. A esse ponto de partida somam-se três potencializadores documentados. A &lt;strong&gt;gentamicina&lt;/strong&gt;, aminoglicosídeo, e a &lt;strong&gt;clindamicina&lt;/strong&gt;, lincosamida, inibem a liberação pré-juncional de acetilcolina e ainda deprimem a sensibilidade pós-juncional do receptor nicotínico. O &lt;strong&gt;sulfato de magnésio&lt;/strong&gt; bloqueia os canais de cálcio pré-sinápticos que disparam a liberação de acetilcolina. E o &lt;strong&gt;halogenado&lt;/strong&gt; da anestesia balanceada potencializa o bloqueio por efeito farmacodinâmico próprio.&lt;/p&gt;&lt;p&gt;O erro seguinte está na reversão. &lt;strong&gt;Neostigmina&lt;/strong&gt; tem &lt;strong&gt;efeito teto&lt;/strong&gt;: por atuar inibindo a acetilcolinesterase, depende de que já exista recuperação espontânea suficiente. Administrada diante de bloqueio profundo (o esperado após 1,2 mg/kg em apenas 30 minutos), a reversão é incompleta, e o efeito pode &lt;strong&gt;dissipar-se antes&lt;/strong&gt; que o rocurônio seja eliminado, gerando &lt;strong&gt;recurarização&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Por fim, os sinais que motivaram a extubação são &lt;strong&gt;clinicamente insuficientes&lt;/strong&gt;. Sustentar a cabeça por cinco segundos e ventilar espontaneamente ocorrem com &lt;strong&gt;razão T4/T1 em torno de 0,5&lt;/strong&gt;, muito abaixo do limiar de segurança de &lt;strong&gt;0,9&lt;/strong&gt;. Nessa faixa persiste fraqueza da musculatura faríngea e dos quimiorreceptores carotídeos, com risco de obstrução de via aérea e broncoaspiração, o que explica a tosse e a queda da saturação para 79% na sala de recuperação. Só a &lt;strong&gt;monitorização quantitativa&lt;/strong&gt; descarta bloqueio residual.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Bloqueio neuromuscular residual&lt;/strong&gt;: correta. Dose elevada, cirurgia curta, três potencializadores associados, reversão provavelmente prematura e critérios clínicos insensíveis compõem o quadro.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Embolia gasosa por pneumoperitônio&lt;/strong&gt;: incorreta. É evento intraoperatório súbito, com colapso hemodinâmico e queda abrupta da EtCO2.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Magnésio intensificando resíduo de anestésico inalatório&lt;/strong&gt;: incorreta no mecanismo. O magnésio potencializa o bloqueio neuromuscular por inibição de canais de cálcio pré-sinápticos.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Fentanil residual&lt;/strong&gt;: incorreta. Produziria sonolência, bradipneia e miose, e não tosse com dessaturação de padrão obstrutivo.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A atelectasia é uma causa comum de shunt e hipoxemia no pós-operatório imediato, especialmente em pacientes obesos após anestesia geral e laparoscopia. Recrutamento pulmonar, CPAP e analgesia adequada podem ser necessários.</t>
+          <t>&lt;p&gt;Diante de hipoxemia na sala de recuperação, o raciocínio produtivo é percorrer os mecanismos possíveis e escolher o que a fisiologia perioperatória torna mais provável.&lt;/p&gt;&lt;p&gt;A causa dominante é o &lt;strong&gt;shunt intrapulmonar direita-esquerda por atelectasia&lt;/strong&gt;. A anestesia geral reduz a &lt;strong&gt;capacidade residual funcional&lt;/strong&gt; desde a indução, e o colapso alveolar nas regiões dependentes se instala em minutos. Nesta paciente, os fatores se acumulam: &lt;strong&gt;índice de massa corporal em torno de 40 kg/m²&lt;/strong&gt;, que por si só reduz a capacidade residual funcional; &lt;strong&gt;pneumoperitônio&lt;/strong&gt;, que eleva o diafragma e comprime as bases; e o decúbito. Unidades perfundidas e não ventiladas não corrigem com aumento da fração inspirada de oxigênio, daí a persistência da SpO&lt;sub&gt;2&lt;/sub&gt; em 91% mesmo sob suplementação. O tratamento é &lt;strong&gt;recrutamento e pressão positiva&lt;/strong&gt;, não simplesmente mais oxigênio.&lt;/p&gt;&lt;p&gt;Vale contrastar com os demais mecanismos da lista. A &lt;strong&gt;hipóxia de difusão&lt;/strong&gt; exige óxido nitroso e é improvável sob oxigênio suplementar; não houve óxido nitroso nesta anestesia. A &lt;strong&gt;hipoventilação alveolar&lt;/strong&gt; por efeito residual de anestésicos ou bloqueadores neuromusculares é causa frequente, mas cursa com hipercapnia e responde bem ao oxigênio, ao contrário do shunt verdadeiro. E os anestésicos residuais &lt;strong&gt;inibem&lt;/strong&gt; a vasoconstrição pulmonar hipóxica (o mecanismo que desviaria fluxo das áreas colapsadas), agravando a hipoxemia em vez de protegê-la.&lt;/p&gt;&lt;p&gt;Quanto à alta, o índice de &lt;strong&gt;Aldrete-Kroulik modificado&lt;/strong&gt; exige &lt;strong&gt;pontuação igual ou superior a 9&lt;/strong&gt;. Nesta paciente somam-se 2 pela movimentação dos quatro membros, 1 pela dispneia, 1 pela consciência ao chamado, 1 pela queda pressórica em torno de 30% do nível pré-anestésico e 1 por manter saturação acima de 90% apenas sob oxigênio: &lt;strong&gt;total de 6&lt;/strong&gt;. A alta está de fato contraindicada, mas por uma pontuação inferior à que a alternativa propõe.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Atelectasia como causa mais comum de shunt pulmonar no pós-operatório imediato&lt;/strong&gt;: correta. A queda da capacidade residual funcional, agravada por obesidade e pneumoperitônio, produz shunt refratário ao aumento da fração inspirada de oxigênio.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipóxia de difusão como principal suspeita&lt;/strong&gt;: incorreta. Depende de óxido nitroso, não utilizado aqui, e é improvável sob oxigênio suplementar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Índice de Aldrete-Kroulik modificado de 7&lt;/strong&gt;: incorreta na pontuação. O somatório dos itens resulta em 6, ainda que a contraindicação à alta seja pertinente.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anestésicos residuais estimulando a vasoconstrição pulmonar hipóxica&lt;/strong&gt;: incorreta, e no sentido inverso: eles inibem esse mecanismo compensatório.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>A pergunta de pesquisa orienta o desenho do estudo, a estratégia de busca e a estrutura da revisão bibliográfica. Uma pergunta bem formulada delimita população, intervenção/exposição, comparação e desfechos.</t>
+          <t>&lt;p&gt;A &lt;strong&gt;pergunta-problema&lt;/strong&gt; é o elemento estruturante de todo o projeto de pesquisa, e sua função vai muito além de abrir o texto. Uma pergunta bem formulada &lt;strong&gt;orienta a revisão bibliográfica&lt;/strong&gt; (que é justamente o instrumento pelo qual se demonstra a necessidade do estudo), &lt;strong&gt;determina o desenho&lt;/strong&gt;, define os &lt;strong&gt;métodos&lt;/strong&gt; e o &lt;strong&gt;cálculo do tamanho amostral&lt;/strong&gt;, e limita o potencial de &lt;strong&gt;erro e viés&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;É essa cadeia de dependências que responde à questão. A extensão e a estrutura da revisão de literatura não são arbitrárias: derivam diretamente do que a pergunta delimita. Perguntar sobre uma população específica, uma intervenção específica e um desfecho específico define, por consequência, quais corpos de evidência precisam ser percorridos e até onde a busca deve ir. Uma pergunta vaga produz revisão dispersa; uma pergunta precisa produz revisão delimitada e demonstrável.&lt;/p&gt;&lt;p&gt;O formato &lt;strong&gt;PICOTS&lt;/strong&gt; (População, Intervenção, Comparador, Desfecho, Horizonte temporal e Cenário) é o arcabouço mais difundido para estruturar essa pergunta e comprovadamente melhora sua qualidade. Em estudos observacionais, a intervenção e o comparador podem ser baseados em características do paciente ou do cuidado, em vez de randomizados. Já durante a elaboração do protocolo, as perguntas de pesquisa são convertidas em &lt;strong&gt;hipóteses formais&lt;/strong&gt;, cuja estrutura depende de o investigador predizer superioridade, equivalência ou não inferioridade.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Capacidade de determinar toda a extensão da estrutura da revisão bibliográfica&lt;/strong&gt;: correta. É a pergunta que orienta a revisão, a qual por sua vez estabelece a necessidade do estudo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dispensa de projetos-piloto&lt;/strong&gt;: incorreta. O piloto testa viabilidade e logística e permanece necessário independentemente da qualidade da pergunta.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Abrangência de no mínimo duas áreas de pesquisa&lt;/strong&gt;: incorreta. Não há tal exigência; relevância não se mede por amplitude temática.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Número expressivo de ensaios clínicos na área&lt;/strong&gt;: incorreta, e no sentido inverso. Muitos ensaios prévios sugerem lacuna já preenchida, reduzindo a relevância da pergunta.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>O traçado mostra reinalação de CO2 por falha da válvula expiratória, com linha de base inspiratória acima de zero. Deve-se verificar imediatamente valvas, absorvedor e circuito.</t>
+          <t>&lt;p&gt;Cada anormalidade do capnograma tem uma assinatura morfológica própria, e reconhecê-las é uma habilidade diagnóstica de beira de leito.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;válvula expiratória defeituosa&lt;/strong&gt; permite que gás já exalado retorne ao ramo inspiratório. O resultado é &lt;strong&gt;reinalação de CO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt;, cuja assinatura inconfundível é a &lt;strong&gt;linha de base inspiratória que não retorna a zero&lt;/strong&gt;: o CO&lt;sub&gt;2&lt;/sub&gt; inspirado permanece consistentemente acima de zero ao longo de todo o ciclo. A mesma morfologia surge com &lt;strong&gt;absorvedor de cal sodada exaurido&lt;/strong&gt;, e por isso as duas hipóteses caminham juntas na avaliação.&lt;/p&gt;&lt;p&gt;Convém distinguir da &lt;strong&gt;válvula inspiratória defeituosa&lt;/strong&gt;, que produz achado diferente: a fase descendente da curva torna-se mais lenta e se prolonga para dentro da fase inspiratória, porque o CO&lt;sub&gt;2&lt;/sub&gt; presente no ramo inspiratório é reinalado; o padrão afeta a inclinação da descida, e não o nível da linha de base.&lt;/p&gt;&lt;p&gt;As demais morfologias seguem lógicas distintas. As &lt;strong&gt;oscilações cardiogênicas&lt;/strong&gt; aparecem como pequenas ondulações rítmicas &lt;strong&gt;ao final da expiração&lt;/strong&gt;, quando o fluxo cai a zero e o coração pulsátil promove esvaziamento alternado de regiões pulmonares diferentes, movimentando gás exalado e gás fresco. Os &lt;strong&gt;esforços de respiração espontânea&lt;/strong&gt; durante ventilação controlada produzem &lt;strong&gt;fendas verticais na fase III&lt;/strong&gt; do platô, o clássico entalhe da curare. E um &lt;strong&gt;vazamento na linha de amostragem&lt;/strong&gt; reduz a amplitude do traçado e falseia a EtCO&lt;sub&gt;2&lt;/sub&gt; para baixo, sem elevar a linha de base.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Válvula expiratória com defeito&lt;/strong&gt;: correta. Provoca reinalação de CO&lt;sub&gt;2&lt;/sub&gt;, com linha de base inspiratória consistentemente acima de zero.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Vazamento na linha de capnografia&lt;/strong&gt;: incorreta. Reduz a amplitude e subestima a EtCO&lt;sub&gt;2&lt;/sub&gt;, sem deslocar a linha de base.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Oscilações cardiogênicas ao final da expiração&lt;/strong&gt;: incorreta como explicação deste traçado. Manifestam-se como ondulações rítmicas na porção terminal da expiração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Esforços de respiração espontânea durante ventilação controlada&lt;/strong&gt;: incorreta. Geram fendas na fase III do platô, não alteração da linha de base.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>O termocompensador ajusta a divisão do fluxo conforme a temperatura, mantendo a concentração de saída mais estável. Materiais com coeficientes de dilatação diferentes são usados para compensar o resfriamento do anestésico.</t>
+          <t>&lt;p&gt;A vaporização de um anestésico halogenado consome calor latente, e o líquido &lt;strong&gt;esfria&lt;/strong&gt; à medida que é vaporizado. Como a &lt;strong&gt;pressão de vapor saturado&lt;/strong&gt; é diretamente dependente da temperatura, esse resfriamento reduz a quantidade de anestésico incorporada ao gás, e a concentração entregue cairia progressivamente ao longo da anestesia se nada corrigisse o fenômeno.&lt;/p&gt;&lt;p&gt;A solução dos vaporizadores calibrados é o &lt;strong&gt;termocompensador&lt;/strong&gt;, um elemento de expansão-contração, na prática uma &lt;strong&gt;lâmina bimetálica&lt;/strong&gt;, formada por dois metais com &lt;strong&gt;coeficientes de dilatação diferentes&lt;/strong&gt;. Justamente por serem materiais de &lt;strong&gt;alto coeficiente de dilatação&lt;/strong&gt;, e distintos entre si, a lâmina se encurva de forma previsível conforme a temperatura varia. O mecanismo funciona como uma válvula automática que altera a &lt;strong&gt;razão entre o fluxo desviado&lt;/strong&gt; pela câmara de derivação e o fluxo que atravessa a câmara de vaporização: quando a temperatura &lt;strong&gt;cai&lt;/strong&gt;, a lâmina se curva de modo a &lt;strong&gt;desviar mais gás para a câmara de vaporização&lt;/strong&gt;, compensando a menor pressão de vapor; quando a temperatura &lt;strong&gt;sobe&lt;/strong&gt;, ela se curva no sentido oposto, encaminhando mais gás pelo bypass.&lt;/p&gt;&lt;p&gt;É importante distinguir esse mecanismo &lt;strong&gt;ativo&lt;/strong&gt; de medidas apenas &lt;strong&gt;passivas&lt;/strong&gt;. Construir o vaporizador com material de alta capacidade térmica e boa condutividade (o cobre dos modelos históricos, o bronze e o aço dos atuais) retarda a queda de temperatura ao funcionar como reservatório de calor, mas apenas &lt;strong&gt;amortece&lt;/strong&gt; a variação. Quem efetivamente mantém a concentração de saída constante ao longo da faixa de temperatura de trabalho é o elemento termocompensador.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Termocompensador construído com material de alto coeficiente de dilatação&lt;/strong&gt;: correta. A lâmina bimetálica redistribui ativamente o fluxo entre as câmaras conforme a temperatura varia.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Vaporizador universal com ajuste automático do borbulhamento&lt;/strong&gt;: incorreta. Os universais não compensam temperatura; essa foi a limitação superada pelos vaporizadores calibrados.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material de alta capacidade térmica para evitar aquecimento&lt;/strong&gt;: incorreta quanto ao papel. Estabiliza a temperatura de forma passiva, sem corrigir a concentração entregue.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Material de alto calor específico&lt;/strong&gt;, incorreta pelo mesmo motivo: amortece a variação térmica, mas não realiza a compensação ativa.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>No primeiro caso de segunda-feira, degradação de anestésicos halogenados em absorvedor dessecado pode produzir monóxido de carbono. A conduta é interromper o agente, oferecer alta FiO2, trocar o circuito/absorvedor e confirmar com gasometria e co-oximetria.</t>
+          <t>&lt;p&gt;O cenário reúne todos os elementos do fenômeno: &lt;strong&gt;primeiro caso da manhã de segunda-feira&lt;/strong&gt;, &lt;strong&gt;desflurano&lt;/strong&gt; e queda de saturação que não responde às medidas convencionais. É o quadro descrito na literatura como &lt;strong&gt;"fenômeno da manhã de segunda-feira"&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O mecanismo começa no fim de semana. Se o fluxo de gases frescos permanece ligado com o aparelho ocioso, o fluxo contínuo através do canister &lt;strong&gt;resseca o absorvedor&lt;/strong&gt; de dióxido de carbono. A base forte presente no absorvedor ressecado degrada os anestésicos halogenados que contêm o grupamento &lt;strong&gt;difluorometil&lt;/strong&gt;, produzindo &lt;strong&gt;monóxido de carbono&lt;/strong&gt;; o &lt;strong&gt;desflurano é o agente que gera as maiores concentrações&lt;/strong&gt;, seguido por enflurano e isoflurano, enquanto halotano e sevoflurano produzem quantidades mínimas.&lt;/p&gt;&lt;p&gt;O diagnóstico é traiçoeiro por uma razão específica: a &lt;strong&gt;oximetria de pulso não distingue carboxiemoglobina de oxiemoglobina&lt;/strong&gt;, de modo que a SpO&lt;sub&gt;2&lt;/sub&gt; subestima a gravidade. Leituras moderadamente reduzidas apesar de pressão parcial arterial de oxigênio adequada devem levantar a suspeita e motivar a &lt;strong&gt;dosagem de carboxiemoglobina por co-oximetria&lt;/strong&gt;. Agrava o quadro o fato de não existir método rotineiro para detectar monóxido de carbono no circuito ou identificar o ressecamento do absorvedor: a &lt;strong&gt;mudança de cor do absorvedor não ocorre&lt;/strong&gt; em resposta ao ressecamento nem à formação de monóxido de carbono. Um sinal indireto útil é a &lt;strong&gt;leitura errônea do analisador de gases&lt;/strong&gt;, que pode indicar enflurano quando se administra desflurano, artefato atribuído ao trifluorometano produzido junto com o monóxido de carbono.&lt;/p&gt;&lt;p&gt;A conduta é, portanto, &lt;strong&gt;interromper a fonte&lt;/strong&gt;, &lt;strong&gt;maximizar a fração inspirada de oxigênio&lt;/strong&gt; (que acelera a dissociação da carboxiemoglobina) e &lt;strong&gt;confirmar por gasometria com co-oximetria&lt;/strong&gt;. Trocar o absorvedor e o circuito completa a medida.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Descontinuar o desflurano, aumentar a FiO&lt;sub&gt;2&lt;/sub&gt; e solicitar gasometria considerando intoxicação por monóxido de carbono&lt;/strong&gt;: correta. Remove a fonte, acelera a eliminação da carboxiemoglobina e confirma o diagnóstico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Administração de inotrópico&lt;/strong&gt;: incorreta. Não interrompe a produção do gás nem corrige a hipóxia tecidual, e a pressão já havia sido restabelecida.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bolus de cristaloide&lt;/strong&gt;: incorreta. A dessaturação não tem origem hipovolêmica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Associar óxido nitroso&lt;/strong&gt;: incorreta e prejudicial. Manteria o desflurano sobre o absorvedor ressecado e reduziria a fração inspirada de oxigênio.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Não existe uma teoria única capaz de explicar integralmente a ação dos anestésicos inalatórios. Eles modulam múltiplos alvos, incluindo receptores GABA_A, glicina, canais de potássio e receptores excitatórios.</t>
+          <t>&lt;p&gt;Esta é uma questão sobre &lt;strong&gt;o estado da ciência&lt;/strong&gt;, e a resposta correta é justamente reconhecer a ausência de uma explicação única. Diferentemente dos anestésicos venosos, cujo alvo principal está bem caracterizado, os agentes inalatórios &lt;strong&gt;não possuem uma teoria unitária&lt;/strong&gt; capaz de explicar seu mecanismo.&lt;/p&gt;&lt;p&gt;Historicamente, o campo partiu de mecanismos &lt;strong&gt;centrados em lipídios&lt;/strong&gt;. A correlação de &lt;strong&gt;Meyer-Overton&lt;/strong&gt; entre potência anestésica e solubilidade em óleo sustentou por décadas a ideia de que a anestesia resultaria de perturbação inespecífica da bicamada lipídica. Esse paradigma foi progressivamente substituído por mecanismos &lt;strong&gt;centrados em proteínas&lt;/strong&gt;, com evidências de que os halogenados se ligam a &lt;strong&gt;bolsões hidrofóbicos&lt;/strong&gt; em canais iônicos e proteínas de membrana.&lt;/p&gt;&lt;p&gt;O que emergiu, porém, não foi um alvo único, mas &lt;strong&gt;múltiplos alvos com redundância&lt;/strong&gt; entre subtipos de canais iônicos: receptores &lt;strong&gt;GABA&lt;sub&gt;A&lt;/sub&gt;&lt;/strong&gt;, receptores de &lt;strong&gt;glicina&lt;/strong&gt;, canais de &lt;strong&gt;potássio de dois poros&lt;/strong&gt;, receptores &lt;strong&gt;NMDA&lt;/strong&gt; e receptores nicotínicos, entre outros. Essa multiplicidade é exatamente o que torna o estudo experimental dos inalatórios mais difícil que o dos venosos: silenciar um alvo isolado raramente abole o efeito.&lt;/p&gt;&lt;p&gt;Paralelamente, consolidou-se a compreensão de que a anestesia não é um estado único, mas um &lt;strong&gt;estado neurofarmacológico composto&lt;/strong&gt;, formado por componentes &lt;strong&gt;separáveis e ao menos parcialmente independentes&lt;/strong&gt; (imobilidade, amnésia, hipnose, atenuação da resposta autonômica), cada um envolvendo mecanismos distintos em regiões diferentes do sistema nervoso central, com potências relativas que variam entre os agentes. A &lt;strong&gt;imobilidade&lt;/strong&gt;, medida pela CAM, é mediada em grande parte na &lt;strong&gt;medula espinhal&lt;/strong&gt;, ao passo que amnésia e hipnose dependem de estruturas supraespinhais.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Inexiste uma teoria única que explique o mecanismo de ação dos agentes inalatórios&lt;/strong&gt;: correta. Há múltiplos alvos moleculares redundantes e componentes anestésicos separáveis, sem explicação unitária.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bloqueio de receptores glutamatérgicos NMDA&lt;/strong&gt;: incorreta como explicação da classe. Participa da ação de óxido nitroso e xenônio, mas não a esgota.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ativação do complexo ionóforo do receptor GABA&lt;/strong&gt;: incorreta como resposta suficiente. É um dos alvos dos halogenados, entre vários outros.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ativação de receptores alfa-2 adrenérgicos pós-sinápticos&lt;/strong&gt;: incorreta. Corresponde ao mecanismo da dexmedetomidina e da clonidina, agentes venosos.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>O etomidato tende a preservar ou prolongar a atividade convulsiva e é usado quando se deseja aumentar a duração da crise na eletroconvulsoterapia. Propofol e benzodiazepínicos têm maior efeito anticonvulsivante.</t>
+          <t>&lt;p&gt;A eletroconvulsoterapia depende de uma &lt;strong&gt;convulsão generalizada de duração adequada&lt;/strong&gt; para ser eficaz, o que coloca o anestesiologista diante de um dilema incomum: o hipnótico precisa produzir inconsciência sem suprimir a convulsão terapêutica. É essa tensão que define o perfil de cada agente.&lt;/p&gt;&lt;p&gt;De um lado estão os fármacos que &lt;strong&gt;elevam o limiar convulsivo&lt;/strong&gt;. &lt;strong&gt;Benzodiazepínicos&lt;/strong&gt; e &lt;strong&gt;barbitúricos&lt;/strong&gt; atuam sobre o receptor GABA&lt;sub&gt;A&lt;/sub&gt;, produzem inibição do sistema nervoso central, aumentam o limiar e &lt;strong&gt;reduzem a duração&lt;/strong&gt; das convulsões, motivo pelo qual alguns autores sugerem suspender benzodiazepínicos de uso prévio ou revertê-los com &lt;strong&gt;flumazenil&lt;/strong&gt; antes da anestesia. O &lt;strong&gt;propofol&lt;/strong&gt; segue a mesma direção: metanálise demonstrou redução significativa da duração da convulsão em comparação ao metoexital, o que o torna útil quando se deseja limitar crises excessivamente longas.&lt;/p&gt;&lt;p&gt;Do outro lado está o &lt;strong&gt;etomidato&lt;/strong&gt;, que se comporta de forma oposta. É reconhecidamente &lt;strong&gt;proconvulsivante&lt;/strong&gt;: produz atividade epileptiforme no eletroencefalograma, com padrão de &lt;strong&gt;ponta-onda&lt;/strong&gt;, e &lt;strong&gt;mioclonias&lt;/strong&gt; que podem generalizar-se em movimentos tônico-clônicos, exatamente o quadro descrito, ocorrendo &lt;strong&gt;antes da succinilcolina&lt;/strong&gt; e, portanto, antes de qualquer estímulo elétrico. O risco de &lt;strong&gt;convulsões prolongadas&lt;/strong&gt; é a razão pela qual se recomenda evitar tanto o etomidato quanto a cetamina em populações de menor limiar convulsivo.&lt;/p&gt;&lt;p&gt;O contexto clínico reforça a suspeita: o paciente é &lt;strong&gt;epiléptico&lt;/strong&gt;, e faz uso de &lt;strong&gt;clozapina&lt;/strong&gt; e &lt;strong&gt;venlafaxina&lt;/strong&gt;, ambos capazes de reduzir o limiar convulsivo, além de &lt;strong&gt;lítio&lt;/strong&gt;, associado a maior risco de estado confusional e de convulsões prolongadas nesse contexto.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Etomidato&lt;/strong&gt;: correto. Agente proconvulsivante, produz padrão de ponta-onda e mioclonias generalizadas antes mesmo do estímulo elétrico, sobretudo em paciente epiléptico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Propofol&lt;/strong&gt;: incorreto. Reduz de forma significativa a duração da convulsão, em vez de desencadeá-la.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cetamina&lt;/strong&gt;: incorreto neste caso. Também deve ser evitada por favorecer convulsões prolongadas, mas não produz o padrão descrito antes do estímulo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midazolam&lt;/strong&gt;: incorreto. Eleva o limiar convulsivo e encurta a convulsão, efeito oposto ao observado.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Na anestesia regional intravenosa, o torniquete é geralmente insuflado a cerca de 250 mmHg no membro superior ou aproximadamente 100 mmHg acima da pressão sistólica. O tempo de insuflação e a dose do anestésico local devem ser rigorosamente controlados.</t>
+          <t>&lt;p&gt;A anestesia regional intravenosa, ou &lt;strong&gt;bloqueio de Bier&lt;/strong&gt;, consiste em excluir o membro da circulação sistêmica por um garrote e preencher seu leito venoso com anestésico local, que difunde retrogradamente até os troncos nervosos. Toda a técnica gira em torno de um único princípio de segurança: &lt;strong&gt;manter o anestésico local confinado ao membro&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Daí decorre a pressão do garrote. Ela precisa &lt;strong&gt;superar a pressão arterial sistólica em 100 a 150 mmHg&lt;/strong&gt;; na prática, os clássicos 250 mmHg no membro superior. Pressão insuficiente permite &lt;strong&gt;vazamento da solução para a circulação sistêmica&lt;/strong&gt;, com risco de toxicidade, e ainda deixa sangramento no campo cirúrgico. O &lt;strong&gt;tempo&lt;/strong&gt; também é limitado: o garrote não deve permanecer além de &lt;strong&gt;60 a 90 minutos&lt;/strong&gt; no membro superior, o que restringe a técnica a &lt;strong&gt;procedimentos curtos&lt;/strong&gt;; cirurgias prolongadas são contraindicação formal. Pacientes diabéticos, idosos e debilitados toleram menos tempo ainda.&lt;/p&gt;&lt;p&gt;Os detalhes técnicos seguem a mesma lógica. Usa-se cateter de &lt;strong&gt;fino calibre, 22 ou 24 gauge&lt;/strong&gt;, puncionado na &lt;strong&gt;extremidade distal&lt;/strong&gt; do membro: a punção mais proximal encontra válvulas venosas que limitam a dispersão distal da solução. O anestésico de escolha é a &lt;strong&gt;lidocaína a 0,5% sem vasoconstritor&lt;/strong&gt;, injetada lentamente para não gerar pressões venosas superiores à do garrote. A liberação intencional ou acidental do garrote é o principal mecanismo de &lt;strong&gt;toxicidade sistêmica&lt;/strong&gt;, cujo tratamento é a emulsão lipídica a 20%.&lt;/p&gt;&lt;p&gt;Quanto à profilaxia antimicrobiana, o raciocínio é direto: o antibiótico deve circular &lt;strong&gt;antes&lt;/strong&gt; da insuflação, pois depois dela o membro está isolado e o fármaco não alcança o tecido operado.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Garrote insuflado em 250 mmHg ou 100 mmHg acima da pressão arterial sistólica&lt;/strong&gt;: correta. Reproduz a faixa recomendada para impedir vazamento sistêmico e garantir campo exangue.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Procedimentos de moderada a longa duração&lt;/strong&gt;: incorreta. O limite de 60 a 90 minutos de garrote restringe a técnica a cirurgias curtas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Antibióticos após o bloqueio&lt;/strong&gt;: incorreta. Com o garrote insuflado, o antibiótico não atinge o membro isolado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Acessos venosos de 18 ou 16 gauge&lt;/strong&gt;: incorreta. Recomenda-se cateter fino, de 22 ou 24 gauge, na porção distal do membro.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A ultrassonografia permite visualizar nervo, agulha, disseminação do anestésico e estruturas adjacentes, aumentando a segurança. Isso reduz risco de punção vascular, pleural e injeção intraneural quando usada adequadamente.</t>
+          <t>&lt;p&gt;A neuroestimulação localiza o nervo de forma &lt;strong&gt;indireta&lt;/strong&gt;: o anestesiologista infere a proximidade a partir da resposta motora evocada, sem qualquer informação sobre o que existe no trajeto da agulha. A ultrassonografia substitui essa inferência por &lt;strong&gt;visualização direta em tempo real&lt;/strong&gt;: do nervo, da agulha, das estruturas vizinhas e da dispersão do anestésico local.&lt;/p&gt;&lt;p&gt;É dessa mudança de natureza que nasce o ganho principal, e ele é de &lt;strong&gt;segurança&lt;/strong&gt;. Ver a agulha permite evitar estruturas que a neuroestimulação simplesmente não detecta: &lt;strong&gt;vasos&lt;/strong&gt;, cuja punção inadvertida é o mecanismo central da &lt;strong&gt;toxicidade sistêmica por anestésico local&lt;/strong&gt;; a &lt;strong&gt;pleura&lt;/strong&gt;, nos bloqueios de parede torácica e de plexo braquial supraclavicular, com risco de pneumotórax; e o próprio &lt;strong&gt;nervo&lt;/strong&gt;, evitando injeção intraneural. A redução do risco de toxicidade sistêmica com o uso da ultrassonografia é o desfecho de segurança mais bem documentado da técnica.&lt;/p&gt;&lt;p&gt;Há um segundo ganho de segurança, indireto: ao confirmar visualmente a dispersão perineural adequada, a ultrassonografia permite &lt;strong&gt;reduzir o volume e a dose total&lt;/strong&gt; de anestésico local necessários, o que diminui a massa de fármaco disponível para absorção sistêmica.&lt;/p&gt;&lt;p&gt;Os demais benefícios existem, mas são condicionais. A &lt;strong&gt;taxa de sucesso&lt;/strong&gt; melhora em alguns bloqueios e é equivalente em outros, já que a neuroestimulação atinge bons resultados em técnicas consagradas. O &lt;strong&gt;tempo de execução&lt;/strong&gt; depende da curva de aprendizado. E a &lt;strong&gt;facilidade&lt;/strong&gt; é discutível: a técnica exige domínio de anatomia sonográfica e coordenação entre a imagem e a agulha, competências que demandam treinamento formal.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Maior segurança para o paciente&lt;/strong&gt;: correta. A visualização direta de agulha, nervo, vasos e pleura previne complicações que a neuroestimulação não permite antecipar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Menor taxa de falha técnica&lt;/strong&gt;: incorreta como principal vantagem. O ganho é variável conforme o bloqueio, e a neuroestimulação já apresenta altas taxas de sucesso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Menor tempo de procedimento&lt;/strong&gt;: incorreta. Resultado inconsistente, dependente da experiência do operador.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Maior facilidade para o anestesiologista&lt;/strong&gt;: incorreta. Exige treinamento específico e coordenação visuomotora que não simplificam a técnica por si.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A paciente apresenta acidose metabólica hiperclorêmica com ânion gap normal. Pela fórmula de Winter, a PaCO2 esperada é próxima de 35 mmHg, compatível com compensação respiratória apropriada e distúrbio simples.</t>
+          <t>&lt;p&gt;O caso pede a interpretação completa de um distúrbio ácido-base, e o caminho é aritmético antes de ser conceitual.&lt;/p&gt;&lt;p&gt;Primeiro, o &lt;strong&gt;ânion gap&lt;/strong&gt;: Na&lt;sup&gt;+&lt;/sup&gt; − (Cl&lt;sup&gt;−&lt;/sup&gt; + HCO&lt;sub&gt;3&lt;/sub&gt;&lt;sup&gt;−&lt;/sup&gt;) = 143 − (115 + 18) = &lt;strong&gt;10 mmol/L&lt;/strong&gt;, portanto &lt;strong&gt;normal&lt;/strong&gt;. Trata-se de uma &lt;strong&gt;acidose metabólica hiperclorêmica&lt;/strong&gt;: perda de bicarbonato compensada por retenção de cloreto para manter a eletroneutralidade. A causa é evidente no enunciado: a &lt;strong&gt;fístula pancreática&lt;/strong&gt; pelo dreno abdominal drena secreção rica em bicarbonato, mecanismo idêntico ao das perdas intestinais baixas e da acidose tubular renal.&lt;/p&gt;&lt;p&gt;Segundo, a &lt;strong&gt;compensação respiratória&lt;/strong&gt;. Pela fórmula de Winter, a PaCO&lt;sub&gt;2&lt;/sub&gt; esperada é 1,5 × 18 + 8 ± 2, isto é, entre &lt;strong&gt;33 e 37 mmHg&lt;/strong&gt;. O valor medido, &lt;strong&gt;34 mmHg&lt;/strong&gt;, cai exatamente nessa faixa: a compensação é &lt;strong&gt;adequada&lt;/strong&gt;, e não há distúrbio respiratório associado. Estamos diante de uma &lt;strong&gt;acidose metabólica pura&lt;/strong&gt; com resposta ventilatória apropriada: se a PaCO&lt;sub&gt;2&lt;/sub&gt; estivesse acima de 37, haveria acidose respiratória concomitante; abaixo de 33, alcalose respiratória associada.&lt;/p&gt;&lt;p&gt;Sobre a &lt;strong&gt;correção do ânion gap&lt;/strong&gt;, o conceito é legítimo e importante: &lt;strong&gt;albumina&lt;/strong&gt; e &lt;strong&gt;fosfato&lt;/strong&gt; são ácidos fracos que compõem parte da carga negativa não medida, e a hipoalbuminemia do paciente crítico &lt;strong&gt;mascara&lt;/strong&gt; ânions não medidos, subestimando o gap. Nesta paciente, porém, a albumina é explicitamente normal, tornando a correção desnecessária.&lt;/p&gt;&lt;p&gt;Por fim, a &lt;strong&gt;curva de dissociação da hemoglobina&lt;/strong&gt;: a alcalinização com bicarbonato de sódio a desloca para a &lt;strong&gt;esquerda&lt;/strong&gt;, aumentando a afinidade da hemoglobina pelo oxigênio e, portanto, &lt;strong&gt;dificultando&lt;/strong&gt; sua liberação tecidual, o inverso do efeito Bohr que ocorre na acidose.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Acidose metabólica pura com PaCO&lt;sub&gt;2&lt;/sub&gt; de 34 mmHg refletindo compensação respiratória&lt;/strong&gt;: correta. A PaCO&lt;sub&gt;2&lt;/sub&gt; esperada situa-se entre 33 e 37 mmHg, e o valor medido está na faixa.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ânion gap aumentado por elevação do cloreto&lt;/strong&gt;: incorreta, e conceitualmente invertida. A hipercloremia é justamente o que mantém o ânion gap normal, aqui igual a 10 mmol/L.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ânion gap corrigido pela albumina e pelo fosfato reduzidos&lt;/strong&gt;: incorreta neste caso. O conceito é válido, mas a albumina desta paciente é normal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bicarbonato desviando a curva para a esquerda e facilitando a liberação de oxigênio&lt;/strong&gt;: incorreta e autocontraditória. O desvio à esquerda dificulta a liberação de oxigênio aos tecidos.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Soluções salinas hipertônicas podem reduzir a pressão intracraniana e o edema cerebral, além de expandir o volume intravascular. Em vários cenários apresentam efeito pelo menos comparável e, em algumas análises, superior ao manitol.</t>
+          <t>&lt;p&gt;O manejo de expansores plasmáticos no paciente neurológico obedece a uma regra que antecede a escolha do produto: o que importa para o cérebro é a &lt;strong&gt;osmolaridade&lt;/strong&gt;, não a oncoticidade. A barreira hematoencefálica é impermeável a solutos pequenos mas permeável à água, de modo que o gradiente &lt;strong&gt;osmótico&lt;/strong&gt; é o que governa o movimento de água entre o plasma e o tecido cerebral.&lt;/p&gt;&lt;p&gt;Daí a proscrição das &lt;strong&gt;soluções hipotônicas&lt;/strong&gt;. Ao equilibrarem-se com o líquido extracelular, elas o tornam hipotônico em relação ao intracelular; a água entra na célula por osmose e produz &lt;strong&gt;edema celular&lt;/strong&gt;, desfecho particularmente indesejável em paciente com hipertensão intracraniana ou massa intracraniana. O Ringer lactato, discretamente hipotônico em relação ao plasma, merece cautela por esse motivo.&lt;/p&gt;&lt;p&gt;Na direção oposta atua a &lt;strong&gt;terapia hiperosmolar&lt;/strong&gt;, com &lt;strong&gt;manitol&lt;/strong&gt; ou &lt;strong&gt;salina hipertônica&lt;/strong&gt;, ambas listadas entre os métodos de redução rápida da pressão intracraniana e do volume cerebral. A salina hipertônica tem características que a favorecem no paciente instável: por não ser diurético osmótico, &lt;strong&gt;expande&lt;/strong&gt; o volume intravascular em vez de depletá-lo, preservando a pressão de perfusão cerebral, e seu coeficiente de reflexão praticamente completo limita o extravasamento para o tecido. O manitol, por sua diurese obrigatória, pode induzir hipovolemia e hipotensão, além de efeito rebote quando a barreira está lesada.&lt;/p&gt;&lt;p&gt;Quanto aos demais produtos, três conceitos: a preocupação com &lt;strong&gt;príons&lt;/strong&gt; recai sobre produtos de origem &lt;strong&gt;bovina&lt;/strong&gt;, isto é, as &lt;strong&gt;gelatinas&lt;/strong&gt;; os &lt;strong&gt;coloides&lt;/strong&gt;, gelatinas e dextranos inclusive, estão entre os agentes mais implicados em &lt;strong&gt;anafilaxia perioperatória&lt;/strong&gt; e interferem na hemostasia; e os &lt;strong&gt;carreadores de oxigênio à base de hemoglobina&lt;/strong&gt; não se firmaram como substitutos seguros da transfusão.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Salina hiperosmolar reduzindo o edema cerebral de forma superior ao manitol&lt;/strong&gt;: correta na conduta. Por expandir o intravascular em vez de depletá-lo, favorece a manutenção da pressão de perfusão cerebral.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Coloides semissintéticos associados à transmissão de príons&lt;/strong&gt;: incorreta. O risco prionico associa-se a produtos de origem bovina, ou seja, às gelatinas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gelatina assegurando expansão em portadores de von Willebrand&lt;/strong&gt;: incorreta. Não trata a doença e, como coloide, agrava a disfunção hemostática.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Carreadores de oxigênio baseados em hemoglobina como alternativa segura&lt;/strong&gt;: incorreta. O desenvolvimento clínico foi limitado por vasoconstrição e eventos cardiovasculares adversos.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>A dabigatrana é inibidor direto da trombina e seu antídoto específico é o idarucizumabe. Em hemorragia intracraniana com cirurgia de emergência, a reversão específica deve ser administrada prontamente.</t>
+          <t>&lt;p&gt;O caso exige uma decisão em minutos, e ela depende de identificar corretamente o &lt;strong&gt;mecanismo do anticoagulante&lt;/strong&gt;. A &lt;strong&gt;dabigatrana&lt;/strong&gt; é um &lt;strong&gt;inibidor direto da trombina&lt;/strong&gt;: não depende de antitrombina, não consome fatores, apenas neutraliza o fator IIa. Reverter esse efeito exige remover a molécula de circulação, e não repor fatores de coagulação.&lt;/p&gt;&lt;p&gt;O antídoto específico é o &lt;strong&gt;idarucizumabe&lt;/strong&gt;, fragmento de anticorpo monoclonal humanizado com afinidade pela dabigatrana cerca de 350 vezes superior à da própria trombina. Ele sequestra o fármaco de forma praticamente irreversível, com &lt;strong&gt;normalização dos testes de coagulação em minutos&lt;/strong&gt;. É a conduta indicada em &lt;strong&gt;hemorragia com risco de vida&lt;/strong&gt; ou diante da necessidade de &lt;strong&gt;cirurgia de emergência&lt;/strong&gt;, exatamente o cenário de um hematoma subdural extenso que precisa de drenagem imediata.&lt;/p&gt;&lt;p&gt;Dois agravantes do caso reforçam a escolha. A &lt;strong&gt;doença renal crônica estágio IV&lt;/strong&gt; é decisiva: a dabigatrana tem &lt;strong&gt;eliminação predominantemente renal&lt;/strong&gt;, de modo que sua meia-vida se prolonga substancialmente e o simples aguardar da depuração não é opção. E a &lt;strong&gt;amiodarona&lt;/strong&gt; inibe a glicoproteína-P, aumentando a exposição à dabigatrana. Vale registrar, ainda, que a dabigatrana é o único anticoagulante oral direto significativamente &lt;strong&gt;dialisável&lt;/strong&gt;, alternativa que a urgência cirúrgica aqui não permite aguardar.&lt;/p&gt;&lt;p&gt;Para os &lt;strong&gt;inibidores do fator Xa&lt;/strong&gt; (rivaroxabana, apixabana, edoxabana), o antídoto específico é o &lt;strong&gt;andexanet alfa&lt;/strong&gt;, e o &lt;strong&gt;complexo protrombínico&lt;/strong&gt; permanece como resgate quando não há antídoto disponível. Reconhecer o mecanismo determina o antídoto.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Idarucizumabe&lt;/strong&gt;: correto. Antídoto específico da dabigatrana, com reversão em minutos, indicado em hemorragia grave ou cirurgia de emergência.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Complexo pró-trombínico&lt;/strong&gt;: incorreto como melhor conduta. É estratégia de resgate na ausência de antídoto específico, cenário que não se aplica aqui.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Concentrado de fibrinogênio&lt;/strong&gt;: incorreto. Trata hipofibrinogenemia e não interfere na inibição direta da trombina.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Concentrado de plaquetas&lt;/strong&gt;: incorreto. A dabigatrana não atua sobre a função plaquetária.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Em procedimentos curtos, a terapia renal substitutiva contínua pode ser temporariamente interrompida se distúrbios como acidose e hipercalemia estiverem controlados. A decisão deve considerar estabilidade volêmica e metabólica.</t>
+          <t>&lt;p&gt;O paciente em terapia de substituição renal chega ao centro cirúrgico com duas ameaças de naturezas opostas, e o manejo consiste em navegar entre elas.&lt;/p&gt;&lt;p&gt;A primeira é o &lt;strong&gt;distúrbio metabólico&lt;/strong&gt;. A doença renal avançada cursa com &lt;strong&gt;acidose metabólica&lt;/strong&gt; e &lt;strong&gt;hipercalemia&lt;/strong&gt;, e é justamente isso que a diálise corrige. São essas duas alterações que carregam risco imediato: a hipercalemia por arritmias graves, a acidose por depressão miocárdica e por potencializar a própria hipercalemia. Uma vez corrigidas, e tratando-se de &lt;strong&gt;procedimento curto&lt;/strong&gt;, é aceitável &lt;strong&gt;suspender temporariamente a terapia dialítica contínua&lt;/strong&gt; durante o ato, retomando-a em seguida; a diálise, afinal, corrige apenas parte das anormalidades da uremia e ela mesma introduz complicações.&lt;/p&gt;&lt;p&gt;A segunda ameaça é o &lt;strong&gt;estado volêmico&lt;/strong&gt;, e o erro mais comum é raciocinar na direção errada. O paciente &lt;strong&gt;recém-dialisado&lt;/strong&gt; acabou de sofrer &lt;strong&gt;ultrafiltração&lt;/strong&gt; e frequentemente está &lt;strong&gt;hipovolêmico&lt;/strong&gt;, com risco de hipotensão grave à indução, porém sem capacidade de excretar excesso de volume, o que torna a sobrecarga igualmente perigosa. A conduta é reposição &lt;strong&gt;cautelosa e titulada&lt;/strong&gt;, guiada por parâmetros dinâmicos, e não expansão ampla. Por isso a avaliação volêmica que interessa é a realizada &lt;strong&gt;após&lt;/strong&gt; a última sessão, com o peso seco atingido e o balanço de ultrafiltração conhecidos.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;diálise peritoneal&lt;/strong&gt;, a conduta é &lt;strong&gt;drenar a cavidade antes&lt;/strong&gt; do procedimento: manter o volume intraperitoneal eleva o diafragma, reduz complacência e capacidade residual funcional e aumenta o risco de regurgitação. Vale lembrar ainda que o &lt;strong&gt;tempo de sangramento&lt;/strong&gt; pode permanecer prolongado mesmo em pacientes bem dialisados, e que a &lt;strong&gt;desmopressina&lt;/strong&gt; e o crioprecipitado são recursos nesse contexto.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Suspensão da hemodiálise contínua em procedimentos curtos, com acidose e hipercalemia corrigidas&lt;/strong&gt;: correta. Resolvidas as alterações de risco imediato, a interrupção temporária é aceitável em cirurgias breves.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Avaliação volêmica antes da última diálise&lt;/strong&gt;: incorreta. O que define o estado de chegada à sala é a avaliação posterior à sessão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter a diálise peritoneal durante o procedimento&lt;/strong&gt;: incorreta. A cavidade deve ser drenada para preservar a mecânica respiratória e reduzir o risco de aspiração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Reposição volêmica ampla no recém-dialisado&lt;/strong&gt;: incorreta. Ele tende à hipovolemia, mas não excreta excessos; a reposição é titulada.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>A gravidez é contraindicação absoluta à litotripsia extracorpórea devido ao risco fetal relacionado às ondas de choque e à radiação associada ao procedimento.</t>
+          <t>&lt;p&gt;A litotripsia extracorpórea por ondas de choque concentra energia acústica sobre o cálculo, e as contraindicações absolutas derivam de duas preocupações: &lt;strong&gt;estruturas que não devem receber a energia&lt;/strong&gt; e &lt;strong&gt;situações em que a fragmentação seria inútil ou perigosa&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;gravidez&lt;/strong&gt; é a contraindicação absoluta mais categórica, pelo risco de &lt;strong&gt;malformações e aborto&lt;/strong&gt; decorrentes tanto das ondas de choque quanto da radiação empregada na localização do cálculo. Em mulheres em idade fértil, a recomendação é afastar ativamente a possibilidade de gestação antes do procedimento. Compõem a mesma lista os &lt;strong&gt;distúrbios da coagulação&lt;/strong&gt; (as ondas produzem lesão parenquimatosa renal e hematoma perirrenal), a &lt;strong&gt;hipertensão arterial não controlada&lt;/strong&gt;, pelo mesmo risco hemorrágico, a &lt;strong&gt;infecção ativa do trato urinário&lt;/strong&gt;, pelo risco de sepse ao liberar bactérias do interior do cálculo fragmentado, e a &lt;strong&gt;obstrução urinária distal&lt;/strong&gt;, que impediria a eliminação dos fragmentos.&lt;/p&gt;&lt;p&gt;É importante separar essas situações das &lt;strong&gt;limitações relativas&lt;/strong&gt;, que exigem planejamento e não proibição. O &lt;strong&gt;marca-passo&lt;/strong&gt; é o exemplo clássico: as ondas de choque podem inibir ou danificar o dispositivo, de modo que se deve avaliar tipo e condição do gerador, &lt;strong&gt;posicionar o paciente com o dispositivo fora do campo&lt;/strong&gt; das ondas e ter disponíveis recursos para reprogramação ou implante de marca-passo externo. Do mesmo modo, &lt;strong&gt;próteses ortopédicas&lt;/strong&gt; pedem apenas cuidado com o posicionamento, e a &lt;strong&gt;obesidade&lt;/strong&gt; impõe dificuldade de focalização e de acoplamento, não vedação ao método.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Gravidez&lt;/strong&gt;: correta. Contraindicação absoluta, pelo risco de malformações e aborto associado às ondas de choque e à radiação de localização.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Paciente portador de marca-passo&lt;/strong&gt;: incorreta. Exige avaliação e posicionamento adequados, não constituindo contraindicação absoluta.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Presença de prótese ortopédica&lt;/strong&gt;: incorreta. Demanda apenas cuidado para mantê-la fora da trajetória das ondas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Obesidade grau III&lt;/strong&gt;: incorreta. Configura dificuldade técnica relativa, sem proibir o procedimento.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>No primeiro estágio do trabalho de parto predomina dor visceral, transmitida principalmente por fibras C que acompanham vias simpáticas até T10-L1. A distensão cervical e as contrações uterinas são os principais estímulos.</t>
+          <t>&lt;p&gt;A dor do trabalho de parto muda de natureza conforme o parto avança, e distinguir os dois estágios é o que permite escolher e ajustar a analgesia.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;primeiro estágio&lt;/strong&gt;, a dor origina-se das &lt;strong&gt;contrações uterinas&lt;/strong&gt; e da &lt;strong&gt;dilatação do colo&lt;/strong&gt;, e tem caráter predominantemente &lt;strong&gt;visceral&lt;/strong&gt;. O estímulo aferente resulta de &lt;strong&gt;isquemia miometrial&lt;/strong&gt; e da &lt;strong&gt;reação inflamatória&lt;/strong&gt; produzidas pelas contrações, e é conduzido a partir da região paracervical pelo &lt;strong&gt;nervo e plexo hipogástricos&lt;/strong&gt; até os segmentos medulares de &lt;strong&gt;T10 a L1&lt;/strong&gt;. Curiosamente, a distensão do corpo uterino em si não parece produzir dor: durante a gestação, as fibras aferentes dessa região sofrem regressão, num processo de denervação do miométrio.&lt;/p&gt;&lt;p&gt;A veiculação se dá por &lt;strong&gt;fibras do tipo C&lt;/strong&gt;, &lt;strong&gt;amielínicas&lt;/strong&gt; e de &lt;strong&gt;condução lenta&lt;/strong&gt;, que respondem pela sensação dolorosa &lt;strong&gt;mal localizada, contínua, surda e intensa&lt;/strong&gt;, tipicamente acompanhada de manifestações neurovegetativas: sudorese, taquicardia, hipertensão. É o oposto das fibras &lt;strong&gt;A-delta&lt;/strong&gt;, finamente mielinizadas e de condução rápida, responsáveis pela dor bem localizada e em pontada. Essa característica explica por que a parturiente do primeiro estágio descreve dor difusa, referida ao abdome inferior e ao dorso, e não um ponto preciso.&lt;/p&gt;&lt;p&gt;Todos esses aferentes fazem sinapse no &lt;strong&gt;corno posterior&lt;/strong&gt; da medula, onde ocorre a primeira modulação do estímulo antes da ascensão pelo trato espinotalâmico. No &lt;strong&gt;segundo estágio&lt;/strong&gt;, acrescenta-se um componente &lt;strong&gt;somático&lt;/strong&gt;, gerado pela distensão do períneo e veiculado pelo &lt;strong&gt;nervo pudendo&lt;/strong&gt; em &lt;strong&gt;S2 a S4&lt;/strong&gt;, razão pela qual o bloqueio precisa ser estendido nessa fase.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Estímulos álgicos transportados preferencialmente por fibras aferentes do tipo C&lt;/strong&gt;: correta. Fibras amielínicas de condução lenta, compatíveis com a dor visceral difusa do primeiro estágio.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Informação predominantemente nociceptiva somática&lt;/strong&gt;: incorreta. O caráter é visceral; o componente somático pertence ao segundo estágio.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Transmissão principalmente aos segmentos L3 a S1&lt;/strong&gt;: incorreta. Os segmentos envolvidos são T10 a L1.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Neurônios do corno anterior responsáveis pela chegada do estímulo ao cérebro&lt;/strong&gt;: incorreta. A sinapse nociceptiva ocorre no corno posterior; o corno anterior é motor.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Segundo o gabarito oficial, a alternativa C é a correta. A morfina pode ser empregada por via sistêmica na fase latente do trabalho de parto, com início de ação em aproximadamente 10 a 20 minutos; seu uso exige avaliação dos efeitos maternos e neonatais. A analgesia com remifentanil requer monitorização contínua, mas não supera a analgesia peridural.</t>
+          <t>&lt;p&gt;A analgesia venosa do trabalho de parto é sempre uma solução de compromisso: todo opioide administrado à mãe atravessa a placenta, e a escolha depende de &lt;strong&gt;quanto tempo a molécula permanece no feto&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;meperidina&lt;/strong&gt; ilustra o pior cenário. Atravessa rapidamente a placenta por difusão passiva, equilibrando-se com a concentração fetal em cerca de seis minutos, e reduz a variabilidade da frequência cardíaca fetal entre 25 e 40 minutos após a administração. O problema decisivo é farmacocinético: a meia-vida materna gira em torno de &lt;strong&gt;3 horas&lt;/strong&gt;, mas a &lt;strong&gt;fetal alcança 18 a 23 horas&lt;/strong&gt;. Some-se a isso a &lt;strong&gt;normeperidina&lt;/strong&gt;, metabólito ativo que também atravessa livremente a placenta e exerce &lt;strong&gt;potente efeito depressor respiratório&lt;/strong&gt;. Está longe, portanto, de ser a opção com menos efeitos adversos.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;morfina&lt;/strong&gt; é opção historicamente empregada por obstetras na &lt;strong&gt;fase latente&lt;/strong&gt;, quando as contrações ainda são irregulares e o objetivo é proporcionar repouso. Sua característica marcante é a &lt;strong&gt;hidrofilia&lt;/strong&gt;, que retarda a passagem pela barreira hematoencefálica e faz o início da analgesia demorar cerca de &lt;strong&gt;10 a 20 minutos&lt;/strong&gt;, latência inaceitável na fase ativa, mas compatível com o ritmo da fase latente.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;fentanil&lt;/strong&gt; é lipossolúvel, com efeito máximo em 3 a 4 minutos e ausência de metabólitos ativos. Nas doses estudadas de 50 a 100 µg por hora, não houve diferença em Apgar, uso de naloxona ou escores neurocomportamentais; a depressão respiratória neonatal correlaciona-se com a &lt;strong&gt;dose total acumulada&lt;/strong&gt;, e não com essa faixa isolada. Já o &lt;strong&gt;remifentanil&lt;/strong&gt; em analgesia controlada pela paciente supera o óxido nitroso e tem menos repercussão fetal que os demais opioides venosos, mas é &lt;strong&gt;inferior à peridural&lt;/strong&gt;, e exige monitorização contínua rigorosa pelo risco de apneia materna.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Morfina usada por obstetras na fase latente, com analgesia iniciando em 10 a 20 minutos&lt;/strong&gt;: correta. A hidrofilia da molécula explica a latência prolongada, tolerável nessa fase do parto.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Remifentanil superior à peridural&lt;/strong&gt;: incorreta. Sua analgesia é inferior à peridural, ainda que exija de fato monitorização intensa.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Meperidina como a de menor incidência de efeitos adversos&lt;/strong&gt;: incorreta. Meia-vida fetal de até 23 horas e metabólito ativo depressor respiratório fazem dela a pior escolha.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Fentanil de 50 a 100 µg/h causando depressão respiratória fetal importante&lt;/strong&gt;: incorreta. Nessa faixa não houve diferença em Apgar, naloxona ou escores neurocomportamentais.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>A distensão abdominal pode aumentar a pressão intra-abdominal e venosa epidural. A aspiração gástrica reduz esse componente e pode diminuir o sangramento venoso durante cirurgia de coluna em decúbito ventral.</t>
+          <t>&lt;p&gt;A questão separa dois grupos de cuidados que costumam ser memorizados juntos: os que previnem &lt;strong&gt;lesão nervosa periférica&lt;/strong&gt; pelo posicionamento e os que reduzem o &lt;strong&gt;sangramento no campo cirúrgico&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O sangramento venoso na cirurgia de coluna vem sobretudo do &lt;strong&gt;plexo venoso epidural&lt;/strong&gt;, e a variável que o governa é a &lt;strong&gt;pressão intra-abdominal&lt;/strong&gt;. No &lt;strong&gt;decúbito ventral&lt;/strong&gt;, se o abdome fica comprimido contra a mesa, a pressão intra-abdominal se eleva, comprime a &lt;strong&gt;veia cava inferior&lt;/strong&gt; e desvia o retorno venoso para o &lt;strong&gt;plexo venoso vertebral&lt;/strong&gt;, que é valvulado de forma incompleta e comunica-se livremente com o sistema ázigo. O resultado é ingurgitação epidural, campo cirúrgico sangrante e maior dificuldade técnica. É por isso que os coxins são posicionados para &lt;strong&gt;deixar o abdome livre&lt;/strong&gt;, e é pelo mesmo raciocínio que a &lt;strong&gt;descompressão gástrica&lt;/strong&gt; por sonda contribui: ao esvaziar o estômago distendido, reduz-se um componente do volume intra-abdominal e, com ele, a pressão transmitida ao sistema venoso.&lt;/p&gt;&lt;p&gt;Os demais cuidados listados pertencem ao domínio da &lt;strong&gt;proteção neural&lt;/strong&gt;. A &lt;strong&gt;abdução do braço inferior a 90 graus&lt;/strong&gt; evita o estiramento do plexo braquial contra a primeira costela e a clavícula. A &lt;strong&gt;flexão do cotovelo inferior a 90 graus&lt;/strong&gt; reduz a pressão sobre o nervo ulnar no túnel cubital, sítio da neuropatia perioperatória mais frequente. São condutas obrigatórias, mas nenhuma delas modifica a pressão venosa epidural.&lt;/p&gt;&lt;p&gt;Já &lt;strong&gt;evitar hipotensão&lt;/strong&gt; é medida voltada à &lt;strong&gt;perfusão&lt;/strong&gt;, da medula espinhal e do nervo óptico, este último no contexto da perda visual pós-operatória em pronação prolongada. Atua sobre o lado arterial da circulação, e não sobre a congestão venosa.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Aspiração gástrica&lt;/strong&gt;: correta. Reduz o volume e a pressão intra-abdominal, diminuindo o desvio de retorno venoso para o plexo epidural.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evitar hipotensão&lt;/strong&gt;: incorreta para o desfecho perguntado. Preserva perfusão medular e ocular, sem reduzir a pressão venosa epidural.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Abdução do braço menor que 90 graus&lt;/strong&gt;: incorreta. Previne lesão do plexo braquial, sem relação com a congestão venosa epidural.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Flexão do cotovelo menor que 90 graus&lt;/strong&gt;: incorreta. Protege o nervo ulnar, também sem efeito sobre a pressão venosa epidural.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>O pneumoperitônio em paciente obesa reduz a capacidade residual funcional e favorece atelectasia, piora da complacência e aumento do shunt. O gabarito oficial indica a alternativa A; porém, a expressão 'diminuição do shunt' parece inconsistente com a fisiologia esperada e merece revisão editorial antes da publicação.</t>
+          <t>&lt;p&gt;A insuflação de CO&lt;sub&gt;2&lt;/sub&gt; a 15 mmHg em uma paciente com índice de massa corporal de 42 kg/m² desencadeia dois conjuntos de alterações simultâneas: &lt;strong&gt;mecânicas&lt;/strong&gt; e &lt;strong&gt;químicas&lt;/strong&gt;. A dessaturação descrita resulta da soma dos dois.&lt;/p&gt;&lt;p&gt;Do lado &lt;strong&gt;mecânico&lt;/strong&gt;, o pneumoperitônio desloca o diafragma cefalicamente e comprime as bases pulmonares. A consequência imediata é a &lt;strong&gt;queda da capacidade residual funcional&lt;/strong&gt;, já reduzida pela obesidade, e a &lt;strong&gt;queda da complacência&lt;/strong&gt; dinâmica, com &lt;strong&gt;elevação da pressão de pico&lt;/strong&gt; nas vias aéreas: a pressão sobe precisamente &lt;em&gt;porque&lt;/em&gt; a complacência cai. O colapso das unidades dependentes gera &lt;strong&gt;atelectasia por compressão&lt;/strong&gt;, criando áreas &lt;strong&gt;perfundidas e não ventiladas&lt;/strong&gt;, isto é, &lt;strong&gt;shunt intrapulmonar&lt;/strong&gt;. É esse shunt que explica uma hipoxemia pouco responsiva ao simples aumento da fração inspirada de oxigênio, e cujo tratamento passa por &lt;strong&gt;manobras de recrutamento e PEEP&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Do lado &lt;strong&gt;químico&lt;/strong&gt;, o CO&lt;sub&gt;2&lt;/sub&gt; é absorvido pelo peritônio e a &lt;strong&gt;hipercapnia&lt;/strong&gt; instala-se em 15 a 30 minutos, com &lt;strong&gt;acidose&lt;/strong&gt;, taquicardia, arritmias e repercussões hemodinâmicas. A acidose &lt;strong&gt;deprime a contratilidade miocárdica&lt;/strong&gt; e, no leito pulmonar, soma-se à hipóxia para produzir &lt;strong&gt;vasoconstrição pulmonar&lt;/strong&gt;, nunca vasodilatação, elevando a resistência vascular pulmonar. A descompressão gástrica por sonda ajuda a reduzir, embora não elimine, o aumento da pressão intra-abdominal.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Formação de atelectasia&lt;/strong&gt;: este é o achado central e correto, pois a compressão diafragmática colapsa unidades alveolares. Registre, porém, que a atelectasia &lt;strong&gt;aumenta&lt;/strong&gt; o shunt intrapulmonar, e não o reduz; é exatamente esse aumento que responde pela queda de saturação apresentada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumento da capacidade residual funcional com queda da capacidade vital&lt;/strong&gt;: incorreta. A capacidade residual funcional diminui pelo deslocamento cefálico do diafragma.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumento da complacência com aumento da pressão de pico&lt;/strong&gt;: incorreta e internamente contraditória. A complacência cai, e é essa queda que eleva a pressão de pico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Acidose hipercápnica com vasodilatação pulmonar&lt;/strong&gt;: parcialmente incorreta. A depressão da contratilidade ocorre, mas o efeito pulmonar da hipercapnia e da hipóxia é vasoconstritor.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Em cirurgia com laser de via aérea, deve-se reduzir a concentração de oxigênio, evitar N2O e proteger o balonete com solução salina, frequentemente corada para detectar ruptura. Essas medidas reduzem o risco de incêndio.</t>
+          <t>&lt;p&gt;A estapedectomia com laser e monitorização do nervo facial impõe três exigências simultâneas, e cada distrator explora o descuido com uma delas.&lt;/p&gt;&lt;p&gt;A primeira é o &lt;strong&gt;risco de fogo na via aérea&lt;/strong&gt;. O laser é uma fonte de ignição em ambiente potencialmente rico em oxigênio, completando a tríade do incêndio. A prevenção é protocolar: manter a &lt;strong&gt;fração de oxigênio em torno de 30% ou menos&lt;/strong&gt;, usando mistura de oxigênio e ar comprimido e &lt;strong&gt;evitando óxido nitroso&lt;/strong&gt;, que é comburente; empregar &lt;strong&gt;tubo traqueal laser-resistente&lt;/strong&gt;; e &lt;strong&gt;insuflar o balonete com solução salina corada&lt;/strong&gt;: o azul de metileno serve de indicador precoce de ruptura, e o líquido extingue a chama caso o balonete seja atingido. Completam o preparo uma seringa de 50 mL de salina pronta para inundar o campo e um tubo traqueal reserva disponível.&lt;/p&gt;&lt;p&gt;A segunda exigência é a &lt;strong&gt;monitorização do nervo facial&lt;/strong&gt;, que impõe uma restrição farmacológica categórica: &lt;strong&gt;não se pode manter bloqueio neuromuscular profundo&lt;/strong&gt;, pois ele abole exatamente a resposta motora que o neuromonitor precisa captar. Após a intubação, o bloqueio deve ser evitado ou plenamente revertido.&lt;/p&gt;&lt;p&gt;A terceira é a &lt;strong&gt;proteção do enxerto&lt;/strong&gt; no ouvido médio. Interessa uma &lt;strong&gt;emergência suave&lt;/strong&gt;, sem tosse nem esforço, porque a manobra de Valsalva pode deslocar a prótese recém-implantada, o que torna a extubação com paciente plenamente desperto e tossindo uma escolha desfavorável. Vale ainda evitar o &lt;strong&gt;óxido nitroso&lt;/strong&gt; por um segundo motivo, específico desta cirurgia: sua difusão para a cavidade do ouvido médio altera a pressão e pode deslocar o enxerto.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Atentar para o risco de fogo na via aérea e insuflar o balonete com solução salina&lt;/strong&gt;: correta. É a medida preventiva protocolar, com a salina corada funcionando como indicador de ruptura e extintor local.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipotensão intraoperatória e extubação com o paciente acordado&lt;/strong&gt;: incorreta. A emergência deve ser suave para proteger a prótese do ouvido médio.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bloqueio neuromuscular profundo e profilaxia de náuseas&lt;/strong&gt;: incorreta na primeira parte. O bloqueio profundo inviabiliza a monitorização do nervo facial.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Mistura O&lt;sub&gt;2&lt;/sub&gt;/ar na proporção 70/30&lt;/strong&gt;: incorreta e invertida. A meta é manter o oxigênio em torno de 30% ou menos.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>A videolaringoscopia pode reduzir força e manipulação em comparação com laringoscopia direta, atenuando resposta hemodinâmica e elevação da pressão intraocular. Ainda assim, deve-se garantir profundidade anestésica adequada.</t>
+          <t>&lt;p&gt;O caso reúne um &lt;strong&gt;olho traumatizado&lt;/strong&gt;, &lt;strong&gt;estômago cheio&lt;/strong&gt; e um paciente &lt;strong&gt;claustrofóbico&lt;/strong&gt;. Cada um desses elementos elimina uma das opções apresentadas, e o que sobra é a técnica que minimiza a elevação da &lt;strong&gt;pressão intraocular&lt;/strong&gt; durante o manejo da via aérea.&lt;/p&gt;&lt;p&gt;O ponto crítico é entender que, no globo com hemorragia vítrea e descolamento de retina, qualquer &lt;strong&gt;elevação abrupta da pressão intraocular&lt;/strong&gt; ameaça a integridade ocular. E o momento de maior risco é a &lt;strong&gt;laringoscopia&lt;/strong&gt;: o estímulo simpático da laringoscopia direta eleva pressão arterial, frequência cardíaca e, junto com elas, a pressão intraocular. A &lt;strong&gt;videolaringoscopia&lt;/strong&gt; exige menor força de elevação e menor deslocamento das estruturas para expor a glote, produzindo &lt;strong&gt;resposta hemodinâmica e pressórica ocular atenuada&lt;/strong&gt; em relação à laringoscopia direta.&lt;/p&gt;&lt;p&gt;A escolha da técnica anestésica também está determinada pelo caso. O paciente &lt;strong&gt;não está em jejum&lt;/strong&gt; (o trauma ocorreu após refeição), o que impõe &lt;strong&gt;anestesia geral com indução em sequência rápida&lt;/strong&gt; e proteção da via aérea, e exclui a sedação com bloqueio peribulbar. Some-se a &lt;strong&gt;claustrofobia&lt;/strong&gt;, incompatível com a imobilidade prolongada sob campos cirúrgicos exigida pelos cuidados monitorados, e o fato de que o bloqueio peribulbar em globo com trauma contuso acrescenta risco.&lt;/p&gt;&lt;p&gt;Por fim, a &lt;strong&gt;emergência&lt;/strong&gt; merece o mesmo cuidado da indução: extubar em plano superficial convida à &lt;strong&gt;tosse&lt;/strong&gt; e ao esforço, com picos de pressão intraocular. O manejo desejável é extubação suave, em plano adequado, eventualmente com lidocaína ou opioide para atenuar o reflexo.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Videolaringoscopia atenuando a elevação da pressão intraocular e as alterações hemodinâmicas&lt;/strong&gt;: correta. Exige menos força de elevação e menor estímulo simpático que a laringoscopia direta.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Etomidato, fentanil e sevoflurano prevenindo delirium&lt;/strong&gt;: incorreta. Nenhum desses agentes tem essa propriedade; a prevenção do delirium é multimodal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cuidados monitorados com bloqueio peribulbar&lt;/strong&gt;: incorreta. O paciente está sem jejum e é claustrofóbico, e o globo traumatizado desaconselha o bloqueio.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Extubação em plano superficial com respiração espontânea&lt;/strong&gt;: incorreta. Favorece tosse e esforço, que elevam bruscamente a pressão intraocular.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>A alta ambulatorial exige acompanhante adulto responsável. Um acompanhante de 16 anos não atende ao critério de segurança, portanto a alta deve ser postergada.</t>
+          <t>&lt;p&gt;A alta após anestesia ambulatorial não se decide por um único parâmetro, mas por um conjunto de critérios que devem estar &lt;strong&gt;simultaneamente&lt;/strong&gt; satisfeitos, e um deles não depende do paciente, mas de quem o levará para casa.&lt;/p&gt;&lt;p&gt;A exigência de &lt;strong&gt;acompanhante adulto e legalmente responsável&lt;/strong&gt; é condição estrutural, não formalidade burocrática. O paciente sai da unidade com &lt;strong&gt;efeitos residuais de anestésicos e opioides&lt;/strong&gt; sobre julgamento, coordenação e memória, ainda que aparente estar lúcido. O acompanhante precisa ser capaz de reconhecer sinais de alarme, tomar decisões clínicas em nome do paciente e acionar o serviço de saúde se necessário, atribuições que um &lt;strong&gt;adolescente de 16 anos não pode assumir&lt;/strong&gt;, por não possuir capacidade civil plena. Nessa situação, a alta deve ser &lt;strong&gt;postergada&lt;/strong&gt; até que um responsável adequado esteja disponível.&lt;/p&gt;&lt;p&gt;Os demais itens integram a rotina de recuperação e não impedem a liberação. Um &lt;strong&gt;episódio isolado de vômito já controlado&lt;/strong&gt; não posterga a alta; o que impede é náusea ou vômito &lt;strong&gt;persistente&lt;/strong&gt; ou incoercível, que compromete a hidratação e a analgesia oral no domicílio. A &lt;strong&gt;dor leve e controlada&lt;/strong&gt; é compatível com a alta, desde que o esquema analgésico prescrito seja factível em casa. E o uso de &lt;strong&gt;rocurônio revertido com neostigmina&lt;/strong&gt; descreve prática corrente: o que postergaria a saída seria evidência clínica de &lt;strong&gt;bloqueio neuromuscular residual&lt;/strong&gt; (fraqueza, dificuldade de deglutição, dessaturação), e não o mero registro da reversão.&lt;/p&gt;&lt;p&gt;Vale reter que os sistemas de pontuação, como o índice de &lt;strong&gt;Aldrete-Kroulik&lt;/strong&gt;, exigem no mínimo &lt;strong&gt;9 de 10&lt;/strong&gt; para a alta da sala de recuperação, mas a liberação para o domicílio acrescenta critérios próprios do regime ambulatorial.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Paciente bem orientado, com acompanhante responsável de 16 anos&lt;/strong&gt;: correta como situação que posterga a alta. O acompanhante precisa ser adulto com capacidade civil plena para assumir a supervisão domiciliar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Um episódio de vômito controlado&lt;/strong&gt;: incorreta. Episódio isolado e resolvido não impede a liberação.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anestesia geral com rocurônio revertido com neostigmina&lt;/strong&gt;: incorreta. É conduta rotineira; apenas o bloqueio residual documentado adiaria a alta.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dor leve controlada&lt;/strong&gt;: incorreta. É compatível com a alta, desde que a analgesia domiciliar esteja assegurada.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Náuseas leves e controladas podem ser compatíveis com alta, desde que o paciente esteja estável, tolerando líquidos conforme protocolo e com sintomas manejáveis em casa. Analgesia deve ser preferencialmente possível por via oral.</t>
+          <t>&lt;p&gt;A alta para o domicílio após anestesia ambulatorial exige critérios mais estritos que a simples saída da sala de recuperação, porque o paciente deixa de estar sob observação profissional. O caso ilustra bem os riscos: a paciente recebeu &lt;strong&gt;morfina 5 mg por via intravenosa&lt;/strong&gt;, opioide de &lt;strong&gt;duração prolongada&lt;/strong&gt;, cujo pico de depressão respiratória pode ocorrer &lt;em&gt;após&lt;/em&gt; a saída da unidade.&lt;/p&gt;&lt;p&gt;Sobre náuseas e vômitos, o critério é de &lt;strong&gt;tolerância proporcional&lt;/strong&gt;. &lt;strong&gt;Náuseas leves&lt;/strong&gt;, se presentes, são &lt;strong&gt;compatíveis com a alta&lt;/strong&gt;, desde que o paciente consiga hidratar-se e utilizar a analgesia prescrita; o que impede a liberação é o vômito &lt;strong&gt;persistente ou incoercível&lt;/strong&gt;, que inviabiliza a ingestão oral e sinaliza risco de desidratação em casa. A ondansetrona administrada cobre boa parte desse risco.&lt;/p&gt;&lt;p&gt;Sobre a dor, o critério é &lt;strong&gt;controle com analgesia oral&lt;/strong&gt;, precisamente porque é isso que existe no domicílio. Um paciente que ainda depende de &lt;strong&gt;analgesia venosa&lt;/strong&gt; não preenche critério de alta, por definição.&lt;/p&gt;&lt;p&gt;Dois pontos administrativos completam o conjunto. A &lt;strong&gt;alta é ato médico&lt;/strong&gt;: a equipe de enfermagem aplica e documenta os escores, mas a decisão e a responsabilidade legal pela liberação são do &lt;strong&gt;anestesiologista&lt;/strong&gt;. E a orientação de segurança cobre cerca de &lt;strong&gt;24 horas&lt;/strong&gt;, período no qual o paciente não deve &lt;strong&gt;dirigir&lt;/strong&gt;, operar máquinas, ingerir álcool ou tomar decisões juridicamente relevantes. É prazo bem superior às 6 horas propostas e compatível com a persistência de efeitos residuais sobre julgamento e coordenação.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Náuseas leves, se estiverem presentes&lt;/strong&gt;: correta. São toleráveis para a alta, desde que não impeçam a hidratação e a analgesia oral.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dor controlada com analgesia oral ou venosa&lt;/strong&gt;: incorreta. A necessidade de via venosa é incompatível com o cuidado domiciliar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Alta dada pela enfermeira responsável&lt;/strong&gt;: incorreta. A alta é ato médico, ainda que a enfermagem aplique e registre os critérios.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evitar dirigir até 6 horas após o procedimento&lt;/strong&gt;: incorreta. A restrição recomendada aproxima-se de 24 horas.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>A analgesia peridural torácica pode atenuar a resposta neuroendócrina ao trauma cirúrgico, reduzindo catecolaminas e cortisol. Também melhora analgesia e função respiratória em pacientes selecionados.</t>
+          <t>&lt;p&gt;A toracotomia é um dos estímulos cirúrgicos mais intensos, e a peridural torácica atua sobre a própria origem da &lt;strong&gt;resposta neuroendócrina ao trauma&lt;/strong&gt;, não apenas sobre a dor percebida.&lt;/p&gt;&lt;p&gt;O mecanismo começa na aferência. O estímulo nociceptivo, conduzido sobretudo por &lt;strong&gt;fibras aferentes esplâncnicas&lt;/strong&gt; cujas terminações alcançam rins e adrenais, desencadeia a liberação de &lt;strong&gt;hormônios contrainsulínicos do estresse&lt;/strong&gt; (GH, cortisol, glucagon, adrenalina, noradrenalina, renina e aldosterona) e de mediadores inflamatórios como interleucinas, fator de necrose tumoral e prostaciclinas. O ambiente metabólico resultante é catabólico, com aumento da &lt;strong&gt;lipólise&lt;/strong&gt; e da &lt;strong&gt;neoglicogênese&lt;/strong&gt;. A magnitude é considerável: em cirurgias abdominais, o cortisol pode elevar-se a valores &lt;strong&gt;dez vezes acima do basal&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Ao bloquear a inervação toracoabdominal, a peridural &lt;strong&gt;interrompe essa cadeia na origem&lt;/strong&gt;, com &lt;strong&gt;diminuição importante das concentrações séricas de cortisol, noradrenalina e adrenalina&lt;/strong&gt;, redução da amplificação da resposta inflamatória e queda da lipólise, efeito que se estende por até duas horas após o término da infusão. Pela quebra da alça de retroalimentação, controla também o pico de hormônios &lt;strong&gt;hipofisários e hipotalâmicos&lt;/strong&gt;: &lt;strong&gt;ADH, prolactina, ACTH e GH&lt;/strong&gt;. Não há, contudo, indício de interferência sobre &lt;strong&gt;hormônios tireoidianos&lt;/strong&gt; ou sobre o glucagon pancreático, o que torna a menção ao TSH improcedente, e reposiciona o cortisol como hormônio adrenal, não hipofisário.&lt;/p&gt;&lt;p&gt;Vale ainda registrar que o bloqueio eficaz da aferência nociceptiva &lt;strong&gt;reduz&lt;/strong&gt; o risco de cronificação da dor pós-toracotomia, ao limitar a sensibilização central, benefício particularmente relevante nesse tipo de incisão.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Diminuição importante das concentrações séricas de cortisol, noradrenalina e adrenalina, reduzindo a magnitude da resposta inflamatória&lt;/strong&gt;: correta. É o efeito nuclear do bloqueio da aferência esplâncnica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bloqueio adequado da aferência aumentando o risco de cronificação da dor&lt;/strong&gt;, incorreta e no sentido inverso: a analgesia eficaz reduz a sensibilização central e a dor persistente.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Controle do pico de TSH e cortisol como hormônios hipofisários&lt;/strong&gt;: incorreta nos hormônios citados. O controle recai sobre ADH, prolactina, ACTH e GH; não há efeito documentado sobre tireoidianos, e o cortisol é adrenal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ausência de evidência científica sobre o benefício da atenuação da resposta ao estresse&lt;/strong&gt;: incorreta. A atenuação é documentada e mensurável.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>O clopidogrel deve ser suspenso geralmente 5 a 7 dias antes de procedimentos com risco de sangramento importante, salvo situação em que o risco trombótico contraindique a interrupção.</t>
+          <t>&lt;p&gt;O paciente será submetido a &lt;strong&gt;ressecção endoscópica de hipófise&lt;/strong&gt;, procedimento em que qualquer sangramento no campo compromete a visualização e no qual um hematoma tem consequências neurológicas graves. Isso torna o &lt;strong&gt;manejo do antiagregante&lt;/strong&gt; a decisão de maior peso.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;clopidogrel&lt;/strong&gt; é um inibidor do receptor &lt;strong&gt;P2Y12&lt;/strong&gt; que se liga de forma &lt;strong&gt;irreversível&lt;/strong&gt; à plaqueta. Como a plaqueta não sintetiza novos receptores, a recuperação da função plaquetária depende da &lt;strong&gt;renovação do pool circulante&lt;/strong&gt;, que se dá à razão aproximada de 10% ao dia. Daí o intervalo mínimo de &lt;strong&gt;cinco dias&lt;/strong&gt; de suspensão antes da cirurgia, quando a reversão da inibição plaquetária é necessária, sendo três dias para ticagrelor, sete para prasugrel e dez para ticlopidina. A ressalva importante é a presença de &lt;strong&gt;stent coronariano recente&lt;/strong&gt;, situação em que a suspensão expõe a trombose de stent e exige decisão compartilhada com o cardiologista.&lt;/p&gt;&lt;p&gt;Os demais fármacos seguem lógicas próprias. O &lt;strong&gt;cetoconazol&lt;/strong&gt;, neste contexto, muito provavelmente não é antifúngico e sim &lt;strong&gt;inibidor da esteroidogênese&lt;/strong&gt;, usado para controlar o hipercortisolismo do adenoma hipofisário, e sua retirada abrupta é indesejável. A &lt;strong&gt;losartana&lt;/strong&gt;, como os demais bloqueadores do sistema renina-angiotensina, é omitida na &lt;strong&gt;manhã&lt;/strong&gt; do procedimento, pelo risco de &lt;strong&gt;hipotensão refratária&lt;/strong&gt; a vasopressores após a indução. E a &lt;strong&gt;insulinoterapia&lt;/strong&gt; é ajustada, não suspensa: a NPH costuma ter a dose reduzida na manhã da cirurgia e a insulina regular é usada como correção guiada por glicemia capilar, evitando tanto hipoglicemia quanto cetose.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Clopidogrel suspenso 5 a 7 dias antes do procedimento&lt;/strong&gt;: correta. O bloqueio irreversível do receptor P2Y12 exige a renovação do pool plaquetário, com intervalo mínimo de cinco dias.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cetoconazol na véspera&lt;/strong&gt;: incorreta. Provável inibidor da esteroidogênese no controle do hipercortisolismo, cuja suspensão abrupta não é recomendada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Insulinoterapia na manhã da cirurgia&lt;/strong&gt;: incorreta. A conduta é ajuste de dose com monitorização glicêmica, não suspensão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Losartana com 72 horas de antecedência&lt;/strong&gt;: incorreta no intervalo. A omissão é da dose da manhã, cerca de 24 horas antes.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>No trauma, o tempo de jejum não é parâmetro confiável porque dor, choque, opioides e resposta metabólica retardam o esvaziamento gástrico. Além disso, pode haver sangue ou secreções deglutidas.</t>
+          <t>&lt;p&gt;O paciente de trauma reúne duas ameaças simultâneas: &lt;strong&gt;via aérea potencialmente difícil&lt;/strong&gt; e &lt;strong&gt;estômago cheio&lt;/strong&gt;, e o manejo consiste em não sacrificar uma em nome da outra.&lt;/p&gt;&lt;p&gt;O primeiro conceito é que o &lt;strong&gt;tempo de jejum não é critério utilizável&lt;/strong&gt; nesse grupo. A &lt;strong&gt;resposta metabólica ao trauma&lt;/strong&gt;, mediada por catecolaminas, dor e opioides, &lt;strong&gt;retarda o esvaziamento gástrico&lt;/strong&gt;, de modo que o estômago pode permanecer cheio horas ou dias após a última refeição. Soma-se a possibilidade de &lt;strong&gt;deglutição de sangue&lt;/strong&gt; em trauma de face e via aérea. A regra prática é considerar &lt;strong&gt;todo politraumatizado como estômago cheio&lt;/strong&gt;, independentemente do relato de jejum.&lt;/p&gt;&lt;p&gt;O segundo conceito diz respeito à &lt;strong&gt;pressão cricoide&lt;/strong&gt;, ou manobra de Sellick, cuja avaliação foi profundamente revista. A evidência atual mostra que ela pode &lt;strong&gt;piorar a visão laringoscópica em até 30% dos pacientes&lt;/strong&gt; sem oferecer prevenção efetiva contra a aspiração; estudo pré-hospitalar demonstrou que &lt;strong&gt;interromper&lt;/strong&gt; a pressão cricoide e a manipulação laríngea &lt;strong&gt;melhorou o sucesso da intubação&lt;/strong&gt;. A conduta apropriada, portanto, é que o intubador &lt;strong&gt;solicite a liberação&lt;/strong&gt; da manobra sempre que suspeitar que ela está dificultando o procedimento; a prioridade absoluta é assegurar a via aérea. Vale registrar ainda que a pressão cricoide &lt;strong&gt;não facilita a ventilação&lt;/strong&gt;; ao contrário, pode comprimir a via aérea e prejudicá-la.&lt;/p&gt;&lt;p&gt;Por fim, diante de paciente &lt;strong&gt;acordado, cooperativo e bem oxigenado&lt;/strong&gt; com preditores de via aérea difícil, a técnica que preserva ventilação e reflexos protetores é a &lt;strong&gt;intubação acordado&lt;/strong&gt;, e não a sequência rápida, que converte uma situação controlada em apneia induzida.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Inadequação de decidir pela conduta com base no tempo de jejum, pela redução do esvaziamento gástrico e pela ingestão de sangue&lt;/strong&gt;: correta. A resposta metabólica ao trauma torna o jejum informado irrelevante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter pressão cricoide durante ventilação sob máscara por facilitar a ventilação e proteger da regurgitação&lt;/strong&gt;: incorreta em ambos os termos. Não facilita a ventilação nem previne de forma efetiva a aspiração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sequência rápida como escolha diante de preditores de via aérea difícil em paciente cooperativo&lt;/strong&gt;: incorreta. A escolha é a intubação com o paciente acordado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter a manobra de Sellick mesmo dificultando a intubação&lt;/strong&gt;: incorreta. Deve ser liberada quando compromete a laringoscopia.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>O ponto B representa fase em que, segundo o gráfico, a intervenção transfusional já não recupera o débito cardíaco de modo sustentado, caracterizando choque irreversível no modelo apresentado.</t>
+          <t>&lt;p&gt;O choque hemorrágico evolui em fases cuja distinção não é acadêmica: define se a reposição volêmica ainda muda o desfecho.&lt;/p&gt;&lt;p&gt;Na fase &lt;strong&gt;compensada&lt;/strong&gt;, a queda do volume circulante é contrabalançada por &lt;strong&gt;vasoconstrição simpática&lt;/strong&gt;, taquicardia, aumento da contratilidade e redistribuição de fluxo para coração e cérebro, à custa dos territórios esplâncnico, muscular e cutâneo. A pressão arterial pode permanecer normal, e é por isso que ela é um marcador tardio e traiçoeiro; os sinais precoces são a &lt;strong&gt;taquicardia&lt;/strong&gt;, o estreitamento da pressão de pulso, a queda do &lt;strong&gt;débito urinário&lt;/strong&gt; e a elevação do &lt;strong&gt;lactato&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Na fase &lt;strong&gt;progressiva&lt;/strong&gt;, a hipoperfusão sustentada instala o &lt;strong&gt;metabolismo anaeróbio&lt;/strong&gt; e a &lt;strong&gt;acidose láctica&lt;/strong&gt;. A acidose deprime a contratilidade miocárdica e reduz a resposta vascular às catecolaminas; a vasoconstrição pré-capilar cede antes da pós-capilar, e o sangue passa a estagnar no leito capilar. Instala-se a &lt;strong&gt;tríade letal&lt;/strong&gt; (&lt;strong&gt;acidose, hipotermia e coagulopatia&lt;/strong&gt;), em que cada elemento agrava os outros.&lt;/p&gt;&lt;p&gt;A fase &lt;strong&gt;irreversível&lt;/strong&gt; define-se por um critério funcional, e não por um valor isolado: é o ponto a partir do qual o &lt;strong&gt;débito cardíaco continua a cair apesar da reposição volêmica adequada&lt;/strong&gt;. Nele já ocorreram lesão endotelial difusa com perda da integridade capilar, disfunção mitocondrial que impede a célula de utilizar o oxigênio ainda que ele seja ofertado, e depressão miocárdica estabelecida. A transfusão deixa de alterar o prognóstico porque o problema deixou de ser de &lt;strong&gt;oferta&lt;/strong&gt; e passou a ser de &lt;strong&gt;utilização&lt;/strong&gt; de oxigênio. É essa transição que justifica a máxima do controle de danos: interromper a hemorragia e restaurar a perfusão &lt;strong&gt;antes&lt;/strong&gt; que a curva atinja esse ponto.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ponto em que o débito cardíaco segue caindo apesar da reposição adequada&lt;/strong&gt;: é o marco da irreversibilidade, quando lesão endotelial, disfunção mitocondrial e depressão miocárdica já estão estabelecidas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pontos situados na fase compensada ou progressiva inicial&lt;/strong&gt;: não caracterizam irreversibilidade, pois nessas etapas a reposição volêmica e o controle da hemorragia ainda revertem o quadro.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>O etomidato oferece maior estabilidade hemodinâmica e reduz o metabolismo cerebral, sendo útil no trauma cranioencefálico com hipotensão. Rocurônio 1,2 mg/kg permite sequência rápida sem os efeitos da succinilcolina.</t>
+          <t>&lt;p&gt;O caso impõe uma equação simultânea. A &lt;strong&gt;pressão de perfusão cerebral&lt;/strong&gt; é a diferença entre a &lt;strong&gt;pressão arterial média&lt;/strong&gt; e a &lt;strong&gt;pressão intracraniana&lt;/strong&gt;. Com PIC de &lt;strong&gt;25 mmHg&lt;/strong&gt; e pressão arterial de &lt;strong&gt;85/50 mmHg&lt;/strong&gt; (pressão arterial média em torno de &lt;strong&gt;62 mmHg&lt;/strong&gt;), a pressão de perfusão cerebral já está em aproximadamente &lt;strong&gt;37 mmHg&lt;/strong&gt;, muito abaixo do alvo. Qualquer queda adicional da pressão arterial converte lesão primária em &lt;strong&gt;lesão secundária&lt;/strong&gt; por isquemia.&lt;/p&gt;&lt;p&gt;Isso elimina de imediato os hipnóticos com perfil vasodilatador. O &lt;strong&gt;propofol&lt;/strong&gt; reduz a taxa metabólica cerebral e a PIC, mas ao custo de &lt;strong&gt;vasodilatação e depressão miocárdica dose-dependentes&lt;/strong&gt;: em paciente já hipotenso e taquicárdico, a queda de pressão arterial média supera qualquer benefício sobre a PIC. O &lt;strong&gt;etomidato&lt;/strong&gt;, ao contrário, mantém &lt;strong&gt;estabilidade hemodinâmica&lt;/strong&gt; notável, preservando a pressão arterial média enquanto reduz o metabolismo cerebral, perfil que o consagrou na indução do politraumatizado com traumatismo cranioencefálico. Sua limitação conhecida é a &lt;strong&gt;supressão adrenocortical&lt;/strong&gt; após dose única, cuja relevância clínica permanece debatida e que não contraindica seu uso nesta situação.&lt;/p&gt;&lt;p&gt;Quanto ao bloqueador neuromuscular, o paciente tem &lt;strong&gt;estômago cheio&lt;/strong&gt; e precisa de &lt;strong&gt;sequência rápida&lt;/strong&gt;. O &lt;strong&gt;rocurônio a 1,2 mg/kg&lt;/strong&gt; oferece condições de intubação em cerca de &lt;strong&gt;60 segundos&lt;/strong&gt;, comparáveis às da succinilcolina, com a vantagem de evitar as fasciculações e a elevação transitória da PIC, e com reversão possível por &lt;strong&gt;sugamadex&lt;/strong&gt; caso a intubação falhe. As alternativas com &lt;strong&gt;vecurônio&lt;/strong&gt;, &lt;strong&gt;cisatracúrio&lt;/strong&gt; ou &lt;strong&gt;midazolam&lt;/strong&gt; falham por lentidão de início (inaceitável quando cada segundo de apneia agrava a hipóxia) e por duração excessiva num paciente que precisará de reavaliação neurológica seriada.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Etomidato com rocurônio 1,2 mg/kg&lt;/strong&gt;: correta. Preserva a pressão arterial média, e portanto a pressão de perfusão cerebral, com condições de intubação rápidas e reversíveis.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cetamina com vecurônio 0,2 mg/kg&lt;/strong&gt;: incorreta pelo bloqueador. Início lento e duração prolongada, incompatíveis com sequência rápida e com reavaliação neurológica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Propofol com succinilcolina 1 mg/kg&lt;/strong&gt;: incorreta pelo hipnótico. A hipotensão adicional reduziria ainda mais uma pressão de perfusão cerebral já criticamente baixa.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midazolam com cisatracúrio 0,3 mg/kg&lt;/strong&gt;: incorreta. Início de ação lento e imprevisível para ambos os fármacos neste cenário.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Prednisona 10 mg/dia pode suprimir o eixo hipotálamo-hipófise-adrenal. Em cirurgia de emergência de estresse moderado, a suplementação pode ser feita com hidrocortisona; a alternativa apresenta dose equivalente de 40 mg.</t>
+          <t>&lt;p&gt;A questão exige duas operações encadeadas: reconhecer o &lt;strong&gt;risco de insuficiência adrenal&lt;/strong&gt; e converter corretamente a dose entre corticosteroides.&lt;/p&gt;&lt;p&gt;A paciente usa &lt;strong&gt;prednisona 10 mg ao dia&lt;/strong&gt; de forma crônica, faixa em que a &lt;strong&gt;supressão do eixo hipotálamo-hipófise-adrenal&lt;/strong&gt; pode ou não estar presente: doses de 5 a 20 mg diários por mais de três semanas situam-se justamente na zona de incerteza. Diante de &lt;strong&gt;abdome agudo oclusivo&lt;/strong&gt; e cirurgia de &lt;strong&gt;emergência&lt;/strong&gt;, não há tempo para investigar o eixo, e a conduta segura é &lt;strong&gt;suplementar&lt;/strong&gt;: um eixo suprimido é incapaz de produzir o surto de cortisol que o estresse cirúrgico demanda, e a consequência é &lt;strong&gt;crise adrenal&lt;/strong&gt;, com hipotensão distributiva refratária a vasopressores.&lt;/p&gt;&lt;p&gt;O fármaco de escolha para a reposição perioperatória é a &lt;strong&gt;hidrocortisona&lt;/strong&gt; (o próprio &lt;strong&gt;cortisol&lt;/strong&gt;), por reproduzir o hormônio endógeno e reunir atividade glicocorticoide &lt;strong&gt;e mineralocorticoide&lt;/strong&gt;, esta última relevante para a manutenção da volemia e do tônus vascular. Convém notar que &lt;strong&gt;dexametasona&lt;/strong&gt; e &lt;strong&gt;betametasona&lt;/strong&gt; têm potência mineralocorticoide &lt;strong&gt;nula&lt;/strong&gt;, o que as torna inadequadas quando se busca reposição fisiológica.&lt;/p&gt;&lt;p&gt;A conversão vem da tabela de equivalências: &lt;strong&gt;20 mg de hidrocortisona equivalem a 5 mg de prednisona&lt;/strong&gt;. Como a paciente usa &lt;strong&gt;10 mg&lt;/strong&gt; de prednisona, sua dose diária corresponde a &lt;strong&gt;40 mg de hidrocortisona&lt;/strong&gt;. As demais opções falham na aritmética (5 mg de prednisolona equivalem a 5 mg de prednisona, 1 mg de dexametasona a cerca de 6,7 mg, e 5 mg de metilprednisolona a cerca de 6,25 mg), todas &lt;strong&gt;abaixo&lt;/strong&gt; da dose de uso contínuo, o que significa reduzir a exposição do paciente justamente no momento de maior demanda.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Hidrocortisona 40 mg&lt;/strong&gt;: correta. Reproduz exatamente o equivalente de 10 mg de prednisona e é o fármaco com perfil glicocorticoide e mineralocorticoide adequado à reposição.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Prednisolona 5 mg&lt;/strong&gt;: incorreta. Equivale a apenas metade da dose diária habitual da paciente.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dexametasona 1 mg&lt;/strong&gt;: incorreta. Corresponde a cerca de 6,7 mg de prednisona e não possui atividade mineralocorticoide.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Metilprednisolona 5 mg&lt;/strong&gt;: incorreta. Equivale a aproximadamente 6,25 mg de prednisona, aquém da dose de uso crônico.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>O bloqueio contínuo do plexo braquial promove analgesia e simpatectomia regional, melhorando fluxo sanguíneo e facilitando microanastomoses no reimplante de dedos.</t>
+          <t>&lt;p&gt;O sucesso de um reimplante digital depende de manter &lt;strong&gt;fluxo sanguíneo através de anastomoses de calibre milimétrico&lt;/strong&gt;, e todas as metas anestésicas convergem para esse objetivo único.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;bloqueio contínuo do plexo braquial&lt;/strong&gt; é a técnica de eleição porque age em três frentes simultâneas. Produz &lt;strong&gt;simpatectomia química&lt;/strong&gt; do membro, com &lt;strong&gt;vasodilatação&lt;/strong&gt; sustentada que aumenta o fluxo distal e reduz o risco de espasmo das anastomoses. Oferece &lt;strong&gt;analgesia prolongada&lt;/strong&gt; no pós-operatório, o que importa porque a dor é potente estímulo simpático e desencadeia vasoconstrição, ameaçando o enxerto. E permite &lt;strong&gt;manter o cateter por dias&lt;/strong&gt;, cobrindo justamente o período crítico de viabilidade vascular; há evidência específica de que o bloqueio contínuo do plexo influencia a &lt;strong&gt;sobrevida dos dígitos reimplantados&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;As metas hemodinâmicas seguem a mesma lógica. Deseja-se &lt;strong&gt;débito cardíaco preservado com resistência vascular periférica baixa&lt;/strong&gt; (vasodilatação, e não vasoconstrição), &lt;strong&gt;normotermia rigorosa&lt;/strong&gt;, já que o frio é estímulo vasoconstritor potente, e &lt;strong&gt;normovolemia&lt;/strong&gt;. Quanto ao hematócrito, busca-se &lt;strong&gt;hemodiluição moderada&lt;/strong&gt;, em torno de &lt;strong&gt;30%&lt;/strong&gt;: reduzir a viscosidade favorece o fluxo em vasos de pequeno calibre, e um hematócrito elevado age no sentido oposto ao desejado.&lt;/p&gt;&lt;p&gt;Vale registrar que &lt;strong&gt;vasoconstritores&lt;/strong&gt; devem ser evitados sempre que possível, e que &lt;strong&gt;heparina e dextrano&lt;/strong&gt;, quando usados, seguem protocolo institucional e momento definido; administrá-los desde o início da cirurgia agrava o sangramento no campo microcirúrgico.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Bloqueio contínuo do plexo braquial facilitando as microanastomoses vasculares&lt;/strong&gt;: correta. Simpatectomia, vasodilatação sustentada e analgesia prolongada favorecem a perfusão do segmento reimplantado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Manter o hematócrito acima de 35%&lt;/strong&gt;: incorreta. O alvo é hemodiluição moderada, próxima de 30%, para reduzir a viscosidade.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aumentar débito cardíaco e resistência vascular periférica&lt;/strong&gt;: incorreta na segunda parte. A vasoconstrição compromete o fluxo distal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Heparina e dextrano desde o início da cirurgia&lt;/strong&gt;: incorreta. Seu uso é protocolar e temporizado, não indiscriminado desde a incisão.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Na cirurgia ortognática, a intubação nasal é frequente; a via submentoniana é alternativa quando é necessário acesso simultâneo ao nariz e à oclusão dentária. O plano de extubação deve priorizar segurança da via aérea.</t>
+          <t>&lt;p&gt;A cirurgia ortognática cria um conflito estrutural: o cirurgião precisa da &lt;strong&gt;cavidade oral inteiramente livre&lt;/strong&gt; para aferir a oclusão dentária, enquanto o anestesiologista precisa de uma via aérea segura no mesmo espaço. A solução está na &lt;strong&gt;rota de intubação&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;intubação nasotraqueal&lt;/strong&gt; é utilizada na quase totalidade dos casos, por oferecer melhor campo cirúrgico, permitir os procedimentos intrabucais e viabilizar a &lt;strong&gt;fixação intermaxilar com normoclusão&lt;/strong&gt;: impossível com um tubo atravessando a linha interoclusal. Empregam-se tubos aramados siliconizados, com balonete de baixa pressão e alto volume, precedidos de vasoconstritor nasal e lubrificação, com calibre não superior a &lt;strong&gt;7,5 mm&lt;/strong&gt; para limitar o traumatismo e o sangramento nasal. Quando a via nasal é inviável (fratura cominutiva de terço médio da face, com risco de penetração iatrogênica na base do crânio), a alternativa é a &lt;strong&gt;intubação submentoniana&lt;/strong&gt; ou submandibular, que libera &lt;strong&gt;ambas&lt;/strong&gt; as rotas da posição interoclusal e favorece o manejo de faces polifraturadas.&lt;/p&gt;&lt;p&gt;Sobre a hemodinâmica, o território é intensamente vascularizado e o sangramento é preocupação central: a conduta consagrada é a &lt;strong&gt;hipotensão arterial induzida&lt;/strong&gt;, e não a manutenção de pressões elevadas.&lt;/p&gt;&lt;p&gt;Por fim, a &lt;strong&gt;emergência&lt;/strong&gt; é o momento de maior risco. Com &lt;strong&gt;fixação intermaxilar&lt;/strong&gt;, a boca não abre: a ventilação sob máscara e qualquer resgate da via aérea tornam-se extremamente difíceis. Por isso a extubação exige paciente &lt;strong&gt;plenamente desperto&lt;/strong&gt;, com reflexos protetores íntegros, após aspiração cuidadosa e inspeção da cavidade oral, e o &lt;strong&gt;alicate corta-fios&lt;/strong&gt; deve permanecer junto ao leito.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Intubação nasal ou submentoniana indicadas&lt;/strong&gt;: correta. Ambas liberam a cavidade oral, permitindo a aferição da oclusão e a fixação intermaxilar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pressão arterial média acima de 80 mmHg&lt;/strong&gt;: incorreta. A recomendação é hipotensão induzida para reduzir o sangramento.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Extubação em plano anestésico&lt;/strong&gt;: incorreta e perigosa. Com a boca bloqueada, o paciente precisa despertar plenamente antes da extubação.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Fixação intermaxilar facilitando a ventilação sob máscara&lt;/strong&gt;, incorreta, e no sentido oposto: ela impede a abertura bucal e dificulta enormemente o resgate da via aérea.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>O tubo de duplo lúmen é geralmente mais rápido de posicionar e permite isolamento e aspiração independentes, mas a seleção do tamanho pode ser difícil. A confirmação broncoscópica permanece recomendada.</t>
+          <t>&lt;p&gt;A escolha do dispositivo de isolamento pulmonar é um exercício de contrapor vantagens e desvantagens, e cada distrator inverte um item conhecido dessa comparação.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;tubo de duplo lúmen&lt;/strong&gt; permanece o padrão. Uma vez posicionado, &lt;strong&gt;raramente exige reposicionamento&lt;/strong&gt;, permite &lt;strong&gt;broncoscopia e aspiração do pulmão isolado&lt;/strong&gt;, aceita &lt;strong&gt;CPAP&lt;/strong&gt; com facilidade, possibilita alternar a ventilação monopulmonar entre os lados e é o &lt;strong&gt;melhor dispositivo para isolamento absoluto&lt;/strong&gt;, situação de hemoptise maciça ou fístula broncopleural. Suas desvantagens são reconhecidas: a &lt;strong&gt;seleção do tamanho é mais difícil&lt;/strong&gt;, a inserção é problemática em via aérea difícil ou traqueia anômala, não é ideal para ventilação pós-operatória prolongada e há risco de trauma laríngeo e brônquico.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;bloqueadores brônquicos&lt;/strong&gt; (Arndt, Cohen, Fuji, EZ-Blocker) invertem esse perfil. A &lt;strong&gt;seleção de tamanho raramente é problema&lt;/strong&gt;, acoplam-se a um tubo traqueal comum, permitem &lt;strong&gt;ventilar durante o posicionamento&lt;/strong&gt; e são mais fáceis de instalar em via aérea difícil e em crianças; ao final, basta recuar o bloqueador para retomar a ventilação bipulmonar. Em contrapartida, &lt;strong&gt;exigem mais tempo&lt;/strong&gt;, &lt;strong&gt;deslocam-se com mais frequência&lt;/strong&gt;, &lt;strong&gt;dependem obrigatoriamente do broncoscópio&lt;/strong&gt; para o posicionamento e oferecem isolamento limitado à direita, pela anatomia do lobo superior direito.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;tubo Univent&lt;/strong&gt; compartilha o perfil dos bloqueadores, com a diferença de alojar o bloqueador em canal próprio, o que consome área de secção e &lt;strong&gt;aumenta a resistência ao fluxo&lt;/strong&gt;. Já a intubação brônquica com &lt;strong&gt;tubo traqueal comum&lt;/strong&gt; encontra sua maior dificuldade à &lt;strong&gt;direita&lt;/strong&gt;, pois o brônquio lobar superior direito origina-se a apenas 1,5 a 2 cm da carina e é facilmente ocluído.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Tubo de duplo lúmen mais fácil de posicionar, porém com seleção de tamanho mais difícil&lt;/strong&gt;: correta. Reproduz exatamente o par vantagem-desvantagem da tabela comparativa.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bloqueador de Cohen dispensando broncoscópio&lt;/strong&gt;: incorreta. O broncoscópio é essencial no posicionamento de qualquer bloqueador brônquico.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Univent com menor resistência ao fluxo que o tubo traqueal regular&lt;/strong&gt;: incorreta. O canal do bloqueador reduz o lúmen efetivo e aumenta a resistência.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Extrema dificuldade de ventilação monopulmonar do pulmão esquerdo com tubo comum&lt;/strong&gt;: incorreta. A dificuldade anatômica recai sobre o lado direito, pela origem precoce do brônquio lobar superior.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Na estenose aórtica grave há aumento importante da pressão sistólica do ventrículo esquerdo e hipertrofia concêntrica, produzindo alça pressão-volume alta e relativamente estreita. A figura A representa esse padrão.</t>
+          <t>&lt;p&gt;A alça &lt;strong&gt;pressão-volume&lt;/strong&gt; do ventrículo esquerdo traduz graficamente o ciclo cardíaco, e cada valvopatia imprime nela uma deformação característica. Reconhecer a da &lt;strong&gt;estenose aórtica grave&lt;/strong&gt; exige acompanhar o que a obstrução fixa à ejeção provoca em cada fase.&lt;/p&gt;&lt;p&gt;A obstrução impõe uma &lt;strong&gt;sobrecarga de pressão&lt;/strong&gt;: para vencer o gradiente transvalvar, o ventrículo precisa gerar pressões sistólicas muito superiores às da aorta. A alça, portanto, torna-se &lt;strong&gt;alta e estreita&lt;/strong&gt;: o segmento de ejeção desloca-se para cima, com pico de pressão sistólica intraventricular bem acima do normal, enquanto o &lt;strong&gt;volume sistólico&lt;/strong&gt;, representado pela largura da alça, permanece normal ou reduzido.&lt;/p&gt;&lt;p&gt;A resposta adaptativa é a &lt;strong&gt;hipertrofia concêntrica&lt;/strong&gt;, com aumento da espessura parietal sem dilatação da cavidade. Essa parede espessa é &lt;strong&gt;rígida&lt;/strong&gt;, o que se manifesta na alça por uma &lt;strong&gt;curva de enchimento diastólico mais inclinada&lt;/strong&gt;: pequenos aumentos de volume produzem grandes elevações de pressão diastólica final. Daí decorrem as consequências que governam a conduta anestésica. O ventrículo torna-se &lt;strong&gt;dependente da contração atrial&lt;/strong&gt;, responsável por até 40% do enchimento; perder o ritmo sinusal é catastrófico. Torna-se &lt;strong&gt;dependente de pré-carga&lt;/strong&gt;, e mal tolera hipovolemia ou venodilatação. Exige &lt;strong&gt;ritmo controlado&lt;/strong&gt;, pois a taquicardia encurta a diástole e compromete tanto o enchimento quanto a perfusão coronariana subendocárdica. E exige &lt;strong&gt;manutenção da resistência vascular sistêmica&lt;/strong&gt;, já que a hipotensão reduz a pressão de perfusão coronariana num miocárdio hipertrofiado e com demanda elevada.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Curva alta e estreita, com pressão sistólica ventricular muito elevada, volume sistólico preservado ou reduzido e enchimento diastólico de inclinação acentuada&lt;/strong&gt;: é o padrão da estenose aórtica grave, decorrente de sobrecarga de pressão e hipertrofia concêntrica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Curvas alargadas, com aumento do volume diastólico final e queda da pressão de ejeção&lt;/strong&gt;: correspondem a sobrecarga de volume, padrão das regurgitações, e não da estenose aórtica.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>A reperfusão com sangue aquecido e normocalêmico auxilia a remoção do excesso de potássio e o retorno da atividade eletromecânica após cardioplegia. A composição e a temperatura variam conforme a estratégia.</t>
+          <t>&lt;p&gt;A cirurgia cardíaca com circulação extracorpórea exige um coração &lt;strong&gt;imóvel e exangue&lt;/strong&gt;, e a cardioplegia é o recurso que torna isso compatível com a sobrevivência do miocárdio.&lt;/p&gt;&lt;p&gt;O agente de parada é sempre o &lt;strong&gt;potássio&lt;/strong&gt;. Elevar a concentração extracelular de potássio &lt;strong&gt;despolariza&lt;/strong&gt; a membrana da célula miocárdica e a mantém nesse estado, impedindo a geração de novos potenciais de ação: o coração para em &lt;strong&gt;diástole&lt;/strong&gt;, flácido, sem consumir energia com contração. O efeito protetor é notável: o consumo miocárdico de oxigênio cai cerca de &lt;strong&gt;97%&lt;/strong&gt;, permitindo que o tecido tolere interrupção completa do fluxo por períodos de &lt;strong&gt;20 a 90 minutos&lt;/strong&gt;, conforme o tipo de cardioplegia. As soluções multidose oferecem 20 a 30 minutos de parada segura entre as doses; as de dose única alcançam de 45 minutos, com del Nido, a 90 minutos, com HTK.&lt;/p&gt;&lt;p&gt;As concentrações seguem um padrão em duas etapas: uma solução de &lt;strong&gt;alto potássio&lt;/strong&gt;, em torno de &lt;strong&gt;20 a 30 mEq&lt;/strong&gt;, para &lt;strong&gt;induzir&lt;/strong&gt; a parada, seguida de uma solução de &lt;strong&gt;baixo potássio&lt;/strong&gt;, aproximadamente &lt;strong&gt;10 mEq&lt;/strong&gt;, para &lt;strong&gt;mantê-la&lt;/strong&gt; após o traçado isoelétrico. A composição varia entre serviços (de sangue enriquecido com potássio a soluções complexas com múltiplos aditivos), mas o potássio é constante.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;retorno da atividade eletromecânica&lt;/strong&gt; é obtido revertendo as duas condições que a suprimiam: a parada é desfeita ao reperfundir as artérias coronárias com &lt;strong&gt;sangue aquecido e normocalêmico&lt;/strong&gt;. O reaquecimento restaura a cinética enzimática e a normalização do potássio repolariza a membrana, permitindo que o potencial de ação volte a se propagar.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Retorno da atividade eletromecânica após infusão de sangue aquecido e normocalêmico nas coronárias&lt;/strong&gt;: correta. Restaura temperatura e potássio, revertendo a despolarização mantida.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Solução cristaloide e hipotônica&lt;/strong&gt;: incorreta. A composição varia, com uso frequente de sangue enriquecido com potássio; a hipotonicidade favoreceria edema celular.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Concentração de potássio de aproximadamente 50 mEq&lt;/strong&gt;: incorreta. A indução usa 20 a 30 mEq, e a manutenção cerca de 10 mEq.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Redução do consumo de oxigênio em 60%&lt;/strong&gt;: incorreta. A queda é da ordem de 97%.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>O Doppler precordial é menos sensível que a ecocardiografia transesofágica, porém é não invasivo, acessível e permite monitorização contínua para detecção de embolia aérea venosa.</t>
+          <t>&lt;p&gt;A embolia aérea venosa exige duas condições simultâneas: um &lt;strong&gt;vaso aberto e não colapsável&lt;/strong&gt; e um &lt;strong&gt;gradiente de pressão&lt;/strong&gt; que favoreça a entrada de ar. Toda a questão se resolve compreendendo esses dois fatores.&lt;/p&gt;&lt;p&gt;Os vasos em causa nas craniotomias são os &lt;strong&gt;seios durais&lt;/strong&gt; e os &lt;strong&gt;canais venosos diploicos&lt;/strong&gt; do osso, que não colapsam quando seccionados porque estão ancorados a estruturas rígidas; permanecem escancarados, prontos a aspirar ar. O gradiente vem da &lt;strong&gt;posição&lt;/strong&gt;: quando o sítio cirúrgico está &lt;strong&gt;acima do nível do átrio direito&lt;/strong&gt;, como nas posições &lt;strong&gt;sentada e de cadeira de praia&lt;/strong&gt;, a coluna hidrostática torna a pressão venosa no campo &lt;strong&gt;subatmosférica&lt;/strong&gt;, e o ar é literalmente sugado. Os números confirmam a magnitude: em cirurgias de fossa posterior na &lt;strong&gt;posição sentada&lt;/strong&gt;, a embolia aérea é detectada por &lt;strong&gt;Doppler precordial em cerca de 40%&lt;/strong&gt; dos pacientes e por &lt;strong&gt;ecocardiografia transesofágica em até 76%&lt;/strong&gt;; nas posições &lt;strong&gt;não sentadas&lt;/strong&gt;, a incidência cai para aproximadamente &lt;strong&gt;12%&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Esses mesmos números respondem à questão da monitorização. A &lt;strong&gt;ecocardiografia transesofágica&lt;/strong&gt; é o método mais sensível, capaz de detectar volumes mínimos e de identificar embolia paradoxal por forame oval patente; o &lt;strong&gt;Doppler precordial&lt;/strong&gt; é menos sensível, mas é &lt;strong&gt;não invasivo, amplamente disponível e permite monitorização contínua&lt;/strong&gt; com sinal audível, combinação que o consagrou como padrão prático nesses procedimentos.&lt;/p&gt;&lt;p&gt;Quanto às medidas preventivas, o raciocínio é simples: tudo o que &lt;strong&gt;fecha os vasos abertos&lt;/strong&gt; reduz o risco. A &lt;strong&gt;cera de osso&lt;/strong&gt; sela os canais diploicos e a &lt;strong&gt;hemostasia rigorosa&lt;/strong&gt; oclui os vasos seccionados: ambas &lt;strong&gt;diminuem&lt;/strong&gt;, e não aumentam, a chance de embolia.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sonar precordial menos sensível que a ecocardiografia transesofágica, porém mais acessível e com monitorização contínua&lt;/strong&gt;: correta. Detecta cerca de 40% dos episódios na posição sentada, contra até 76% da via transesofágica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cera de osso aumentando o risco&lt;/strong&gt;, incorreta e no sentido inverso: ela sela os canais venosos diploicos.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hemostasia rigorosa aumentando a chance&lt;/strong&gt;: incorreta. Ocluir os vasos abertos reduz a via de entrada do ar.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Menor risco na cadeira de praia que no decúbito dorsal&lt;/strong&gt;: incorreta. O gradiente hidrostático da posição elevada aumenta substancialmente o risco.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>A hipotermia reduz a secreção/ação inicial do ADH e promove diurese fria. Também aumenta a solubilidade dos gases, reduz metabolismo e causa resistência à insulina e hiperglicemia.</t>
+          <t>&lt;p&gt;A hipotermia altera praticamente todos os sistemas, e a chave para não errar está em separar a fase &lt;strong&gt;leve&lt;/strong&gt; da progressão para graus mais profundos.&lt;/p&gt;&lt;p&gt;O achado renal é o mais característico da fase inicial. A &lt;strong&gt;vasoconstrição periférica&lt;/strong&gt; desloca sangue para o compartimento central, o que &lt;strong&gt;aumenta o fluxo sanguíneo renal&lt;/strong&gt;. Esse aumento, somado à &lt;strong&gt;redução da atividade do hormônio antidiurético&lt;/strong&gt;, produz a chamada &lt;strong&gt;diurese fria&lt;/strong&gt;, poliúria paradoxal em um paciente que está, na verdade, caminhando para a hipovolemia. À medida que a hipotermia progride, fluxo renal e filtração glomerular caem, mas a diurese pode persistir pela inibição da reabsorção tubular de água. O resultado prático é &lt;strong&gt;depleção de volume circulante&lt;/strong&gt;, agravada pelo edema dos tecidos periféricos lesados, o que exige atenção ao reaquecer o paciente.&lt;/p&gt;&lt;p&gt;No sistema respiratório, a evolução é de &lt;strong&gt;depressão&lt;/strong&gt;: o centro respiratório é progressivamente deprimido, com &lt;strong&gt;hipoventilação&lt;/strong&gt; e tendência à &lt;strong&gt;acidose respiratória&lt;/strong&gt;, o oposto de hiperventilação com alcalose.&lt;/p&gt;&lt;p&gt;No metabolismo dos gases, vale reter o princípio físico: a &lt;strong&gt;solubilidade de um gás em um líquido aumenta quando a temperatura cai&lt;/strong&gt;. É por isso que a interpretação da gasometria no paciente hipotérmico exige decidir entre as abordagens alfa-stat e pH-stat.&lt;/p&gt;&lt;p&gt;No eixo glicêmico, a hipotermia leve cursa com &lt;strong&gt;hipocalemia&lt;/strong&gt; e &lt;strong&gt;hiperglicemia&lt;/strong&gt;, esta última resultante da &lt;strong&gt;redução tanto da sensibilidade quanto da secreção de insulina&lt;/strong&gt;. Com o resfriamento progressivo aparecem acidose, aumento da excreção de sódio e &lt;strong&gt;hipercalemia&lt;/strong&gt;, cuja toxicidade cardíaca se manifesta em limiares mais baixos quanto mais frio o paciente.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Menor atividade inicial do ADH e aumento da diurese&lt;/strong&gt;: correta. É a diurese fria, decorrente do aumento do fluxo renal central somado à queda da atividade do hormônio antidiurético.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hiperventilação e alcalose respiratória&lt;/strong&gt;: incorreta. A hipotermia deprime a ventilação, com tendência à acidose respiratória.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Diminuição da solubilidade sanguínea do O&lt;sub&gt;2&lt;/sub&gt; e do CO&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt;: incorreta. A solubilidade dos gases aumenta com a queda da temperatura.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hipoglicemia e diminuição da sensibilidade à insulina&lt;/strong&gt;: incorreta na glicemia. A redução da sensibilidade e da secreção de insulina produz hiperglicemia.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>O paciente apresenta pelo menos dois critérios clássicos de resposta inflamatória sistêmica: taquicardia, taquipneia, febre e leucocitose. Sem evidência de infecção, o diagnóstico é SIRS secundária ao trauma.</t>
+          <t>&lt;p&gt;Diante de febre e leucocitose em um politraumatizado, o reflexo de suspeitar de infecção é compreensível, mas cronologicamente impossível. A resposta está em reconhecer que a &lt;strong&gt;inflamação sistêmica não exige um agente infeccioso&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;síndrome da resposta inflamatória sistêmica&lt;/strong&gt; é definida pela presença de pelo menos &lt;strong&gt;dois&lt;/strong&gt; dos quatro critérios: &lt;strong&gt;temperatura&lt;/strong&gt; acima de 38 °C ou abaixo de 36 °C; &lt;strong&gt;frequência cardíaca&lt;/strong&gt; superior a 90 batimentos por minuto; &lt;strong&gt;frequência respiratória&lt;/strong&gt; acima de 20 incursões por minuto ou PaCO&lt;sub&gt;2&lt;/sub&gt; abaixo de 32 mmHg; e &lt;strong&gt;leucócitos&lt;/strong&gt; acima de 12.000 ou abaixo de 4.000 por mm³, ou mais de 10% de formas jovens. Este paciente preenche os &lt;strong&gt;quatro&lt;/strong&gt;: temperatura de 38,2 °C, frequência cardíaca de 105 bpm, frequência respiratória de 24 e 13.500 leucócitos.&lt;/p&gt;&lt;p&gt;O gatilho aqui é o próprio &lt;strong&gt;trauma&lt;/strong&gt;. A lesão tecidual extensa libera &lt;strong&gt;padrões moleculares associados a dano&lt;/strong&gt; a partir das células destruídas, que ativam a imunidade inata pelos mesmos receptores acionados por produtos bacterianos. O resultado é ativação das cascatas humorais e celulares, elevação das &lt;strong&gt;citocinas pró-inflamatórias&lt;/strong&gt; e intensificação do recrutamento leucocitário, um quadro clinicamente indistinguível da resposta à infecção, mas de origem &lt;strong&gt;estéril&lt;/strong&gt;. Múltiplas fraturas, lacerações e hematomas extensos são estímulo mais que suficiente.&lt;/p&gt;&lt;p&gt;A distinção conceitual é direta: &lt;strong&gt;sepse&lt;/strong&gt; é disfunção orgânica ameaçadora à vida causada por resposta desregulada a uma &lt;strong&gt;infecção&lt;/strong&gt;; &lt;strong&gt;choque séptico&lt;/strong&gt; acrescenta hipotensão dependente de vasopressor com hiperlactatemia. Sem foco infeccioso, nenhum dos dois se aplica, o que não dispensa a vigilância, já que o politraumatizado é candidato a desenvolver infecção nos dias seguintes.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Síndrome da Resposta Inflamatória Sistêmica&lt;/strong&gt;: correta. Os quatro critérios estão preenchidos, com gatilho traumático estéril e sem foco infeccioso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sepse&lt;/strong&gt;: incorreta. Exige infecção documentada ou suspeita, ausente neste quadro agudo pós-trauma.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Choque séptico&lt;/strong&gt;: incorreta. Requer, além da infecção, hipotensão dependente de vasopressor e hiperlactatemia.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Lesão Pulmonar Aguda&lt;/strong&gt;: incorreta. Demandaria hipoxemia com infiltrados bilaterais de origem não cardiogênica, não descritos.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>No choque hemorrágico há redução da oferta de oxigênio, queda da saturação venosa mista e aumento da variação do volume sistólico em pacientes responsivos a fluidos. A reposição volêmica e o controle da hemorragia são prioritários.</t>
+          <t>&lt;p&gt;O paciente apresenta o quadro clássico de &lt;strong&gt;choque hemorrágico classe III&lt;/strong&gt; (confusão mental, frequência cardíaca de 130 bpm e pressão arterial de 75/50 mmHg), com dois focos hemorrágicos evidentes: &lt;strong&gt;abdome distendido&lt;/strong&gt; e &lt;strong&gt;fratura de pelve&lt;/strong&gt;. Reconhecer o padrão hemodinâmico correto é o que separa a conduta salvadora da conduta iatrogênica.&lt;/p&gt;&lt;p&gt;A hemorragia reduz o &lt;strong&gt;volume intravascular&lt;/strong&gt; e, com ele, a &lt;strong&gt;pré-carga&lt;/strong&gt;. Pelo mecanismo de Frank-Starling, cai o &lt;strong&gt;volume sistólico&lt;/strong&gt; e cai o &lt;strong&gt;índice cardíaco&lt;/strong&gt;, apesar da taquicardia compensatória. Como a &lt;strong&gt;oferta de oxigênio&lt;/strong&gt; é o produto do débito cardíaco pelo conteúdo arterial de oxigênio, e ambos estão reduzidos (o débito pela hipovolemia, o conteúdo pela perda de hemoglobina), a &lt;strong&gt;oferta tecidual de oxigênio despenca&lt;/strong&gt;. Os tecidos respondem extraindo mais oxigênio do sangue que lhes chega, e a consequência mensurável é a &lt;strong&gt;queda da saturação venosa mista&lt;/strong&gt;, marcador precoce e sensível do desequilíbrio entre oferta e consumo. O metabolismo anaeróbio resultante produz &lt;strong&gt;hiperlactatemia&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;variação do volume sistólico&lt;/strong&gt; é a variável que fecha o raciocínio. Em ventilação mecânica, as oscilações de pressão intratorácica modulam o retorno venoso; quando o ventrículo opera na porção &lt;strong&gt;ascendente&lt;/strong&gt; da curva de Frank-Starling (isto é, quando está hipovolêmico), essa modulação se traduz em &lt;strong&gt;grande variação do volume sistólico&lt;/strong&gt; batimento a batimento. Um valor elevado identifica o paciente &lt;strong&gt;responsivo a volume&lt;/strong&gt;, e a conduta é &lt;strong&gt;reposição volêmica&lt;/strong&gt;, com hemoderivados e controle da fonte de sangramento.&lt;/p&gt;&lt;p&gt;Convém rejeitar com firmeza os padrões alternativos. Débito elevado com resistência baixa caracteriza o &lt;strong&gt;choque distributivo&lt;/strong&gt;; pressões de enchimento elevadas caracterizam o &lt;strong&gt;cardiogênico&lt;/strong&gt;. Nenhum deles descreve este paciente, e tratar hipovolemia com vasodilatador ou apenas com vasopressor agrava a isquemia tecidual.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Oferta de oxigênio reduzida, variação de volume sistólico aumentada, saturação venosa mista reduzida; administração de volume&lt;/strong&gt;: correta. É o perfil hipovolêmico responsivo a volume, com a conduta que trata a causa.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Débito cardíaco elevado com resistência vascular reduzida e vasodilatador&lt;/strong&gt;: incorreta e perigosa. Descreve choque distributivo, e o vasodilatador aprofundaria a hipotensão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pressão de oclusão da artéria pulmonar aumentada com administração de oxigênio&lt;/strong&gt;: incorreta. As pressões de enchimento estão baixas, e oxigênio isolado não corrige a perda volêmica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Índice cardíaco normal com pressão de oclusão aumentada e vasopressor&lt;/strong&gt;: incorreta em todos os termos. O índice está reduzido, as pressões de enchimento baixas, e o vasopressor apenas mascara a hipovolemia.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Estratégias poupadoras de opioides reduzem sedação, náusea, atraso do esvaziamento gástrico e depressão respiratória, fatores que podem contribuir para broncoaspiração no idoso.</t>
+          <t>&lt;p&gt;O paciente idoso concentra vulnerabilidades para &lt;strong&gt;broncoaspiração&lt;/strong&gt;: reflexos protetores de via aérea atenuados, esvaziamento gástrico mais lento, menor tônus do esfíncter esofágico inferior, prevalência elevada de disfagia e sensibilidade aumentada a fármacos depressores. A questão pede a medida que efetivamente reduz esse risco.&lt;/p&gt;&lt;p&gt;A resposta está na farmacologia. Os &lt;strong&gt;opioides&lt;/strong&gt; agem por três vias que convergem para o mesmo desfecho: &lt;strong&gt;deprimem os reflexos protetores&lt;/strong&gt; de via aérea (tosse e deglutição), &lt;strong&gt;retardam o esvaziamento gástrico&lt;/strong&gt;, mantendo conteúdo residual no estômago, e &lt;strong&gt;deprimem o nível de consciência&lt;/strong&gt;, comprometendo a capacidade de proteger a via aérea. No idoso, cuja sensibilidade a esses fármacos é substancialmente maior, doses convencionais produzem efeito desproporcional. As &lt;strong&gt;estratégias poupadoras de opioides&lt;/strong&gt; (analgesia multimodal com dipirona ou paracetamol, anti-inflamatórios quando permitido, e sobretudo &lt;strong&gt;bloqueios regionais&lt;/strong&gt;) oferecem controle da dor sem esse custo. Os anexos, aliás, listam nominalmente o &lt;strong&gt;uso de opioides&lt;/strong&gt; e o de &lt;strong&gt;bloqueadores neuromusculares&lt;/strong&gt; entre os fatores relacionados ao manejo anestésico que aumentam complicações respiratórias na recuperação.&lt;/p&gt;&lt;p&gt;As demais opções falham por razões distintas. A &lt;strong&gt;metoclopramida&lt;/strong&gt; tem fundamento fisiológico, mas efeito isolado modesto e sem eficácia estabelecida sobre o desfecho. O &lt;strong&gt;citrato de sódio&lt;/strong&gt; é antiácido &lt;strong&gt;não particulado&lt;/strong&gt; de ação curta; sua função é elevar o pH do conteúdo gástrico já presente, e deve ser administrado &lt;strong&gt;imediatamente antes da indução&lt;/strong&gt;; duas horas antes, o efeito já se dissipou. E os &lt;strong&gt;bloqueadores de ação intermediária&lt;/strong&gt; são justamente os mais implicados em &lt;strong&gt;bloqueio residual&lt;/strong&gt;, que compromete a musculatura faríngea e é fator de risco reconhecido para aspiração; o que protege não é a escolha da classe, mas a &lt;strong&gt;monitorização quantitativa&lt;/strong&gt; e a reversão adequada.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Estratégias poupadoras de opioides para analgesia&lt;/strong&gt;: correta. Preservam reflexos protetores, motilidade gástrica e nível de consciência no paciente mais sensível a essa classe.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Metoclopramida intravenosa no pré-anestésico&lt;/strong&gt;: incorreta. Efeito isolado modesto, sem eficácia demonstrada sobre o risco de aspiração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Citrato de sódio oral duas horas antes&lt;/strong&gt;: incorreta no momento da administração. Deve ser dado imediatamente antes da indução.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bloqueadores neuromusculares de ação intermediária&lt;/strong&gt;: incorreta. São os mais associados a bloqueio residual, que aumenta o risco de aspiração.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Pela regra 4-2-1: 4 mL/kg/h para os primeiros 10 kg, 2 mL/kg/h para os 10 kg seguintes e 1 mL/kg/h para os 5 kg restantes. Total: 40 + 20 + 5 = 65 mL/h.</t>
+          <t>&lt;p&gt;A fórmula de &lt;strong&gt;Holliday e Segar&lt;/strong&gt;, conhecida como &lt;strong&gt;regra 4-2-1&lt;/strong&gt;, estima a necessidade hídrica de manutenção horária a partir do peso, e sua estrutura é &lt;strong&gt;escalonada&lt;/strong&gt;: cada faixa de peso recebe uma taxa diferente, e as parcelas se somam.&lt;/p&gt;&lt;p&gt;A lógica por trás dos degraus é metabólica: a necessidade de água acompanha o &lt;strong&gt;gasto energético&lt;/strong&gt;, que não cresce linearmente com o peso. Crianças pequenas têm taxa metabólica por quilograma muito superior à de crianças maiores, e por isso os primeiros quilos consomem proporcionalmente mais água.&lt;/p&gt;&lt;p&gt;A aplicação é direta: &lt;strong&gt;4 mL/kg/h&lt;/strong&gt; para os &lt;strong&gt;primeiros 10 kg&lt;/strong&gt;, &lt;strong&gt;2 mL/kg/h&lt;/strong&gt; para os &lt;strong&gt;10 kg seguintes&lt;/strong&gt; (ou seja, de 10 a 20 kg) e &lt;strong&gt;1 mL/kg/h&lt;/strong&gt; para &lt;strong&gt;cada quilo acima de 20 kg&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Para uma criança de &lt;strong&gt;25 kg&lt;/strong&gt;, o cálculo se decompõe assim: os primeiros 10 kg contribuem com 10 × 4 = &lt;strong&gt;40 mL/h&lt;/strong&gt;; a faixa dos 10 aos 20 kg contribui com 10 × 2 = &lt;strong&gt;20 mL/h&lt;/strong&gt;; e os 5 kg restantes, acima de 20 kg, contribuem com 5 × 1 = &lt;strong&gt;5 mL/h&lt;/strong&gt;. A soma é &lt;strong&gt;65 mL/h&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Vale registrar que essa taxa representa a &lt;strong&gt;manutenção&lt;/strong&gt;, e não a reposição total no perioperatório. A ela somam-se o déficit acumulado pelo jejum, as perdas para o terceiro espaço conforme o porte cirúrgico e as perdas sanguíneas, embora a prática contemporânea tenha abandonado o jejum prolongado e a reposição generosa dos antigos protocolos, favorecendo a ingestão de líquidos claros até duas horas antes do procedimento.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;65 mL/h&lt;/strong&gt;: correta. Corresponde a 40 mL pelos primeiros 10 kg, 20 mL pela faixa de 10 a 20 kg e 5 mL pelos 5 kg excedentes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;45 mL/h&lt;/strong&gt;: incorreta. Omite a faixa intermediária de 2 mL/kg/h.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;50 mL/h&lt;/strong&gt;: incorreta. Resulta de aplicar uma taxa única a todo o peso, ignorando o escalonamento.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;60 mL/h&lt;/strong&gt;: incorreta. Deixa de somar 1 mL/kg/h referente aos 5 kg acima de 20 kg.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>O fentanil intranasal tem início rápido e é útil em procedimentos menores ou analgesia de resgate quando ainda não há acesso venoso. Exige monitorização e cálculo cuidadoso da dose.</t>
+          <t>&lt;p&gt;A analgesia pós-operatória pediátrica organiza-se em torno de dois princípios: &lt;strong&gt;multimodalidade&lt;/strong&gt;, para reduzir a exposição a opioides, e &lt;strong&gt;vias de administração adaptadas à criança&lt;/strong&gt;, que frequentemente chega ao centro cirúrgico sem acesso venoso e para quem a punção é fonte adicional de sofrimento.&lt;/p&gt;&lt;p&gt;É nesse contexto que a &lt;strong&gt;via nasal&lt;/strong&gt; se destaca. A mucosa nasal é ricamente vascularizada e drena diretamente para a circulação sistêmica, &lt;strong&gt;evitando o metabolismo de primeira passagem&lt;/strong&gt; hepático. O &lt;strong&gt;fentanil intranasal&lt;/strong&gt;, na dose aproximada de &lt;strong&gt;2 µg/kg&lt;/strong&gt;, mostrou-se tão eficaz quanto a morfina intramuscular ou intravenosa no controle da dor pós-operatória e do delirium de emergência em crianças submetidas a miringotomia bilateral, e a analgesia controlada com fentanil intranasal equivale à via intravenosa. É, portanto, um recurso valioso em &lt;strong&gt;procedimentos menores sem acesso venoso estabelecido&lt;/strong&gt;: a lipossolubilidade do fármaco garante início rápido, compatível com a necessidade clínica.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;anti-inflamatórios não esteroidais&lt;/strong&gt; merecem correção conceitual: têm segurança e eficácia bem estabelecidas em pediatria e constituem pilar da analgesia multimodal, permitindo reduzir substancialmente a dose de opioides e seus efeitos adversos.&lt;/p&gt;&lt;p&gt;Quanto à &lt;strong&gt;anestesia regional em regime ambulatorial&lt;/strong&gt;, a orientação aos pais é decisiva e vai na direção oposta à proposta: o bloqueio regride, e a dor pode retornar &lt;strong&gt;abruptamente&lt;/strong&gt;, com frequência durante a noite. A instrução correta é &lt;strong&gt;iniciar o analgésico oral de forma programada, antes que o bloqueio ceda&lt;/strong&gt;, e não aguardar o surgimento da dor.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Fentanil nasal útil em procedimentos menores quando não há acesso intravenoso&lt;/strong&gt;: correta. Eficácia comparável às vias intramuscular e intravenosa, com início rápido e sem necessidade de punção.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evitar morfina como analgésico único após fentanil&lt;/strong&gt;: incorreta. Não há proscrição; o cuidado é de titulação e vigilância pelos efeitos depressores somados.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anti-inflamatórios não esteroidais com pequena segurança e eficácia em pediatria&lt;/strong&gt;: incorreta. São eficazes, seguros e centrais na estratégia poupadora de opioides.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dispensar analgésicos orais após anestesia regional em regime ambulatorial&lt;/strong&gt;: incorreta e potencialmente danosa. O analgésico oral deve ser iniciado antes da regressão do bloqueio.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>A recuperação de estágio III corresponde à recuperação tardia, quando o paciente já consegue andar, alimentar-se e apresenta sintomas controlados. A recuperação psicomotora completa pode ocorrer apenas mais tarde.</t>
+          <t>&lt;p&gt;A recuperação da anestesia não é um evento, mas um &lt;strong&gt;processo em quatro estágios&lt;/strong&gt;, cada um com critérios clínicos próprios. Confundi-los é o erro que a questão explora, e a maneira de não errar é ancorar cada estágio no seu &lt;strong&gt;marco funcional&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;estágio I&lt;/strong&gt; é o &lt;strong&gt;despertar da anestesia&lt;/strong&gt;. Seus critérios são elementares: o paciente &lt;strong&gt;responde a comandos verbais&lt;/strong&gt;, &lt;strong&gt;mantém as vias aéreas pérvias&lt;/strong&gt;, sustenta saturação acima de 94% com ou sem suplementação de oxigênio, e não apresenta complicações anestésicas ou cirúrgicas relevantes. É o momento da extubação ou da retirada da máscara laríngea e do transporte.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;estágio II&lt;/strong&gt; é a &lt;strong&gt;recuperação precoce&lt;/strong&gt;, e acrescenta exigências: &lt;strong&gt;sinais vitais estáveis&lt;/strong&gt;, saturação normal &lt;strong&gt;em ar ambiente&lt;/strong&gt;, &lt;strong&gt;retorno dos reflexos de proteção&lt;/strong&gt; (tosse e deglutição), paciente &lt;strong&gt;acordado e alerta&lt;/strong&gt;, ausência de sangramento e &lt;strong&gt;índice de Aldrete acima de 9&lt;/strong&gt;. Note que estar acordado e alerta é conquista &lt;em&gt;do&lt;/em&gt; estágio II, e não sua condição de entrada.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;estágio III&lt;/strong&gt; é a &lt;strong&gt;recuperação intermediária&lt;/strong&gt;, correspondente à &lt;strong&gt;alta anestésica&lt;/strong&gt;. Aqui o paciente preenche os critérios de alta estabelecidos, &lt;strong&gt;levanta e anda sem auxílio&lt;/strong&gt;, está &lt;strong&gt;livre de complicações e efeitos colaterais&lt;/strong&gt;, e a realimentação foi bem tolerada. É neste estágio que ocorre a liberação para o domicílio no regime ambulatorial.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;estágio IV&lt;/strong&gt; é a &lt;strong&gt;recuperação tardia&lt;/strong&gt; e transcorre &lt;strong&gt;fora do hospital&lt;/strong&gt;: as funções psicomotoras retornam ao estado pré-operatório, assim como memória, funções cognitivas, concentração, discriminação e razão. É o período em que se aplicam as restrições para dirigir e tomar decisões relevantes.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Estágio III com o paciente apto a levantar e andar sem ajuda, sem efeitos colaterais e com realimentação bem-sucedida&lt;/strong&gt;: correta. Corresponde à recuperação intermediária e à alta anestésica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Estágio I com estabilidade hemodinâmica e respiratória na sala de recuperação&lt;/strong&gt;: incorreta. O estágio I define-se pelo despertar; a estabilidade dos sinais vitais pertence ao estágio II.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Estágio II iniciando com o paciente acordado e alerta&lt;/strong&gt;: incorreta. Esse é um critério de conclusão do estágio II, e a alta da recuperação corresponde ao estágio III.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Estágio IV como momento da alta para o domicílio&lt;/strong&gt;: incorreta. A alta ocorre no estágio III; o estágio IV é a recuperação tardia, já em casa.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Serviços de dor aguda melhoram padronização, educação, segurança e qualidade assistencial, com benefícios para paciente, instituição e sociedade. O impacto em custos depende da estrutura e do modelo de implantação.</t>
+          <t>&lt;p&gt;Um &lt;strong&gt;serviço de tratamento de dor aguda&lt;/strong&gt; é uma estrutura organizacional, e não um conjunto de técnicas. Compreender essa distinção resolve a questão.&lt;/p&gt;&lt;p&gt;O retorno que justifica sua existência distribui-se em &lt;strong&gt;três níveis&lt;/strong&gt;. No nível &lt;strong&gt;individual&lt;/strong&gt;, o paciente obtém analgesia sistematicamente avaliada e titulada, com menor incidência de dor mal controlada, mobilização mais precoce, redução de complicações respiratórias e tromboembólicas e menor risco de &lt;strong&gt;cronificação da dor&lt;/strong&gt; pós-operatória. No nível &lt;strong&gt;institucional&lt;/strong&gt;, a existência de protocolos padronizados reduz a variabilidade de conduta, gera indicadores mensuráveis de qualidade, cria um canal formal de manejo de complicações e agrega valor à assistência; a analgesia adequada é, aliás, componente com forte grau de recomendação nos protocolos de recuperação acelerada. No nível &lt;strong&gt;social&lt;/strong&gt;, há retorno mais amplo: retorno mais rápido às atividades laborais, menor consumo crônico de analgésicos e redução da carga de dor persistente.&lt;/p&gt;&lt;p&gt;Três equívocos frequentes merecem correção. O serviço de dor aguda &lt;strong&gt;não se confunde com o serviço de anestesia regional&lt;/strong&gt;: os bloqueios são um dos recursos disponíveis, ao lado da analgesia sistêmica multimodal, dos protocolos institucionais, da avaliação sistemática e da educação da equipe. Sua &lt;strong&gt;viabilidade não é uniforme&lt;/strong&gt; entre instituições: depende de porte, perfil cirúrgico, volume de pacientes e disponibilidade de pessoal, de modo que o modelo precisa ser dimensionado a cada realidade. E a &lt;strong&gt;redução de custos&lt;/strong&gt; não é achado consistente: há investimento inicial em pessoal e estrutura, e o retorno econômico é variável, ainda que o benefício clínico seja bem estabelecido.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Serviços valiosos por fornecerem retorno nos níveis individual, institucional e social&lt;/strong&gt;: correta. É a justificativa que sustenta sua implantação.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Mesma definição e finalidade do serviço de anestesia regional&lt;/strong&gt;: incorreta. A anestesia regional é uma das técnicas empregadas, não o escopo do serviço.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Mesma viabilidade em instituições de diferentes portes&lt;/strong&gt;: incorreta. A implantação depende de porte, perfil e recursos disponíveis.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Associação com redução dos custos assistenciais&lt;/strong&gt;: incorreta como afirmação geral. O retorno econômico é variável; o benefício consistente é clínico.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>O Inventário Breve da Dor é curto, de fácil aplicação e validado em diferentes idiomas e culturas. Avalia intensidade da dor e interferência nas atividades diárias.</t>
+          <t>&lt;p&gt;Os instrumentos de avaliação da dor dividem-se em &lt;strong&gt;unidimensionais&lt;/strong&gt; (escala visual analógica, escala numérica), que capturam apenas a &lt;strong&gt;intensidade&lt;/strong&gt;, e &lt;strong&gt;multidimensionais&lt;/strong&gt;, que acrescentam domínios afetivos, sensoriais e funcionais. Entre estes últimos figuram o &lt;strong&gt;questionário de McGill&lt;/strong&gt;, o &lt;strong&gt;Inventário Breve da Dor&lt;/strong&gt; em sua forma abreviada e as medidas do sistema PROMIS.&lt;/p&gt;&lt;p&gt;A vantagem distintiva do &lt;strong&gt;Inventário Breve da Dor de Wisconsin&lt;/strong&gt; está no equilíbrio entre &lt;strong&gt;profundidade e simplicidade&lt;/strong&gt;. Ele avalia a intensidade da dor em quatro momentos (pior, menor, média e atual) e, sobretudo, mede a &lt;strong&gt;interferência da dor&lt;/strong&gt; em domínios funcionais concretos: atividade geral, humor, capacidade de caminhar, trabalho, relações interpessoais, sono e prazer de viver. Essa combinação captura um espectro amplo de informação sem a extensão e a complexidade lexical do questionário de McGill.&lt;/p&gt;&lt;p&gt;É justamente essa simplicidade que sustenta a característica mais valiosa do instrumento: a &lt;strong&gt;validade transcultural&lt;/strong&gt;. Como o inventário se apoia em &lt;strong&gt;números e em domínios funcionais universais&lt;/strong&gt;, e não em uma lista extensa de descritores verbais carregados de nuance idiomática (o ponto que torna a tradução do McGill notoriamente difícil), ele foi validado em múltiplos idiomas e contextos culturais, permitindo comparar resultados entre populações e serviços diferentes.&lt;/p&gt;&lt;p&gt;Vale ainda registrar que o instrumento é &lt;strong&gt;autoaplicável&lt;/strong&gt;: o próprio paciente responde. Longe de ser limitação, isso &lt;strong&gt;reduz o viés do observador&lt;/strong&gt;, respeita a natureza subjetiva do sintoma e viabiliza a aplicação em larga escala, inclusive em pesquisa.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Entre os questionários mais simples, considerado válido transculturalmente&lt;/strong&gt;: correta. A ancoragem em números e domínios funcionais universais permitiu validação em múltiplos idiomas e culturas.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Aplicado pelo médico, diminuindo vieses&lt;/strong&gt;: incorreta. É autoaplicável, e é a autoaplicação que reduz o viés do observador.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dispensa a representação gráfica do questionário de McGill&lt;/strong&gt;: incorreta. São instrumentos distintos e complementares, sem relação de substituição.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dispensa perguntas sobre características da dor e sintomas associados&lt;/strong&gt;: incorreta. Avalia intensidade e interferência funcional, o que o define como instrumento multidimensional.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ventiladores com pistão usam câmara de baixa complacência e deslocamento controlado, permitindo entrega mais precisa do volume corrente, com menor influência da compressibilidade do sistema.</t>
+          <t>&lt;p&gt;A precisão do volume corrente entregue por um ventilador depende de uma única variável física: &lt;strong&gt;quanto do volume deslocado pelo mecanismo motor se perde por compressão antes de chegar ao paciente&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;ventilador com fole&lt;/strong&gt;, o volume é empurrado por &lt;strong&gt;gás comprimido&lt;/strong&gt; que preenche a carcaça rígida ao redor do fole. Esse &lt;strong&gt;gás propulsor é compressível&lt;/strong&gt;, e o grau de compressão varia com a pressão gerada no sistema: quanto maior a resistência das vias aéreas ou menor a complacência pulmonar, maior a fração do volume deslocado que se perde comprimindo gás em vez de ventilar o paciente. O volume efetivamente entregue passa a depender da mecânica respiratória, fonte de imprecisão.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;ventilador com pistão&lt;/strong&gt;, o desenho elimina essa variável. Um &lt;strong&gt;motor de passo controlado por computador&lt;/strong&gt; substitui o gás propulsor, de modo que se trata de um sistema de &lt;strong&gt;circuito único&lt;/strong&gt;, sem circuito separado de gás motriz. O pistão opera &lt;strong&gt;como o êmbolo de uma seringa em um cilindro de complacência essencialmente nula&lt;/strong&gt;: o deslocamento mecânico do êmbolo corresponde quase integralmente ao volume entregue, porque praticamente nada se perde por compressão. É exatamente a &lt;strong&gt;baixa complacência da câmara do pistão&lt;/strong&gt; que confere ao dispositivo o potencial de entrega muito acurada do volume corrente.&lt;/p&gt;&lt;p&gt;Há vantagens acessórias que não se confundem com a causa da precisão: sem gás comprimido para acionar o fole, esses sistemas &lt;strong&gt;consomem drasticamente menos gás comprimido&lt;/strong&gt;, o que tem valor clínico em locais remotos ou sem rede de gases. E vale notar que, em ambos os tipos, a &lt;strong&gt;compensação de complacência do circuito&lt;/strong&gt; e a medida do volume inspirado funcionam como sinais de retroalimentação para estabilizar a entrega.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Câmara do pistão eletrônico com baixa complacência&lt;/strong&gt;: correta. É a razão física da precisão: quase nada do volume deslocado se perde por compressão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bolsa reservatório fora do circuito durante a ventilação&lt;/strong&gt;: incorreta. Não é o fator determinante da acurácia do volume entregue.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Peso associado à gravidade na fase descendente&lt;/strong&gt;: incorreta. Descreve o fole descendente clássico, não o mecanismo do pistão.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Força motriz eletronicamente controlada&lt;/strong&gt;: incorreta como explicação da precisão. O motor de passo governa o deslocamento, mas quem elimina a perda por compressão é a baixa complacência da câmara.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Segurança do paciente envolve prevenir, evitar e reduzir danos relacionados aos processos assistenciais. Melhoria da qualidade é contínua, baseada em medição, revisão e intervenção.</t>
+          <t>&lt;p&gt;A questão é de &lt;strong&gt;precisão terminológica&lt;/strong&gt;, e a confusão entre os termos é justamente o que ela testa, trocando as definições entre si. Vale fixar cada conceito por aquilo que o distingue.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Segurança do paciente&lt;/strong&gt; é a definição mais ampla e a que estrutura toda a disciplina: consiste em &lt;strong&gt;evitar, prevenir e melhorar&lt;/strong&gt; os resultados adversos ou as lesões decorrentes dos &lt;strong&gt;processos de assistência à saúde&lt;/strong&gt;. Repare em dois elementos. O primeiro é o escopo tríplice: não basta evitar o dano depois de identificado o risco; é preciso preveni-lo por desenho de sistema e melhorar continuamente os desfechos quando ele ocorre. O segundo é a fonte do dano: os &lt;strong&gt;processos de cuidado&lt;/strong&gt;, e não a doença de base. É essa delimitação que separa o campo da segurança do campo da evolução natural da doença.&lt;/p&gt;&lt;p&gt;Os demais termos ocupam posições hierárquicas distintas. O &lt;strong&gt;acidente&lt;/strong&gt;, ou incidente, é o &lt;strong&gt;evento não planejado, inesperado e indesejado&lt;/strong&gt;, que pode ou não resultar em dano; é a ocorrência, independentemente de sua consequência. O &lt;strong&gt;evento adverso&lt;/strong&gt; é o &lt;strong&gt;dano causado pelo manejo em saúde&lt;/strong&gt;, e não pela doença subjacente, podendo resultar em incapacidade mensurável, prolongamento da internação ou morte. Nem todo acidente gera evento adverso, e é precisamente por isso que os &lt;strong&gt;quase-erros&lt;/strong&gt; são tão valiosos: revelam falhas latentes do sistema sem que um paciente tenha sido lesado.&lt;/p&gt;&lt;p&gt;Por fim, a &lt;strong&gt;melhoria da qualidade&lt;/strong&gt; é &lt;strong&gt;processo contínuo e cíclico&lt;/strong&gt; (medir, revisar, intervir e medir novamente), e não uma atividade episódica. Sua lógica é &lt;strong&gt;sistêmica&lt;/strong&gt;: busca as condições latentes que permitiram o erro, em vez de responsabilizar o indivíduo na ponta.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Segurança do paciente como evitar, prevenir e melhorar resultados adversos decorrentes dos processos de assistência&lt;/strong&gt;: correta. É a definição consagrada, delimitando o dano originado no cuidado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Melhoria da qualidade como processo ocasional&lt;/strong&gt;: incorreta. Trata-se de ciclo contínuo de medição, revisão e intervenção.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Acidente como lesão causada pelo tratamento médico com incapacidade mensurável&lt;/strong&gt;: incorreta. Essa é a definição de lesão iatrogênica; acidente é o evento não planejado, com ou sem dano.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Evento adverso como evento não planejado, inesperado e indesejado&lt;/strong&gt;: incorreta. Essa formulação define acidente; evento adverso é o dano decorrente do cuidado.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Com custo de superutilização duas vezes maior, deve-se comparar subutilização + 2 × superutilização. A reserva de 10 horas apresenta a menor ineficiência total no quadro fornecido.</t>
+          <t>&lt;p&gt;O problema é de &lt;strong&gt;otimização assimétrica&lt;/strong&gt;, e toda a sua lógica está na assimetria de custos: cada hora de &lt;strong&gt;superutilização&lt;/strong&gt; custa o dobro de cada hora de &lt;strong&gt;subutilização&lt;/strong&gt;. A função a minimizar é &lt;strong&gt;ineficiência = horas subutilizadas + 2 × horas superutilizadas&lt;/strong&gt;, com utilização média fixa em &lt;strong&gt;9 horas&lt;/strong&gt; semanais.&lt;/p&gt;&lt;p&gt;Basta aplicar a fórmula a cada opção de reserva. Com &lt;strong&gt;reserva zero&lt;/strong&gt;, as 9 horas efetivamente utilizadas são todas excedentes: 2 × 9 = &lt;strong&gt;18&lt;/strong&gt;. Com &lt;strong&gt;8 horas&lt;/strong&gt; reservadas, a utilização excede a reserva em 1 hora: 2 × 1 = &lt;strong&gt;2&lt;/strong&gt;. Com &lt;strong&gt;10 horas&lt;/strong&gt; reservadas, sobra 1 hora ociosa: 1 × 1 = &lt;strong&gt;1&lt;/strong&gt;. Com &lt;strong&gt;13 horas&lt;/strong&gt;, sobram 4 horas ociosas: 4 × 1 = &lt;strong&gt;4&lt;/strong&gt;. O mínimo é &lt;strong&gt;10 horas&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O resultado carrega uma lição de gestão que vale além do cálculo. Como a superutilização custa o dobro, &lt;strong&gt;compensa reservar ligeiramente mais do que a utilização média&lt;/strong&gt;, a chamada margem de segurança. Reservar exatamente a média, ou menos, expõe o serviço ao custo dobrado das horas extras: pessoal em regime extraordinário, atraso de casos subsequentes, cancelamentos e desgaste da equipe. Reservar muito acima, por outro lado, desperdiça capacidade instalada que poderia servir a outras especialidades, embora a um custo unitário menor.&lt;/p&gt;&lt;p&gt;Vale ainda registrar que a utilização real varia semana a semana em torno da média. Uma análise mais refinada consideraria a &lt;strong&gt;distribuição&lt;/strong&gt; dessa variabilidade, e não apenas o valor médio: quanto maior a dispersão, maior a margem que compensa reservar, dado o custo assimétrico das horas excedentes.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;10 horas&lt;/strong&gt;: correta. Produz ineficiência de 1, o menor valor entre as opções, refletindo o princípio de reservar uma pequena margem acima da média quando a superutilização custa o dobro.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;0 horas&lt;/strong&gt;: incorreta. Todas as 9 horas seriam superutilização, com ineficiência de 18.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;8 horas&lt;/strong&gt;: incorreta. Gera 1 hora de superutilização, com ineficiência de 2.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;13 horas&lt;/strong&gt;: incorreta. Deixa 4 horas ociosas, com ineficiência de 4.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fibrinogênio de 0,6 g/L causa redução importante da firmeza do coágulo nos testes viscoelásticos, representada por baixa amplitude máxima. A figura C corresponde ao traçado de hipofibrinogenemia indicado no gabarito.</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;testes viscoelásticos&lt;/strong&gt; (tromboelastografia e tromboelastometria rotacional) avaliam a formação e a dissolução do coágulo &lt;strong&gt;em sangue total e em tempo real&lt;/strong&gt;, oferecendo o que os testes convencionais de coagulação não fornecem: informação sobre a &lt;strong&gt;firmeza&lt;/strong&gt; do coágulo e sobre a &lt;strong&gt;fibrinólise&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O achado do caso é um &lt;strong&gt;fibrinogênio sérico de 0,6 g/L&lt;/strong&gt;, valor muito abaixo do limiar habitual de 1,5 a 2,0 g/L para o paciente cirúrgico sangrante, e criticamente baixo na fase &lt;strong&gt;pré-anepática&lt;/strong&gt; do transplante hepático, quando a síntese hepática já está comprometida e a manipulação cirúrgica antecede o clampeamento vascular.&lt;/p&gt;&lt;p&gt;A tradução gráfica da &lt;strong&gt;hipofibrinogenemia&lt;/strong&gt; obedece a uma lógica precisa. A &lt;strong&gt;amplitude máxima&lt;/strong&gt; do traçado expressa a &lt;strong&gt;firmeza do coágulo&lt;/strong&gt;, que resulta de duas contribuições: a &lt;strong&gt;rede de fibrina&lt;/strong&gt; e as &lt;strong&gt;plaquetas&lt;/strong&gt;. Os equipamentos separam essas contribuições em canais distintos: um ensaio com &lt;strong&gt;inibidor plaquetário&lt;/strong&gt; (o canal do fibrinogênio) isola a contribuição da fibrina, enquanto o ensaio padrão reflete ambas. Na hipofibrinogenemia isolada, o traçado característico exibe &lt;strong&gt;amplitude máxima acentuadamente reduzida no canal sensível ao fibrinogênio&lt;/strong&gt;, com contribuição plaquetária preservada, gerando um traçado &lt;strong&gt;estreito e de baixa amplitude&lt;/strong&gt;. Os tempos iniciais de coagulação podem permanecer relativamente pouco alterados, o que ilustra por que o teste viscoelástico identifica o defeito que os testes convencionais deixariam passar.&lt;/p&gt;&lt;p&gt;A conduta derivada é &lt;strong&gt;específica&lt;/strong&gt;: repor fibrinogênio, por &lt;strong&gt;concentrado de fibrinogênio&lt;/strong&gt; ou &lt;strong&gt;crioprecipitado&lt;/strong&gt;, em vez de transfundir plasma fresco congelado de forma empírica; a reposição dirigida por teste viscoelástico reduz o volume total de hemocomponentes no transplante hepático.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Traçado com amplitude máxima acentuadamente reduzida no canal sensível ao fibrinogênio, com contribuição plaquetária preservada&lt;/strong&gt;: é o padrão da hipofibrinogenemia, e a conduta é reposição de fibrinogênio ou crioprecipitado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Traçados com prolongamento isolado do tempo de coagulação, ou com queda tardia da amplitude&lt;/strong&gt;: correspondem, respectivamente, a deficiência de fatores da via de iniciação e a fibrinólise, e não ao defeito de fibrinogênio descrito.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
